--- a/docs/Ancestry_MMM_Activity_Dictionary_Builder.xlsx
+++ b/docs/Ancestry_MMM_Activity_Dictionary_Builder.xlsx
@@ -14,7 +14,7 @@
     <sheet name="EXAMPLES" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ALLOWED_VALUES'!$A$1:$D$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ALLOWED_VALUES'!$A$1:$D$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -202,9 +202,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ActivityCandidates" displayName="ActivityCandidates" ref="A7:Z31" headerRowCount="1">
-  <autoFilter ref="A7:Z31"/>
-  <tableColumns count="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ActivityCandidates" displayName="ActivityCandidates" ref="A7:X31" headerRowCount="1">
+  <autoFilter ref="A7:X31"/>
+  <tableColumns count="24">
     <tableColumn id="1" name="channel"/>
     <tableColumn id="2" name="market"/>
     <tableColumn id="3" name="activity_ownership"/>
@@ -221,16 +221,14 @@
     <tableColumn id="14" name="Row status"/>
     <tableColumn id="15" name="platform"/>
     <tableColumn id="16" name="campaign_type"/>
-    <tableColumn id="17" name="search_platform"/>
-    <tableColumn id="18" name="search_intent_group_id"/>
-    <tableColumn id="19" name="pooling_group_id"/>
-    <tableColumn id="20" name="funnel_stage"/>
-    <tableColumn id="21" name="marketing_objective"/>
-    <tableColumn id="22" name="product_advertised"/>
-    <tableColumn id="23" name="message_type"/>
-    <tableColumn id="24" name="currency"/>
-    <tableColumn id="25" name="effective_from"/>
-    <tableColumn id="26" name="effective_to"/>
+    <tableColumn id="17" name="pooling_group_id"/>
+    <tableColumn id="18" name="funnel_stage"/>
+    <tableColumn id="19" name="marketing_objective"/>
+    <tableColumn id="20" name="product_advertised"/>
+    <tableColumn id="21" name="message_type"/>
+    <tableColumn id="22" name="currency"/>
+    <tableColumn id="23" name="effective_from"/>
+    <tableColumn id="24" name="effective_to"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -559,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -617,7 +615,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>For Paid Search activities you want split by Brand/Non-Brand and Google/Bing, also fill in campaign_type, search_platform, and search_intent_group_id -- these help build a clear id.</t>
+          <t>For Paid Search activities you want split by Google/Bing and Brand/Non-Brand, also fill in platform and campaign_type -- the same two ordinary dictionary fields any other channel would use, not special Search-only inputs.</t>
         </is>
       </c>
     </row>
@@ -638,7 +636,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Generated ID -- built from channel plus whichever of platform, campaign_type, search_platform, and search_intent_group_id you filled in.</t>
+          <t>Generated ID -- built from channel plus whichever of platform and campaign_type you filled in.</t>
         </is>
       </c>
     </row>
@@ -680,7 +678,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Conditional (amber columns, Paid Search identity only): platform, campaign_type, search_platform, search_intent_group_id.</t>
+          <t>Conditional (amber columns): platform, campaign_type -- fill these in when they help distinguish one activity from another (Google vs Bing, Brand vs Non-Brand); the upload does currently reject a truly empty cell, so a blank one defaults to not specified in DICTIONARY_OUTPUT.</t>
         </is>
       </c>
     </row>
@@ -698,57 +696,64 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Also not asked at all: search_platform and search_intent_group_id. They are not activity_dictionary columns today -- activity_definitions_from_dictionary still doesn't map them from a standard workbook -- so this builder does not pretend they are ordinary fields. The governed Search-taxonomy mapping (Brand/Non-Brand, Google/Bing at the ActivityDefinition level) is configured separately, after upload, until that mapping gap is closed. Use platform and campaign_type above to keep your activity_id readable in the meantime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>How dropdowns work</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>activity_ownership, intended_model_role, economic_treatment, planning_eligibility, funnel_stage, search_platform, and search_intent_group_id are dropdowns built from the app's own governed lists. campaign_type and marketing_objective offer suggestions but also accept free text, matching how the app actually treats them. See the ALLOWED_VALUES sheet for the full, current set with plain-English explanations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>activity_ownership, intended_model_role, economic_treatment, planning_eligibility, and funnel_stage are dropdowns built from the app's own governed lists. campaign_type and marketing_objective offer suggestions but also accept free text, matching how the app actually treats them. See the ALLOWED_VALUES sheet for the full, current set with plain-English explanations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>How validation works</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>The Row status column recalculates automatically as you type. It tells you in plain English whether a row is Ready, missing a required field, or a duplicate activity_id -- fix the thing it names, then check again.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Where the final dictionary output goes</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Select every data row of the DICTIONARY_OUTPUT sheet, copy, and Paste Special &gt; Values into the activity_dictionary sheet of the standard Activity and Media upload workbook.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Where the actual weekly activity numbers go</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>This builder never asks for your weekly spend, clicks, or impressions. Those go in the activity_data sheet of the same upload workbook, one row per period_start x market x activity_id.</t>
         </is>
@@ -765,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ31"/>
+  <dimension ref="A1:AI31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -792,8 +797,8 @@
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="2" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="2" customWidth="1" min="28" max="28"/>
     <col hidden="1" width="2" customWidth="1" min="29" max="29"/>
     <col hidden="1" width="2" customWidth="1" min="30" max="30"/>
     <col hidden="1" width="2" customWidth="1" min="31" max="31"/>
@@ -801,14 +806,6 @@
     <col hidden="1" width="2" customWidth="1" min="33" max="33"/>
     <col hidden="1" width="2" customWidth="1" min="34" max="34"/>
     <col hidden="1" width="2" customWidth="1" min="35" max="35"/>
-    <col hidden="1" width="2" customWidth="1" min="36" max="36"/>
-    <col hidden="1" width="2" customWidth="1" min="37" max="37"/>
-    <col hidden="1" width="2" customWidth="1" min="38" max="38"/>
-    <col hidden="1" width="2" customWidth="1" min="39" max="39"/>
-    <col hidden="1" width="2" customWidth="1" min="40" max="40"/>
-    <col hidden="1" width="2" customWidth="1" min="41" max="41"/>
-    <col hidden="1" width="2" customWidth="1" min="42" max="42"/>
-    <col hidden="1" width="2" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -847,14 +844,6 @@
       <c r="AG1" s="4" t="n"/>
       <c r="AH1" s="4" t="n"/>
       <c r="AI1" s="4" t="n"/>
-      <c r="AJ1" s="4" t="n"/>
-      <c r="AK1" s="4" t="n"/>
-      <c r="AL1" s="4" t="n"/>
-      <c r="AM1" s="4" t="n"/>
-      <c r="AN1" s="4" t="n"/>
-      <c r="AO1" s="4" t="n"/>
-      <c r="AP1" s="4" t="n"/>
-      <c r="AQ1" s="4" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr"/>
@@ -892,14 +881,6 @@
       <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="4" t="n"/>
       <c r="AI2" s="4" t="n"/>
-      <c r="AJ2" s="4" t="n"/>
-      <c r="AK2" s="4" t="n"/>
-      <c r="AL2" s="4" t="n"/>
-      <c r="AM2" s="4" t="n"/>
-      <c r="AN2" s="4" t="n"/>
-      <c r="AO2" s="4" t="n"/>
-      <c r="AP2" s="4" t="n"/>
-      <c r="AQ2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr"/>
@@ -937,14 +918,6 @@
       <c r="AG3" s="4" t="n"/>
       <c r="AH3" s="4" t="n"/>
       <c r="AI3" s="4" t="n"/>
-      <c r="AJ3" s="4" t="n"/>
-      <c r="AK3" s="4" t="n"/>
-      <c r="AL3" s="4" t="n"/>
-      <c r="AM3" s="4" t="n"/>
-      <c r="AN3" s="4" t="n"/>
-      <c r="AO3" s="4" t="n"/>
-      <c r="AP3" s="4" t="n"/>
-      <c r="AQ3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr"/>
@@ -982,14 +955,6 @@
       <c r="AG4" s="4" t="n"/>
       <c r="AH4" s="4" t="n"/>
       <c r="AI4" s="4" t="n"/>
-      <c r="AJ4" s="4" t="n"/>
-      <c r="AK4" s="4" t="n"/>
-      <c r="AL4" s="4" t="n"/>
-      <c r="AM4" s="4" t="n"/>
-      <c r="AN4" s="4" t="n"/>
-      <c r="AO4" s="4" t="n"/>
-      <c r="AP4" s="4" t="n"/>
-      <c r="AQ4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr"/>
@@ -1027,14 +992,6 @@
       <c r="AG5" s="4" t="n"/>
       <c r="AH5" s="4" t="n"/>
       <c r="AI5" s="4" t="n"/>
-      <c r="AJ5" s="4" t="n"/>
-      <c r="AK5" s="4" t="n"/>
-      <c r="AL5" s="4" t="n"/>
-      <c r="AM5" s="4" t="n"/>
-      <c r="AN5" s="4" t="n"/>
-      <c r="AO5" s="4" t="n"/>
-      <c r="AP5" s="4" t="n"/>
-      <c r="AQ5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr"/>
@@ -1072,14 +1029,6 @@
       <c r="AG6" s="4" t="n"/>
       <c r="AH6" s="4" t="n"/>
       <c r="AI6" s="4" t="n"/>
-      <c r="AJ6" s="4" t="n"/>
-      <c r="AK6" s="4" t="n"/>
-      <c r="AL6" s="4" t="n"/>
-      <c r="AM6" s="4" t="n"/>
-      <c r="AN6" s="4" t="n"/>
-      <c r="AO6" s="4" t="n"/>
-      <c r="AP6" s="4" t="n"/>
-      <c r="AQ6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1162,131 +1111,91 @@
           <t>campaign_type</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>search_platform</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>search_intent_group_id</t>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>pooling_group_id</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>funnel_stage</t>
         </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>pooling_group_id</t>
+          <t>marketing_objective</t>
         </is>
       </c>
       <c r="T7" s="7" t="inlineStr">
         <is>
-          <t>funnel_stage</t>
+          <t>product_advertised</t>
         </is>
       </c>
       <c r="U7" s="7" t="inlineStr">
         <is>
-          <t>marketing_objective</t>
+          <t>message_type</t>
         </is>
       </c>
       <c r="V7" s="7" t="inlineStr">
         <is>
-          <t>product_advertised</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="W7" s="7" t="inlineStr">
         <is>
-          <t>message_type</t>
+          <t>effective_from</t>
         </is>
       </c>
       <c r="X7" s="7" t="inlineStr">
         <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="Y7" s="7" t="inlineStr">
-        <is>
-          <t>effective_from</t>
-        </is>
-      </c>
-      <c r="Z7" s="7" t="inlineStr">
-        <is>
           <t>effective_to</t>
         </is>
       </c>
-      <c r="AA7" s="5" t="n"/>
-      <c r="AB7" s="5" t="n"/>
+      <c r="Y7" s="5" t="n"/>
+      <c r="Z7" s="5" t="n"/>
+      <c r="AA7" s="5" t="inlineStr">
+        <is>
+          <t>_A_clean</t>
+        </is>
+      </c>
+      <c r="AB7" s="5" t="inlineStr">
+        <is>
+          <t>_A_collapsed</t>
+        </is>
+      </c>
       <c r="AC7" s="5" t="inlineStr">
         <is>
-          <t>_A_clean</t>
+          <t>_A_token</t>
         </is>
       </c>
       <c r="AD7" s="5" t="inlineStr">
         <is>
-          <t>_A_collapsed</t>
+          <t>_O_clean</t>
         </is>
       </c>
       <c r="AE7" s="5" t="inlineStr">
         <is>
-          <t>_A_token</t>
+          <t>_O_collapsed</t>
         </is>
       </c>
       <c r="AF7" s="5" t="inlineStr">
         <is>
-          <t>_O_clean</t>
+          <t>_O_token</t>
         </is>
       </c>
       <c r="AG7" s="5" t="inlineStr">
         <is>
-          <t>_O_collapsed</t>
+          <t>_P_clean</t>
         </is>
       </c>
       <c r="AH7" s="5" t="inlineStr">
         <is>
-          <t>_O_token</t>
+          <t>_P_collapsed</t>
         </is>
       </c>
       <c r="AI7" s="5" t="inlineStr">
         <is>
-          <t>_P_clean</t>
-        </is>
-      </c>
-      <c r="AJ7" s="5" t="inlineStr">
-        <is>
-          <t>_P_collapsed</t>
-        </is>
-      </c>
-      <c r="AK7" s="5" t="inlineStr">
-        <is>
           <t>_P_token</t>
-        </is>
-      </c>
-      <c r="AL7" s="5" t="inlineStr">
-        <is>
-          <t>_Q_clean</t>
-        </is>
-      </c>
-      <c r="AM7" s="5" t="inlineStr">
-        <is>
-          <t>_Q_collapsed</t>
-        </is>
-      </c>
-      <c r="AN7" s="5" t="inlineStr">
-        <is>
-          <t>_Q_token</t>
-        </is>
-      </c>
-      <c r="AO7" s="5" t="inlineStr">
-        <is>
-          <t>_R_clean</t>
-        </is>
-      </c>
-      <c r="AP7" s="5" t="inlineStr">
-        <is>
-          <t>_R_collapsed</t>
-        </is>
-      </c>
-      <c r="AQ7" s="5" t="inlineStr">
-        <is>
-          <t>_R_token</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1244,7 @@
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4">
-        <f>IF(AE8&lt;&gt;"",AE8,"")&amp;IF(AH8&lt;&gt;"",IF(AE8&lt;&gt;"","_"&amp;AH8,AH8),"")&amp;IF(AK8&lt;&gt;"",IF(AE8&lt;&gt;"","_"&amp;AK8,AK8),"")&amp;IF(AN8&lt;&gt;"",IF(AE8&lt;&gt;"","_"&amp;AN8,AN8),"")&amp;IF(AQ8&lt;&gt;"",IF(AE8&lt;&gt;"","_"&amp;AQ8,AQ8),"")</f>
+        <f>IF(AC8&lt;&gt;"",AC8,"")&amp;IF(AF8&lt;&gt;"",IF(AC8&lt;&gt;"","_"&amp;AF8,AF8),"")&amp;IF(AI8&lt;&gt;"",IF(AC8&lt;&gt;"","_"&amp;AI8,AI8),"")</f>
         <v/>
       </c>
       <c r="M8" s="4">
@@ -1356,84 +1265,50 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="R8" s="4" t="inlineStr">
-        <is>
-          <t>brand_search</t>
-        </is>
-      </c>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="4" t="inlineStr"/>
       <c r="U8" s="4" t="inlineStr"/>
       <c r="V8" s="4" t="inlineStr"/>
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="4" t="inlineStr"/>
-      <c r="AA8" s="4" t="n"/>
-      <c r="AB8" s="4" t="n"/>
+      <c r="Y8" s="4" t="n"/>
+      <c r="Z8" s="4" t="n"/>
+      <c r="AA8" s="4">
+        <f>IF(OR(LOWER(TRIM(A8))="",LOWER(TRIM(A8))="nan",LOWER(TRIM(A8))="none",LOWER(TRIM(A8))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A8))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB8" s="4">
+        <f>IF(AA8="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA8,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC8" s="4">
-        <f>IF(OR(LOWER(TRIM(A8))="",LOWER(TRIM(A8))="nan",LOWER(TRIM(A8))="none",LOWER(TRIM(A8))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A8))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB8="",AB8="_"),"",IF(LEFT(AB8,1)="_",IF(RIGHT(AB8,1)="_",MID(AB8,2,LEN(AB8)-2),RIGHT(AB8,LEN(AB8)-1)),IF(RIGHT(AB8,1)="_",LEFT(AB8,LEN(AB8)-1),AB8)))</f>
         <v/>
       </c>
       <c r="AD8" s="4">
-        <f>IF(AC8="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC8,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O8))="",LOWER(TRIM(O8))="nan",LOWER(TRIM(O8))="none",LOWER(TRIM(O8))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O8))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE8" s="4">
-        <f>IF(OR(AD8="",AD8="_"),"",IF(LEFT(AD8,1)="_",IF(RIGHT(AD8,1)="_",MID(AD8,2,LEN(AD8)-2),RIGHT(AD8,LEN(AD8)-1)),IF(RIGHT(AD8,1)="_",LEFT(AD8,LEN(AD8)-1),AD8)))</f>
+        <f>IF(AD8="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD8,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF8" s="4">
-        <f>IF(OR(LOWER(TRIM(O8))="",LOWER(TRIM(O8))="nan",LOWER(TRIM(O8))="none",LOWER(TRIM(O8))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O8))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE8="",AE8="_"),"",IF(LEFT(AE8,1)="_",IF(RIGHT(AE8,1)="_",MID(AE8,2,LEN(AE8)-2),RIGHT(AE8,LEN(AE8)-1)),IF(RIGHT(AE8,1)="_",LEFT(AE8,LEN(AE8)-1),AE8)))</f>
         <v/>
       </c>
       <c r="AG8" s="4">
-        <f>IF(AF8="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF8,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P8))="",LOWER(TRIM(P8))="nan",LOWER(TRIM(P8))="none",LOWER(TRIM(P8))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P8))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH8" s="4">
-        <f>IF(OR(AG8="",AG8="_"),"",IF(LEFT(AG8,1)="_",IF(RIGHT(AG8,1)="_",MID(AG8,2,LEN(AG8)-2),RIGHT(AG8,LEN(AG8)-1)),IF(RIGHT(AG8,1)="_",LEFT(AG8,LEN(AG8)-1),AG8)))</f>
+        <f>IF(AG8="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG8,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI8" s="4">
-        <f>IF(OR(LOWER(TRIM(P8))="",LOWER(TRIM(P8))="nan",LOWER(TRIM(P8))="none",LOWER(TRIM(P8))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P8))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="4">
-        <f>IF(AI8="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI8,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK8" s="4">
-        <f>IF(OR(AJ8="",AJ8="_"),"",IF(LEFT(AJ8,1)="_",IF(RIGHT(AJ8,1)="_",MID(AJ8,2,LEN(AJ8)-2),RIGHT(AJ8,LEN(AJ8)-1)),IF(RIGHT(AJ8,1)="_",LEFT(AJ8,LEN(AJ8)-1),AJ8)))</f>
-        <v/>
-      </c>
-      <c r="AL8" s="4">
-        <f>IF(OR(LOWER(TRIM(Q8))="",LOWER(TRIM(Q8))="nan",LOWER(TRIM(Q8))="none",LOWER(TRIM(Q8))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q8))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM8" s="4">
-        <f>IF(AL8="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL8,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN8" s="4">
-        <f>IF(OR(AM8="",AM8="_"),"",IF(LEFT(AM8,1)="_",IF(RIGHT(AM8,1)="_",MID(AM8,2,LEN(AM8)-2),RIGHT(AM8,LEN(AM8)-1)),IF(RIGHT(AM8,1)="_",LEFT(AM8,LEN(AM8)-1),AM8)))</f>
-        <v/>
-      </c>
-      <c r="AO8" s="4">
-        <f>IF(OR(LOWER(TRIM(R8))="",LOWER(TRIM(R8))="nan",LOWER(TRIM(R8))="none",LOWER(TRIM(R8))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R8))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP8" s="4">
-        <f>IF(AO8="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO8,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ8" s="4">
-        <f>IF(OR(AP8="",AP8="_"),"",IF(LEFT(AP8,1)="_",IF(RIGHT(AP8,1)="_",MID(AP8,2,LEN(AP8)-2),RIGHT(AP8,LEN(AP8)-1)),IF(RIGHT(AP8,1)="_",LEFT(AP8,LEN(AP8)-1),AP8)))</f>
+        <f>IF(OR(AH8="",AH8="_"),"",IF(LEFT(AH8,1)="_",IF(RIGHT(AH8,1)="_",MID(AH8,2,LEN(AH8)-2),RIGHT(AH8,LEN(AH8)-1)),IF(RIGHT(AH8,1)="_",LEFT(AH8,LEN(AH8)-1),AH8)))</f>
         <v/>
       </c>
     </row>
@@ -1482,7 +1357,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4">
-        <f>IF(AE9&lt;&gt;"",AE9,"")&amp;IF(AH9&lt;&gt;"",IF(AE9&lt;&gt;"","_"&amp;AH9,AH9),"")&amp;IF(AK9&lt;&gt;"",IF(AE9&lt;&gt;"","_"&amp;AK9,AK9),"")&amp;IF(AN9&lt;&gt;"",IF(AE9&lt;&gt;"","_"&amp;AN9,AN9),"")&amp;IF(AQ9&lt;&gt;"",IF(AE9&lt;&gt;"","_"&amp;AQ9,AQ9),"")</f>
+        <f>IF(AC9&lt;&gt;"",AC9,"")&amp;IF(AF9&lt;&gt;"",IF(AC9&lt;&gt;"","_"&amp;AF9,AF9),"")&amp;IF(AI9&lt;&gt;"",IF(AC9&lt;&gt;"","_"&amp;AI9,AI9),"")</f>
         <v/>
       </c>
       <c r="M9" s="4">
@@ -1503,84 +1378,50 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
-        <is>
-          <t>bing</t>
-        </is>
-      </c>
-      <c r="R9" s="4" t="inlineStr">
-        <is>
-          <t>brand_search</t>
-        </is>
-      </c>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="4" t="inlineStr"/>
       <c r="T9" s="4" t="inlineStr"/>
       <c r="U9" s="4" t="inlineStr"/>
       <c r="V9" s="4" t="inlineStr"/>
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="4" t="inlineStr"/>
-      <c r="AA9" s="4" t="n"/>
-      <c r="AB9" s="4" t="n"/>
+      <c r="Y9" s="4" t="n"/>
+      <c r="Z9" s="4" t="n"/>
+      <c r="AA9" s="4">
+        <f>IF(OR(LOWER(TRIM(A9))="",LOWER(TRIM(A9))="nan",LOWER(TRIM(A9))="none",LOWER(TRIM(A9))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A9))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB9" s="4">
+        <f>IF(AA9="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA9,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC9" s="4">
-        <f>IF(OR(LOWER(TRIM(A9))="",LOWER(TRIM(A9))="nan",LOWER(TRIM(A9))="none",LOWER(TRIM(A9))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A9))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB9="",AB9="_"),"",IF(LEFT(AB9,1)="_",IF(RIGHT(AB9,1)="_",MID(AB9,2,LEN(AB9)-2),RIGHT(AB9,LEN(AB9)-1)),IF(RIGHT(AB9,1)="_",LEFT(AB9,LEN(AB9)-1),AB9)))</f>
         <v/>
       </c>
       <c r="AD9" s="4">
-        <f>IF(AC9="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC9,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O9))="",LOWER(TRIM(O9))="nan",LOWER(TRIM(O9))="none",LOWER(TRIM(O9))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O9))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE9" s="4">
-        <f>IF(OR(AD9="",AD9="_"),"",IF(LEFT(AD9,1)="_",IF(RIGHT(AD9,1)="_",MID(AD9,2,LEN(AD9)-2),RIGHT(AD9,LEN(AD9)-1)),IF(RIGHT(AD9,1)="_",LEFT(AD9,LEN(AD9)-1),AD9)))</f>
+        <f>IF(AD9="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD9,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF9" s="4">
-        <f>IF(OR(LOWER(TRIM(O9))="",LOWER(TRIM(O9))="nan",LOWER(TRIM(O9))="none",LOWER(TRIM(O9))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O9))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE9="",AE9="_"),"",IF(LEFT(AE9,1)="_",IF(RIGHT(AE9,1)="_",MID(AE9,2,LEN(AE9)-2),RIGHT(AE9,LEN(AE9)-1)),IF(RIGHT(AE9,1)="_",LEFT(AE9,LEN(AE9)-1),AE9)))</f>
         <v/>
       </c>
       <c r="AG9" s="4">
-        <f>IF(AF9="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF9,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P9))="",LOWER(TRIM(P9))="nan",LOWER(TRIM(P9))="none",LOWER(TRIM(P9))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P9))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH9" s="4">
-        <f>IF(OR(AG9="",AG9="_"),"",IF(LEFT(AG9,1)="_",IF(RIGHT(AG9,1)="_",MID(AG9,2,LEN(AG9)-2),RIGHT(AG9,LEN(AG9)-1)),IF(RIGHT(AG9,1)="_",LEFT(AG9,LEN(AG9)-1),AG9)))</f>
+        <f>IF(AG9="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG9,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI9" s="4">
-        <f>IF(OR(LOWER(TRIM(P9))="",LOWER(TRIM(P9))="nan",LOWER(TRIM(P9))="none",LOWER(TRIM(P9))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P9))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ9" s="4">
-        <f>IF(AI9="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI9,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK9" s="4">
-        <f>IF(OR(AJ9="",AJ9="_"),"",IF(LEFT(AJ9,1)="_",IF(RIGHT(AJ9,1)="_",MID(AJ9,2,LEN(AJ9)-2),RIGHT(AJ9,LEN(AJ9)-1)),IF(RIGHT(AJ9,1)="_",LEFT(AJ9,LEN(AJ9)-1),AJ9)))</f>
-        <v/>
-      </c>
-      <c r="AL9" s="4">
-        <f>IF(OR(LOWER(TRIM(Q9))="",LOWER(TRIM(Q9))="nan",LOWER(TRIM(Q9))="none",LOWER(TRIM(Q9))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q9))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM9" s="4">
-        <f>IF(AL9="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL9,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN9" s="4">
-        <f>IF(OR(AM9="",AM9="_"),"",IF(LEFT(AM9,1)="_",IF(RIGHT(AM9,1)="_",MID(AM9,2,LEN(AM9)-2),RIGHT(AM9,LEN(AM9)-1)),IF(RIGHT(AM9,1)="_",LEFT(AM9,LEN(AM9)-1),AM9)))</f>
-        <v/>
-      </c>
-      <c r="AO9" s="4">
-        <f>IF(OR(LOWER(TRIM(R9))="",LOWER(TRIM(R9))="nan",LOWER(TRIM(R9))="none",LOWER(TRIM(R9))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R9))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP9" s="4">
-        <f>IF(AO9="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO9,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ9" s="4">
-        <f>IF(OR(AP9="",AP9="_"),"",IF(LEFT(AP9,1)="_",IF(RIGHT(AP9,1)="_",MID(AP9,2,LEN(AP9)-2),RIGHT(AP9,LEN(AP9)-1)),IF(RIGHT(AP9,1)="_",LEFT(AP9,LEN(AP9)-1),AP9)))</f>
+        <f>IF(OR(AH9="",AH9="_"),"",IF(LEFT(AH9,1)="_",IF(RIGHT(AH9,1)="_",MID(AH9,2,LEN(AH9)-2),RIGHT(AH9,LEN(AH9)-1)),IF(RIGHT(AH9,1)="_",LEFT(AH9,LEN(AH9)-1),AH9)))</f>
         <v/>
       </c>
     </row>
@@ -1629,7 +1470,7 @@
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="4">
-        <f>IF(AE10&lt;&gt;"",AE10,"")&amp;IF(AH10&lt;&gt;"",IF(AE10&lt;&gt;"","_"&amp;AH10,AH10),"")&amp;IF(AK10&lt;&gt;"",IF(AE10&lt;&gt;"","_"&amp;AK10,AK10),"")&amp;IF(AN10&lt;&gt;"",IF(AE10&lt;&gt;"","_"&amp;AN10,AN10),"")&amp;IF(AQ10&lt;&gt;"",IF(AE10&lt;&gt;"","_"&amp;AQ10,AQ10),"")</f>
+        <f>IF(AC10&lt;&gt;"",AC10,"")&amp;IF(AF10&lt;&gt;"",IF(AC10&lt;&gt;"","_"&amp;AF10,AF10),"")&amp;IF(AI10&lt;&gt;"",IF(AC10&lt;&gt;"","_"&amp;AI10,AI10),"")</f>
         <v/>
       </c>
       <c r="M10" s="4">
@@ -1650,68 +1491,42 @@
       <c r="V10" s="4" t="inlineStr"/>
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="4" t="inlineStr"/>
-      <c r="Z10" s="4" t="inlineStr"/>
-      <c r="AA10" s="4" t="n"/>
-      <c r="AB10" s="4" t="n"/>
+      <c r="Y10" s="4" t="n"/>
+      <c r="Z10" s="4" t="n"/>
+      <c r="AA10" s="4">
+        <f>IF(OR(LOWER(TRIM(A10))="",LOWER(TRIM(A10))="nan",LOWER(TRIM(A10))="none",LOWER(TRIM(A10))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A10))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB10" s="4">
+        <f>IF(AA10="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA10,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC10" s="4">
-        <f>IF(OR(LOWER(TRIM(A10))="",LOWER(TRIM(A10))="nan",LOWER(TRIM(A10))="none",LOWER(TRIM(A10))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A10))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB10="",AB10="_"),"",IF(LEFT(AB10,1)="_",IF(RIGHT(AB10,1)="_",MID(AB10,2,LEN(AB10)-2),RIGHT(AB10,LEN(AB10)-1)),IF(RIGHT(AB10,1)="_",LEFT(AB10,LEN(AB10)-1),AB10)))</f>
         <v/>
       </c>
       <c r="AD10" s="4">
-        <f>IF(AC10="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC10,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O10))="",LOWER(TRIM(O10))="nan",LOWER(TRIM(O10))="none",LOWER(TRIM(O10))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O10))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE10" s="4">
-        <f>IF(OR(AD10="",AD10="_"),"",IF(LEFT(AD10,1)="_",IF(RIGHT(AD10,1)="_",MID(AD10,2,LEN(AD10)-2),RIGHT(AD10,LEN(AD10)-1)),IF(RIGHT(AD10,1)="_",LEFT(AD10,LEN(AD10)-1),AD10)))</f>
+        <f>IF(AD10="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD10,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF10" s="4">
-        <f>IF(OR(LOWER(TRIM(O10))="",LOWER(TRIM(O10))="nan",LOWER(TRIM(O10))="none",LOWER(TRIM(O10))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O10))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE10="",AE10="_"),"",IF(LEFT(AE10,1)="_",IF(RIGHT(AE10,1)="_",MID(AE10,2,LEN(AE10)-2),RIGHT(AE10,LEN(AE10)-1)),IF(RIGHT(AE10,1)="_",LEFT(AE10,LEN(AE10)-1),AE10)))</f>
         <v/>
       </c>
       <c r="AG10" s="4">
-        <f>IF(AF10="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF10,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P10))="",LOWER(TRIM(P10))="nan",LOWER(TRIM(P10))="none",LOWER(TRIM(P10))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P10))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH10" s="4">
-        <f>IF(OR(AG10="",AG10="_"),"",IF(LEFT(AG10,1)="_",IF(RIGHT(AG10,1)="_",MID(AG10,2,LEN(AG10)-2),RIGHT(AG10,LEN(AG10)-1)),IF(RIGHT(AG10,1)="_",LEFT(AG10,LEN(AG10)-1),AG10)))</f>
+        <f>IF(AG10="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG10,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI10" s="4">
-        <f>IF(OR(LOWER(TRIM(P10))="",LOWER(TRIM(P10))="nan",LOWER(TRIM(P10))="none",LOWER(TRIM(P10))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P10))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ10" s="4">
-        <f>IF(AI10="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI10,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK10" s="4">
-        <f>IF(OR(AJ10="",AJ10="_"),"",IF(LEFT(AJ10,1)="_",IF(RIGHT(AJ10,1)="_",MID(AJ10,2,LEN(AJ10)-2),RIGHT(AJ10,LEN(AJ10)-1)),IF(RIGHT(AJ10,1)="_",LEFT(AJ10,LEN(AJ10)-1),AJ10)))</f>
-        <v/>
-      </c>
-      <c r="AL10" s="4">
-        <f>IF(OR(LOWER(TRIM(Q10))="",LOWER(TRIM(Q10))="nan",LOWER(TRIM(Q10))="none",LOWER(TRIM(Q10))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q10))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM10" s="4">
-        <f>IF(AL10="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL10,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN10" s="4">
-        <f>IF(OR(AM10="",AM10="_"),"",IF(LEFT(AM10,1)="_",IF(RIGHT(AM10,1)="_",MID(AM10,2,LEN(AM10)-2),RIGHT(AM10,LEN(AM10)-1)),IF(RIGHT(AM10,1)="_",LEFT(AM10,LEN(AM10)-1),AM10)))</f>
-        <v/>
-      </c>
-      <c r="AO10" s="4">
-        <f>IF(OR(LOWER(TRIM(R10))="",LOWER(TRIM(R10))="nan",LOWER(TRIM(R10))="none",LOWER(TRIM(R10))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R10))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP10" s="4">
-        <f>IF(AO10="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO10,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ10" s="4">
-        <f>IF(OR(AP10="",AP10="_"),"",IF(LEFT(AP10,1)="_",IF(RIGHT(AP10,1)="_",MID(AP10,2,LEN(AP10)-2),RIGHT(AP10,LEN(AP10)-1)),IF(RIGHT(AP10,1)="_",LEFT(AP10,LEN(AP10)-1),AP10)))</f>
+        <f>IF(OR(AH10="",AH10="_"),"",IF(LEFT(AH10,1)="_",IF(RIGHT(AH10,1)="_",MID(AH10,2,LEN(AH10)-2),RIGHT(AH10,LEN(AH10)-1)),IF(RIGHT(AH10,1)="_",LEFT(AH10,LEN(AH10)-1),AH10)))</f>
         <v/>
       </c>
     </row>
@@ -1760,7 +1575,7 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="4">
-        <f>IF(AE11&lt;&gt;"",AE11,"")&amp;IF(AH11&lt;&gt;"",IF(AE11&lt;&gt;"","_"&amp;AH11,AH11),"")&amp;IF(AK11&lt;&gt;"",IF(AE11&lt;&gt;"","_"&amp;AK11,AK11),"")&amp;IF(AN11&lt;&gt;"",IF(AE11&lt;&gt;"","_"&amp;AN11,AN11),"")&amp;IF(AQ11&lt;&gt;"",IF(AE11&lt;&gt;"","_"&amp;AQ11,AQ11),"")</f>
+        <f>IF(AC11&lt;&gt;"",AC11,"")&amp;IF(AF11&lt;&gt;"",IF(AC11&lt;&gt;"","_"&amp;AF11,AF11),"")&amp;IF(AI11&lt;&gt;"",IF(AC11&lt;&gt;"","_"&amp;AI11,AI11),"")</f>
         <v/>
       </c>
       <c r="M11" s="4">
@@ -1781,68 +1596,42 @@
       <c r="V11" s="4" t="inlineStr"/>
       <c r="W11" s="4" t="inlineStr"/>
       <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="4" t="inlineStr"/>
-      <c r="Z11" s="4" t="inlineStr"/>
-      <c r="AA11" s="4" t="n"/>
-      <c r="AB11" s="4" t="n"/>
+      <c r="Y11" s="4" t="n"/>
+      <c r="Z11" s="4" t="n"/>
+      <c r="AA11" s="4">
+        <f>IF(OR(LOWER(TRIM(A11))="",LOWER(TRIM(A11))="nan",LOWER(TRIM(A11))="none",LOWER(TRIM(A11))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A11))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB11" s="4">
+        <f>IF(AA11="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA11,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC11" s="4">
-        <f>IF(OR(LOWER(TRIM(A11))="",LOWER(TRIM(A11))="nan",LOWER(TRIM(A11))="none",LOWER(TRIM(A11))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A11))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB11="",AB11="_"),"",IF(LEFT(AB11,1)="_",IF(RIGHT(AB11,1)="_",MID(AB11,2,LEN(AB11)-2),RIGHT(AB11,LEN(AB11)-1)),IF(RIGHT(AB11,1)="_",LEFT(AB11,LEN(AB11)-1),AB11)))</f>
         <v/>
       </c>
       <c r="AD11" s="4">
-        <f>IF(AC11="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC11,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O11))="",LOWER(TRIM(O11))="nan",LOWER(TRIM(O11))="none",LOWER(TRIM(O11))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O11))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE11" s="4">
-        <f>IF(OR(AD11="",AD11="_"),"",IF(LEFT(AD11,1)="_",IF(RIGHT(AD11,1)="_",MID(AD11,2,LEN(AD11)-2),RIGHT(AD11,LEN(AD11)-1)),IF(RIGHT(AD11,1)="_",LEFT(AD11,LEN(AD11)-1),AD11)))</f>
+        <f>IF(AD11="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD11,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF11" s="4">
-        <f>IF(OR(LOWER(TRIM(O11))="",LOWER(TRIM(O11))="nan",LOWER(TRIM(O11))="none",LOWER(TRIM(O11))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O11))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE11="",AE11="_"),"",IF(LEFT(AE11,1)="_",IF(RIGHT(AE11,1)="_",MID(AE11,2,LEN(AE11)-2),RIGHT(AE11,LEN(AE11)-1)),IF(RIGHT(AE11,1)="_",LEFT(AE11,LEN(AE11)-1),AE11)))</f>
         <v/>
       </c>
       <c r="AG11" s="4">
-        <f>IF(AF11="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF11,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P11))="",LOWER(TRIM(P11))="nan",LOWER(TRIM(P11))="none",LOWER(TRIM(P11))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P11))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH11" s="4">
-        <f>IF(OR(AG11="",AG11="_"),"",IF(LEFT(AG11,1)="_",IF(RIGHT(AG11,1)="_",MID(AG11,2,LEN(AG11)-2),RIGHT(AG11,LEN(AG11)-1)),IF(RIGHT(AG11,1)="_",LEFT(AG11,LEN(AG11)-1),AG11)))</f>
+        <f>IF(AG11="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG11,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI11" s="4">
-        <f>IF(OR(LOWER(TRIM(P11))="",LOWER(TRIM(P11))="nan",LOWER(TRIM(P11))="none",LOWER(TRIM(P11))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P11))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ11" s="4">
-        <f>IF(AI11="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI11,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK11" s="4">
-        <f>IF(OR(AJ11="",AJ11="_"),"",IF(LEFT(AJ11,1)="_",IF(RIGHT(AJ11,1)="_",MID(AJ11,2,LEN(AJ11)-2),RIGHT(AJ11,LEN(AJ11)-1)),IF(RIGHT(AJ11,1)="_",LEFT(AJ11,LEN(AJ11)-1),AJ11)))</f>
-        <v/>
-      </c>
-      <c r="AL11" s="4">
-        <f>IF(OR(LOWER(TRIM(Q11))="",LOWER(TRIM(Q11))="nan",LOWER(TRIM(Q11))="none",LOWER(TRIM(Q11))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q11))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM11" s="4">
-        <f>IF(AL11="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL11,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN11" s="4">
-        <f>IF(OR(AM11="",AM11="_"),"",IF(LEFT(AM11,1)="_",IF(RIGHT(AM11,1)="_",MID(AM11,2,LEN(AM11)-2),RIGHT(AM11,LEN(AM11)-1)),IF(RIGHT(AM11,1)="_",LEFT(AM11,LEN(AM11)-1),AM11)))</f>
-        <v/>
-      </c>
-      <c r="AO11" s="4">
-        <f>IF(OR(LOWER(TRIM(R11))="",LOWER(TRIM(R11))="nan",LOWER(TRIM(R11))="none",LOWER(TRIM(R11))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R11))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP11" s="4">
-        <f>IF(AO11="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO11,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ11" s="4">
-        <f>IF(OR(AP11="",AP11="_"),"",IF(LEFT(AP11,1)="_",IF(RIGHT(AP11,1)="_",MID(AP11,2,LEN(AP11)-2),RIGHT(AP11,LEN(AP11)-1)),IF(RIGHT(AP11,1)="_",LEFT(AP11,LEN(AP11)-1),AP11)))</f>
+        <f>IF(OR(AH11="",AH11="_"),"",IF(LEFT(AH11,1)="_",IF(RIGHT(AH11,1)="_",MID(AH11,2,LEN(AH11)-2),RIGHT(AH11,LEN(AH11)-1)),IF(RIGHT(AH11,1)="_",LEFT(AH11,LEN(AH11)-1),AH11)))</f>
         <v/>
       </c>
     </row>
@@ -1859,7 +1648,7 @@
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="4">
-        <f>IF(AE12&lt;&gt;"",AE12,"")&amp;IF(AH12&lt;&gt;"",IF(AE12&lt;&gt;"","_"&amp;AH12,AH12),"")&amp;IF(AK12&lt;&gt;"",IF(AE12&lt;&gt;"","_"&amp;AK12,AK12),"")&amp;IF(AN12&lt;&gt;"",IF(AE12&lt;&gt;"","_"&amp;AN12,AN12),"")&amp;IF(AQ12&lt;&gt;"",IF(AE12&lt;&gt;"","_"&amp;AQ12,AQ12),"")</f>
+        <f>IF(AC12&lt;&gt;"",AC12,"")&amp;IF(AF12&lt;&gt;"",IF(AC12&lt;&gt;"","_"&amp;AF12,AF12),"")&amp;IF(AI12&lt;&gt;"",IF(AC12&lt;&gt;"","_"&amp;AI12,AI12),"")</f>
         <v/>
       </c>
       <c r="M12" s="4">
@@ -1880,68 +1669,42 @@
       <c r="V12" s="4" t="inlineStr"/>
       <c r="W12" s="4" t="inlineStr"/>
       <c r="X12" s="4" t="inlineStr"/>
-      <c r="Y12" s="4" t="inlineStr"/>
-      <c r="Z12" s="4" t="inlineStr"/>
-      <c r="AA12" s="4" t="n"/>
-      <c r="AB12" s="4" t="n"/>
+      <c r="Y12" s="4" t="n"/>
+      <c r="Z12" s="4" t="n"/>
+      <c r="AA12" s="4">
+        <f>IF(OR(LOWER(TRIM(A12))="",LOWER(TRIM(A12))="nan",LOWER(TRIM(A12))="none",LOWER(TRIM(A12))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A12))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB12" s="4">
+        <f>IF(AA12="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA12,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC12" s="4">
-        <f>IF(OR(LOWER(TRIM(A12))="",LOWER(TRIM(A12))="nan",LOWER(TRIM(A12))="none",LOWER(TRIM(A12))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A12))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB12="",AB12="_"),"",IF(LEFT(AB12,1)="_",IF(RIGHT(AB12,1)="_",MID(AB12,2,LEN(AB12)-2),RIGHT(AB12,LEN(AB12)-1)),IF(RIGHT(AB12,1)="_",LEFT(AB12,LEN(AB12)-1),AB12)))</f>
         <v/>
       </c>
       <c r="AD12" s="4">
-        <f>IF(AC12="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC12,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O12))="",LOWER(TRIM(O12))="nan",LOWER(TRIM(O12))="none",LOWER(TRIM(O12))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O12))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE12" s="4">
-        <f>IF(OR(AD12="",AD12="_"),"",IF(LEFT(AD12,1)="_",IF(RIGHT(AD12,1)="_",MID(AD12,2,LEN(AD12)-2),RIGHT(AD12,LEN(AD12)-1)),IF(RIGHT(AD12,1)="_",LEFT(AD12,LEN(AD12)-1),AD12)))</f>
+        <f>IF(AD12="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD12,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF12" s="4">
-        <f>IF(OR(LOWER(TRIM(O12))="",LOWER(TRIM(O12))="nan",LOWER(TRIM(O12))="none",LOWER(TRIM(O12))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O12))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE12="",AE12="_"),"",IF(LEFT(AE12,1)="_",IF(RIGHT(AE12,1)="_",MID(AE12,2,LEN(AE12)-2),RIGHT(AE12,LEN(AE12)-1)),IF(RIGHT(AE12,1)="_",LEFT(AE12,LEN(AE12)-1),AE12)))</f>
         <v/>
       </c>
       <c r="AG12" s="4">
-        <f>IF(AF12="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF12,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P12))="",LOWER(TRIM(P12))="nan",LOWER(TRIM(P12))="none",LOWER(TRIM(P12))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P12))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH12" s="4">
-        <f>IF(OR(AG12="",AG12="_"),"",IF(LEFT(AG12,1)="_",IF(RIGHT(AG12,1)="_",MID(AG12,2,LEN(AG12)-2),RIGHT(AG12,LEN(AG12)-1)),IF(RIGHT(AG12,1)="_",LEFT(AG12,LEN(AG12)-1),AG12)))</f>
+        <f>IF(AG12="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG12,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI12" s="4">
-        <f>IF(OR(LOWER(TRIM(P12))="",LOWER(TRIM(P12))="nan",LOWER(TRIM(P12))="none",LOWER(TRIM(P12))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P12))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ12" s="4">
-        <f>IF(AI12="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI12,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK12" s="4">
-        <f>IF(OR(AJ12="",AJ12="_"),"",IF(LEFT(AJ12,1)="_",IF(RIGHT(AJ12,1)="_",MID(AJ12,2,LEN(AJ12)-2),RIGHT(AJ12,LEN(AJ12)-1)),IF(RIGHT(AJ12,1)="_",LEFT(AJ12,LEN(AJ12)-1),AJ12)))</f>
-        <v/>
-      </c>
-      <c r="AL12" s="4">
-        <f>IF(OR(LOWER(TRIM(Q12))="",LOWER(TRIM(Q12))="nan",LOWER(TRIM(Q12))="none",LOWER(TRIM(Q12))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q12))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM12" s="4">
-        <f>IF(AL12="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL12,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN12" s="4">
-        <f>IF(OR(AM12="",AM12="_"),"",IF(LEFT(AM12,1)="_",IF(RIGHT(AM12,1)="_",MID(AM12,2,LEN(AM12)-2),RIGHT(AM12,LEN(AM12)-1)),IF(RIGHT(AM12,1)="_",LEFT(AM12,LEN(AM12)-1),AM12)))</f>
-        <v/>
-      </c>
-      <c r="AO12" s="4">
-        <f>IF(OR(LOWER(TRIM(R12))="",LOWER(TRIM(R12))="nan",LOWER(TRIM(R12))="none",LOWER(TRIM(R12))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R12))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP12" s="4">
-        <f>IF(AO12="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO12,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ12" s="4">
-        <f>IF(OR(AP12="",AP12="_"),"",IF(LEFT(AP12,1)="_",IF(RIGHT(AP12,1)="_",MID(AP12,2,LEN(AP12)-2),RIGHT(AP12,LEN(AP12)-1)),IF(RIGHT(AP12,1)="_",LEFT(AP12,LEN(AP12)-1),AP12)))</f>
+        <f>IF(OR(AH12="",AH12="_"),"",IF(LEFT(AH12,1)="_",IF(RIGHT(AH12,1)="_",MID(AH12,2,LEN(AH12)-2),RIGHT(AH12,LEN(AH12)-1)),IF(RIGHT(AH12,1)="_",LEFT(AH12,LEN(AH12)-1),AH12)))</f>
         <v/>
       </c>
     </row>
@@ -1958,7 +1721,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="4">
-        <f>IF(AE13&lt;&gt;"",AE13,"")&amp;IF(AH13&lt;&gt;"",IF(AE13&lt;&gt;"","_"&amp;AH13,AH13),"")&amp;IF(AK13&lt;&gt;"",IF(AE13&lt;&gt;"","_"&amp;AK13,AK13),"")&amp;IF(AN13&lt;&gt;"",IF(AE13&lt;&gt;"","_"&amp;AN13,AN13),"")&amp;IF(AQ13&lt;&gt;"",IF(AE13&lt;&gt;"","_"&amp;AQ13,AQ13),"")</f>
+        <f>IF(AC13&lt;&gt;"",AC13,"")&amp;IF(AF13&lt;&gt;"",IF(AC13&lt;&gt;"","_"&amp;AF13,AF13),"")&amp;IF(AI13&lt;&gt;"",IF(AC13&lt;&gt;"","_"&amp;AI13,AI13),"")</f>
         <v/>
       </c>
       <c r="M13" s="4">
@@ -1979,68 +1742,42 @@
       <c r="V13" s="4" t="inlineStr"/>
       <c r="W13" s="4" t="inlineStr"/>
       <c r="X13" s="4" t="inlineStr"/>
-      <c r="Y13" s="4" t="inlineStr"/>
-      <c r="Z13" s="4" t="inlineStr"/>
-      <c r="AA13" s="4" t="n"/>
-      <c r="AB13" s="4" t="n"/>
+      <c r="Y13" s="4" t="n"/>
+      <c r="Z13" s="4" t="n"/>
+      <c r="AA13" s="4">
+        <f>IF(OR(LOWER(TRIM(A13))="",LOWER(TRIM(A13))="nan",LOWER(TRIM(A13))="none",LOWER(TRIM(A13))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A13))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB13" s="4">
+        <f>IF(AA13="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA13,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC13" s="4">
-        <f>IF(OR(LOWER(TRIM(A13))="",LOWER(TRIM(A13))="nan",LOWER(TRIM(A13))="none",LOWER(TRIM(A13))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A13))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB13="",AB13="_"),"",IF(LEFT(AB13,1)="_",IF(RIGHT(AB13,1)="_",MID(AB13,2,LEN(AB13)-2),RIGHT(AB13,LEN(AB13)-1)),IF(RIGHT(AB13,1)="_",LEFT(AB13,LEN(AB13)-1),AB13)))</f>
         <v/>
       </c>
       <c r="AD13" s="4">
-        <f>IF(AC13="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC13,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O13))="",LOWER(TRIM(O13))="nan",LOWER(TRIM(O13))="none",LOWER(TRIM(O13))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O13))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE13" s="4">
-        <f>IF(OR(AD13="",AD13="_"),"",IF(LEFT(AD13,1)="_",IF(RIGHT(AD13,1)="_",MID(AD13,2,LEN(AD13)-2),RIGHT(AD13,LEN(AD13)-1)),IF(RIGHT(AD13,1)="_",LEFT(AD13,LEN(AD13)-1),AD13)))</f>
+        <f>IF(AD13="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD13,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF13" s="4">
-        <f>IF(OR(LOWER(TRIM(O13))="",LOWER(TRIM(O13))="nan",LOWER(TRIM(O13))="none",LOWER(TRIM(O13))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O13))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE13="",AE13="_"),"",IF(LEFT(AE13,1)="_",IF(RIGHT(AE13,1)="_",MID(AE13,2,LEN(AE13)-2),RIGHT(AE13,LEN(AE13)-1)),IF(RIGHT(AE13,1)="_",LEFT(AE13,LEN(AE13)-1),AE13)))</f>
         <v/>
       </c>
       <c r="AG13" s="4">
-        <f>IF(AF13="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF13,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P13))="",LOWER(TRIM(P13))="nan",LOWER(TRIM(P13))="none",LOWER(TRIM(P13))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P13))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH13" s="4">
-        <f>IF(OR(AG13="",AG13="_"),"",IF(LEFT(AG13,1)="_",IF(RIGHT(AG13,1)="_",MID(AG13,2,LEN(AG13)-2),RIGHT(AG13,LEN(AG13)-1)),IF(RIGHT(AG13,1)="_",LEFT(AG13,LEN(AG13)-1),AG13)))</f>
+        <f>IF(AG13="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG13,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI13" s="4">
-        <f>IF(OR(LOWER(TRIM(P13))="",LOWER(TRIM(P13))="nan",LOWER(TRIM(P13))="none",LOWER(TRIM(P13))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P13))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ13" s="4">
-        <f>IF(AI13="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI13,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK13" s="4">
-        <f>IF(OR(AJ13="",AJ13="_"),"",IF(LEFT(AJ13,1)="_",IF(RIGHT(AJ13,1)="_",MID(AJ13,2,LEN(AJ13)-2),RIGHT(AJ13,LEN(AJ13)-1)),IF(RIGHT(AJ13,1)="_",LEFT(AJ13,LEN(AJ13)-1),AJ13)))</f>
-        <v/>
-      </c>
-      <c r="AL13" s="4">
-        <f>IF(OR(LOWER(TRIM(Q13))="",LOWER(TRIM(Q13))="nan",LOWER(TRIM(Q13))="none",LOWER(TRIM(Q13))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q13))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM13" s="4">
-        <f>IF(AL13="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL13,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN13" s="4">
-        <f>IF(OR(AM13="",AM13="_"),"",IF(LEFT(AM13,1)="_",IF(RIGHT(AM13,1)="_",MID(AM13,2,LEN(AM13)-2),RIGHT(AM13,LEN(AM13)-1)),IF(RIGHT(AM13,1)="_",LEFT(AM13,LEN(AM13)-1),AM13)))</f>
-        <v/>
-      </c>
-      <c r="AO13" s="4">
-        <f>IF(OR(LOWER(TRIM(R13))="",LOWER(TRIM(R13))="nan",LOWER(TRIM(R13))="none",LOWER(TRIM(R13))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R13))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP13" s="4">
-        <f>IF(AO13="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO13,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ13" s="4">
-        <f>IF(OR(AP13="",AP13="_"),"",IF(LEFT(AP13,1)="_",IF(RIGHT(AP13,1)="_",MID(AP13,2,LEN(AP13)-2),RIGHT(AP13,LEN(AP13)-1)),IF(RIGHT(AP13,1)="_",LEFT(AP13,LEN(AP13)-1),AP13)))</f>
+        <f>IF(OR(AH13="",AH13="_"),"",IF(LEFT(AH13,1)="_",IF(RIGHT(AH13,1)="_",MID(AH13,2,LEN(AH13)-2),RIGHT(AH13,LEN(AH13)-1)),IF(RIGHT(AH13,1)="_",LEFT(AH13,LEN(AH13)-1),AH13)))</f>
         <v/>
       </c>
     </row>
@@ -2057,7 +1794,7 @@
       <c r="J14" s="4" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="4">
-        <f>IF(AE14&lt;&gt;"",AE14,"")&amp;IF(AH14&lt;&gt;"",IF(AE14&lt;&gt;"","_"&amp;AH14,AH14),"")&amp;IF(AK14&lt;&gt;"",IF(AE14&lt;&gt;"","_"&amp;AK14,AK14),"")&amp;IF(AN14&lt;&gt;"",IF(AE14&lt;&gt;"","_"&amp;AN14,AN14),"")&amp;IF(AQ14&lt;&gt;"",IF(AE14&lt;&gt;"","_"&amp;AQ14,AQ14),"")</f>
+        <f>IF(AC14&lt;&gt;"",AC14,"")&amp;IF(AF14&lt;&gt;"",IF(AC14&lt;&gt;"","_"&amp;AF14,AF14),"")&amp;IF(AI14&lt;&gt;"",IF(AC14&lt;&gt;"","_"&amp;AI14,AI14),"")</f>
         <v/>
       </c>
       <c r="M14" s="4">
@@ -2078,68 +1815,42 @@
       <c r="V14" s="4" t="inlineStr"/>
       <c r="W14" s="4" t="inlineStr"/>
       <c r="X14" s="4" t="inlineStr"/>
-      <c r="Y14" s="4" t="inlineStr"/>
-      <c r="Z14" s="4" t="inlineStr"/>
-      <c r="AA14" s="4" t="n"/>
-      <c r="AB14" s="4" t="n"/>
+      <c r="Y14" s="4" t="n"/>
+      <c r="Z14" s="4" t="n"/>
+      <c r="AA14" s="4">
+        <f>IF(OR(LOWER(TRIM(A14))="",LOWER(TRIM(A14))="nan",LOWER(TRIM(A14))="none",LOWER(TRIM(A14))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A14))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB14" s="4">
+        <f>IF(AA14="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA14,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC14" s="4">
-        <f>IF(OR(LOWER(TRIM(A14))="",LOWER(TRIM(A14))="nan",LOWER(TRIM(A14))="none",LOWER(TRIM(A14))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A14))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB14="",AB14="_"),"",IF(LEFT(AB14,1)="_",IF(RIGHT(AB14,1)="_",MID(AB14,2,LEN(AB14)-2),RIGHT(AB14,LEN(AB14)-1)),IF(RIGHT(AB14,1)="_",LEFT(AB14,LEN(AB14)-1),AB14)))</f>
         <v/>
       </c>
       <c r="AD14" s="4">
-        <f>IF(AC14="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC14,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O14))="",LOWER(TRIM(O14))="nan",LOWER(TRIM(O14))="none",LOWER(TRIM(O14))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O14))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE14" s="4">
-        <f>IF(OR(AD14="",AD14="_"),"",IF(LEFT(AD14,1)="_",IF(RIGHT(AD14,1)="_",MID(AD14,2,LEN(AD14)-2),RIGHT(AD14,LEN(AD14)-1)),IF(RIGHT(AD14,1)="_",LEFT(AD14,LEN(AD14)-1),AD14)))</f>
+        <f>IF(AD14="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD14,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF14" s="4">
-        <f>IF(OR(LOWER(TRIM(O14))="",LOWER(TRIM(O14))="nan",LOWER(TRIM(O14))="none",LOWER(TRIM(O14))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O14))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE14="",AE14="_"),"",IF(LEFT(AE14,1)="_",IF(RIGHT(AE14,1)="_",MID(AE14,2,LEN(AE14)-2),RIGHT(AE14,LEN(AE14)-1)),IF(RIGHT(AE14,1)="_",LEFT(AE14,LEN(AE14)-1),AE14)))</f>
         <v/>
       </c>
       <c r="AG14" s="4">
-        <f>IF(AF14="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF14,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P14))="",LOWER(TRIM(P14))="nan",LOWER(TRIM(P14))="none",LOWER(TRIM(P14))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P14))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH14" s="4">
-        <f>IF(OR(AG14="",AG14="_"),"",IF(LEFT(AG14,1)="_",IF(RIGHT(AG14,1)="_",MID(AG14,2,LEN(AG14)-2),RIGHT(AG14,LEN(AG14)-1)),IF(RIGHT(AG14,1)="_",LEFT(AG14,LEN(AG14)-1),AG14)))</f>
+        <f>IF(AG14="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG14,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI14" s="4">
-        <f>IF(OR(LOWER(TRIM(P14))="",LOWER(TRIM(P14))="nan",LOWER(TRIM(P14))="none",LOWER(TRIM(P14))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P14))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ14" s="4">
-        <f>IF(AI14="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI14,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK14" s="4">
-        <f>IF(OR(AJ14="",AJ14="_"),"",IF(LEFT(AJ14,1)="_",IF(RIGHT(AJ14,1)="_",MID(AJ14,2,LEN(AJ14)-2),RIGHT(AJ14,LEN(AJ14)-1)),IF(RIGHT(AJ14,1)="_",LEFT(AJ14,LEN(AJ14)-1),AJ14)))</f>
-        <v/>
-      </c>
-      <c r="AL14" s="4">
-        <f>IF(OR(LOWER(TRIM(Q14))="",LOWER(TRIM(Q14))="nan",LOWER(TRIM(Q14))="none",LOWER(TRIM(Q14))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q14))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM14" s="4">
-        <f>IF(AL14="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL14,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN14" s="4">
-        <f>IF(OR(AM14="",AM14="_"),"",IF(LEFT(AM14,1)="_",IF(RIGHT(AM14,1)="_",MID(AM14,2,LEN(AM14)-2),RIGHT(AM14,LEN(AM14)-1)),IF(RIGHT(AM14,1)="_",LEFT(AM14,LEN(AM14)-1),AM14)))</f>
-        <v/>
-      </c>
-      <c r="AO14" s="4">
-        <f>IF(OR(LOWER(TRIM(R14))="",LOWER(TRIM(R14))="nan",LOWER(TRIM(R14))="none",LOWER(TRIM(R14))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R14))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP14" s="4">
-        <f>IF(AO14="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO14,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ14" s="4">
-        <f>IF(OR(AP14="",AP14="_"),"",IF(LEFT(AP14,1)="_",IF(RIGHT(AP14,1)="_",MID(AP14,2,LEN(AP14)-2),RIGHT(AP14,LEN(AP14)-1)),IF(RIGHT(AP14,1)="_",LEFT(AP14,LEN(AP14)-1),AP14)))</f>
+        <f>IF(OR(AH14="",AH14="_"),"",IF(LEFT(AH14,1)="_",IF(RIGHT(AH14,1)="_",MID(AH14,2,LEN(AH14)-2),RIGHT(AH14,LEN(AH14)-1)),IF(RIGHT(AH14,1)="_",LEFT(AH14,LEN(AH14)-1),AH14)))</f>
         <v/>
       </c>
     </row>
@@ -2156,7 +1867,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="4">
-        <f>IF(AE15&lt;&gt;"",AE15,"")&amp;IF(AH15&lt;&gt;"",IF(AE15&lt;&gt;"","_"&amp;AH15,AH15),"")&amp;IF(AK15&lt;&gt;"",IF(AE15&lt;&gt;"","_"&amp;AK15,AK15),"")&amp;IF(AN15&lt;&gt;"",IF(AE15&lt;&gt;"","_"&amp;AN15,AN15),"")&amp;IF(AQ15&lt;&gt;"",IF(AE15&lt;&gt;"","_"&amp;AQ15,AQ15),"")</f>
+        <f>IF(AC15&lt;&gt;"",AC15,"")&amp;IF(AF15&lt;&gt;"",IF(AC15&lt;&gt;"","_"&amp;AF15,AF15),"")&amp;IF(AI15&lt;&gt;"",IF(AC15&lt;&gt;"","_"&amp;AI15,AI15),"")</f>
         <v/>
       </c>
       <c r="M15" s="4">
@@ -2177,68 +1888,42 @@
       <c r="V15" s="4" t="inlineStr"/>
       <c r="W15" s="4" t="inlineStr"/>
       <c r="X15" s="4" t="inlineStr"/>
-      <c r="Y15" s="4" t="inlineStr"/>
-      <c r="Z15" s="4" t="inlineStr"/>
-      <c r="AA15" s="4" t="n"/>
-      <c r="AB15" s="4" t="n"/>
+      <c r="Y15" s="4" t="n"/>
+      <c r="Z15" s="4" t="n"/>
+      <c r="AA15" s="4">
+        <f>IF(OR(LOWER(TRIM(A15))="",LOWER(TRIM(A15))="nan",LOWER(TRIM(A15))="none",LOWER(TRIM(A15))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A15))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB15" s="4">
+        <f>IF(AA15="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA15,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC15" s="4">
-        <f>IF(OR(LOWER(TRIM(A15))="",LOWER(TRIM(A15))="nan",LOWER(TRIM(A15))="none",LOWER(TRIM(A15))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A15))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB15="",AB15="_"),"",IF(LEFT(AB15,1)="_",IF(RIGHT(AB15,1)="_",MID(AB15,2,LEN(AB15)-2),RIGHT(AB15,LEN(AB15)-1)),IF(RIGHT(AB15,1)="_",LEFT(AB15,LEN(AB15)-1),AB15)))</f>
         <v/>
       </c>
       <c r="AD15" s="4">
-        <f>IF(AC15="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC15,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O15))="",LOWER(TRIM(O15))="nan",LOWER(TRIM(O15))="none",LOWER(TRIM(O15))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O15))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE15" s="4">
-        <f>IF(OR(AD15="",AD15="_"),"",IF(LEFT(AD15,1)="_",IF(RIGHT(AD15,1)="_",MID(AD15,2,LEN(AD15)-2),RIGHT(AD15,LEN(AD15)-1)),IF(RIGHT(AD15,1)="_",LEFT(AD15,LEN(AD15)-1),AD15)))</f>
+        <f>IF(AD15="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD15,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF15" s="4">
-        <f>IF(OR(LOWER(TRIM(O15))="",LOWER(TRIM(O15))="nan",LOWER(TRIM(O15))="none",LOWER(TRIM(O15))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O15))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE15="",AE15="_"),"",IF(LEFT(AE15,1)="_",IF(RIGHT(AE15,1)="_",MID(AE15,2,LEN(AE15)-2),RIGHT(AE15,LEN(AE15)-1)),IF(RIGHT(AE15,1)="_",LEFT(AE15,LEN(AE15)-1),AE15)))</f>
         <v/>
       </c>
       <c r="AG15" s="4">
-        <f>IF(AF15="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF15,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P15))="",LOWER(TRIM(P15))="nan",LOWER(TRIM(P15))="none",LOWER(TRIM(P15))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P15))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH15" s="4">
-        <f>IF(OR(AG15="",AG15="_"),"",IF(LEFT(AG15,1)="_",IF(RIGHT(AG15,1)="_",MID(AG15,2,LEN(AG15)-2),RIGHT(AG15,LEN(AG15)-1)),IF(RIGHT(AG15,1)="_",LEFT(AG15,LEN(AG15)-1),AG15)))</f>
+        <f>IF(AG15="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG15,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI15" s="4">
-        <f>IF(OR(LOWER(TRIM(P15))="",LOWER(TRIM(P15))="nan",LOWER(TRIM(P15))="none",LOWER(TRIM(P15))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P15))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ15" s="4">
-        <f>IF(AI15="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI15,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK15" s="4">
-        <f>IF(OR(AJ15="",AJ15="_"),"",IF(LEFT(AJ15,1)="_",IF(RIGHT(AJ15,1)="_",MID(AJ15,2,LEN(AJ15)-2),RIGHT(AJ15,LEN(AJ15)-1)),IF(RIGHT(AJ15,1)="_",LEFT(AJ15,LEN(AJ15)-1),AJ15)))</f>
-        <v/>
-      </c>
-      <c r="AL15" s="4">
-        <f>IF(OR(LOWER(TRIM(Q15))="",LOWER(TRIM(Q15))="nan",LOWER(TRIM(Q15))="none",LOWER(TRIM(Q15))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q15))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM15" s="4">
-        <f>IF(AL15="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL15,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN15" s="4">
-        <f>IF(OR(AM15="",AM15="_"),"",IF(LEFT(AM15,1)="_",IF(RIGHT(AM15,1)="_",MID(AM15,2,LEN(AM15)-2),RIGHT(AM15,LEN(AM15)-1)),IF(RIGHT(AM15,1)="_",LEFT(AM15,LEN(AM15)-1),AM15)))</f>
-        <v/>
-      </c>
-      <c r="AO15" s="4">
-        <f>IF(OR(LOWER(TRIM(R15))="",LOWER(TRIM(R15))="nan",LOWER(TRIM(R15))="none",LOWER(TRIM(R15))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R15))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP15" s="4">
-        <f>IF(AO15="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO15,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ15" s="4">
-        <f>IF(OR(AP15="",AP15="_"),"",IF(LEFT(AP15,1)="_",IF(RIGHT(AP15,1)="_",MID(AP15,2,LEN(AP15)-2),RIGHT(AP15,LEN(AP15)-1)),IF(RIGHT(AP15,1)="_",LEFT(AP15,LEN(AP15)-1),AP15)))</f>
+        <f>IF(OR(AH15="",AH15="_"),"",IF(LEFT(AH15,1)="_",IF(RIGHT(AH15,1)="_",MID(AH15,2,LEN(AH15)-2),RIGHT(AH15,LEN(AH15)-1)),IF(RIGHT(AH15,1)="_",LEFT(AH15,LEN(AH15)-1),AH15)))</f>
         <v/>
       </c>
     </row>
@@ -2255,7 +1940,7 @@
       <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="4">
-        <f>IF(AE16&lt;&gt;"",AE16,"")&amp;IF(AH16&lt;&gt;"",IF(AE16&lt;&gt;"","_"&amp;AH16,AH16),"")&amp;IF(AK16&lt;&gt;"",IF(AE16&lt;&gt;"","_"&amp;AK16,AK16),"")&amp;IF(AN16&lt;&gt;"",IF(AE16&lt;&gt;"","_"&amp;AN16,AN16),"")&amp;IF(AQ16&lt;&gt;"",IF(AE16&lt;&gt;"","_"&amp;AQ16,AQ16),"")</f>
+        <f>IF(AC16&lt;&gt;"",AC16,"")&amp;IF(AF16&lt;&gt;"",IF(AC16&lt;&gt;"","_"&amp;AF16,AF16),"")&amp;IF(AI16&lt;&gt;"",IF(AC16&lt;&gt;"","_"&amp;AI16,AI16),"")</f>
         <v/>
       </c>
       <c r="M16" s="4">
@@ -2276,68 +1961,42 @@
       <c r="V16" s="4" t="inlineStr"/>
       <c r="W16" s="4" t="inlineStr"/>
       <c r="X16" s="4" t="inlineStr"/>
-      <c r="Y16" s="4" t="inlineStr"/>
-      <c r="Z16" s="4" t="inlineStr"/>
-      <c r="AA16" s="4" t="n"/>
-      <c r="AB16" s="4" t="n"/>
+      <c r="Y16" s="4" t="n"/>
+      <c r="Z16" s="4" t="n"/>
+      <c r="AA16" s="4">
+        <f>IF(OR(LOWER(TRIM(A16))="",LOWER(TRIM(A16))="nan",LOWER(TRIM(A16))="none",LOWER(TRIM(A16))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A16))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB16" s="4">
+        <f>IF(AA16="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA16,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC16" s="4">
-        <f>IF(OR(LOWER(TRIM(A16))="",LOWER(TRIM(A16))="nan",LOWER(TRIM(A16))="none",LOWER(TRIM(A16))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A16))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB16="",AB16="_"),"",IF(LEFT(AB16,1)="_",IF(RIGHT(AB16,1)="_",MID(AB16,2,LEN(AB16)-2),RIGHT(AB16,LEN(AB16)-1)),IF(RIGHT(AB16,1)="_",LEFT(AB16,LEN(AB16)-1),AB16)))</f>
         <v/>
       </c>
       <c r="AD16" s="4">
-        <f>IF(AC16="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC16,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O16))="",LOWER(TRIM(O16))="nan",LOWER(TRIM(O16))="none",LOWER(TRIM(O16))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O16))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE16" s="4">
-        <f>IF(OR(AD16="",AD16="_"),"",IF(LEFT(AD16,1)="_",IF(RIGHT(AD16,1)="_",MID(AD16,2,LEN(AD16)-2),RIGHT(AD16,LEN(AD16)-1)),IF(RIGHT(AD16,1)="_",LEFT(AD16,LEN(AD16)-1),AD16)))</f>
+        <f>IF(AD16="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD16,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF16" s="4">
-        <f>IF(OR(LOWER(TRIM(O16))="",LOWER(TRIM(O16))="nan",LOWER(TRIM(O16))="none",LOWER(TRIM(O16))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O16))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE16="",AE16="_"),"",IF(LEFT(AE16,1)="_",IF(RIGHT(AE16,1)="_",MID(AE16,2,LEN(AE16)-2),RIGHT(AE16,LEN(AE16)-1)),IF(RIGHT(AE16,1)="_",LEFT(AE16,LEN(AE16)-1),AE16)))</f>
         <v/>
       </c>
       <c r="AG16" s="4">
-        <f>IF(AF16="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF16,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P16))="",LOWER(TRIM(P16))="nan",LOWER(TRIM(P16))="none",LOWER(TRIM(P16))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P16))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH16" s="4">
-        <f>IF(OR(AG16="",AG16="_"),"",IF(LEFT(AG16,1)="_",IF(RIGHT(AG16,1)="_",MID(AG16,2,LEN(AG16)-2),RIGHT(AG16,LEN(AG16)-1)),IF(RIGHT(AG16,1)="_",LEFT(AG16,LEN(AG16)-1),AG16)))</f>
+        <f>IF(AG16="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG16,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI16" s="4">
-        <f>IF(OR(LOWER(TRIM(P16))="",LOWER(TRIM(P16))="nan",LOWER(TRIM(P16))="none",LOWER(TRIM(P16))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P16))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ16" s="4">
-        <f>IF(AI16="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI16,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK16" s="4">
-        <f>IF(OR(AJ16="",AJ16="_"),"",IF(LEFT(AJ16,1)="_",IF(RIGHT(AJ16,1)="_",MID(AJ16,2,LEN(AJ16)-2),RIGHT(AJ16,LEN(AJ16)-1)),IF(RIGHT(AJ16,1)="_",LEFT(AJ16,LEN(AJ16)-1),AJ16)))</f>
-        <v/>
-      </c>
-      <c r="AL16" s="4">
-        <f>IF(OR(LOWER(TRIM(Q16))="",LOWER(TRIM(Q16))="nan",LOWER(TRIM(Q16))="none",LOWER(TRIM(Q16))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q16))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM16" s="4">
-        <f>IF(AL16="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL16,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN16" s="4">
-        <f>IF(OR(AM16="",AM16="_"),"",IF(LEFT(AM16,1)="_",IF(RIGHT(AM16,1)="_",MID(AM16,2,LEN(AM16)-2),RIGHT(AM16,LEN(AM16)-1)),IF(RIGHT(AM16,1)="_",LEFT(AM16,LEN(AM16)-1),AM16)))</f>
-        <v/>
-      </c>
-      <c r="AO16" s="4">
-        <f>IF(OR(LOWER(TRIM(R16))="",LOWER(TRIM(R16))="nan",LOWER(TRIM(R16))="none",LOWER(TRIM(R16))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R16))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP16" s="4">
-        <f>IF(AO16="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO16,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ16" s="4">
-        <f>IF(OR(AP16="",AP16="_"),"",IF(LEFT(AP16,1)="_",IF(RIGHT(AP16,1)="_",MID(AP16,2,LEN(AP16)-2),RIGHT(AP16,LEN(AP16)-1)),IF(RIGHT(AP16,1)="_",LEFT(AP16,LEN(AP16)-1),AP16)))</f>
+        <f>IF(OR(AH16="",AH16="_"),"",IF(LEFT(AH16,1)="_",IF(RIGHT(AH16,1)="_",MID(AH16,2,LEN(AH16)-2),RIGHT(AH16,LEN(AH16)-1)),IF(RIGHT(AH16,1)="_",LEFT(AH16,LEN(AH16)-1),AH16)))</f>
         <v/>
       </c>
     </row>
@@ -2354,7 +2013,7 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="4">
-        <f>IF(AE17&lt;&gt;"",AE17,"")&amp;IF(AH17&lt;&gt;"",IF(AE17&lt;&gt;"","_"&amp;AH17,AH17),"")&amp;IF(AK17&lt;&gt;"",IF(AE17&lt;&gt;"","_"&amp;AK17,AK17),"")&amp;IF(AN17&lt;&gt;"",IF(AE17&lt;&gt;"","_"&amp;AN17,AN17),"")&amp;IF(AQ17&lt;&gt;"",IF(AE17&lt;&gt;"","_"&amp;AQ17,AQ17),"")</f>
+        <f>IF(AC17&lt;&gt;"",AC17,"")&amp;IF(AF17&lt;&gt;"",IF(AC17&lt;&gt;"","_"&amp;AF17,AF17),"")&amp;IF(AI17&lt;&gt;"",IF(AC17&lt;&gt;"","_"&amp;AI17,AI17),"")</f>
         <v/>
       </c>
       <c r="M17" s="4">
@@ -2375,68 +2034,42 @@
       <c r="V17" s="4" t="inlineStr"/>
       <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
-      <c r="Y17" s="4" t="inlineStr"/>
-      <c r="Z17" s="4" t="inlineStr"/>
-      <c r="AA17" s="4" t="n"/>
-      <c r="AB17" s="4" t="n"/>
+      <c r="Y17" s="4" t="n"/>
+      <c r="Z17" s="4" t="n"/>
+      <c r="AA17" s="4">
+        <f>IF(OR(LOWER(TRIM(A17))="",LOWER(TRIM(A17))="nan",LOWER(TRIM(A17))="none",LOWER(TRIM(A17))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A17))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB17" s="4">
+        <f>IF(AA17="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA17,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC17" s="4">
-        <f>IF(OR(LOWER(TRIM(A17))="",LOWER(TRIM(A17))="nan",LOWER(TRIM(A17))="none",LOWER(TRIM(A17))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A17))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB17="",AB17="_"),"",IF(LEFT(AB17,1)="_",IF(RIGHT(AB17,1)="_",MID(AB17,2,LEN(AB17)-2),RIGHT(AB17,LEN(AB17)-1)),IF(RIGHT(AB17,1)="_",LEFT(AB17,LEN(AB17)-1),AB17)))</f>
         <v/>
       </c>
       <c r="AD17" s="4">
-        <f>IF(AC17="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC17,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O17))="",LOWER(TRIM(O17))="nan",LOWER(TRIM(O17))="none",LOWER(TRIM(O17))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O17))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE17" s="4">
-        <f>IF(OR(AD17="",AD17="_"),"",IF(LEFT(AD17,1)="_",IF(RIGHT(AD17,1)="_",MID(AD17,2,LEN(AD17)-2),RIGHT(AD17,LEN(AD17)-1)),IF(RIGHT(AD17,1)="_",LEFT(AD17,LEN(AD17)-1),AD17)))</f>
+        <f>IF(AD17="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD17,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF17" s="4">
-        <f>IF(OR(LOWER(TRIM(O17))="",LOWER(TRIM(O17))="nan",LOWER(TRIM(O17))="none",LOWER(TRIM(O17))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O17))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE17="",AE17="_"),"",IF(LEFT(AE17,1)="_",IF(RIGHT(AE17,1)="_",MID(AE17,2,LEN(AE17)-2),RIGHT(AE17,LEN(AE17)-1)),IF(RIGHT(AE17,1)="_",LEFT(AE17,LEN(AE17)-1),AE17)))</f>
         <v/>
       </c>
       <c r="AG17" s="4">
-        <f>IF(AF17="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF17,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P17))="",LOWER(TRIM(P17))="nan",LOWER(TRIM(P17))="none",LOWER(TRIM(P17))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P17))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH17" s="4">
-        <f>IF(OR(AG17="",AG17="_"),"",IF(LEFT(AG17,1)="_",IF(RIGHT(AG17,1)="_",MID(AG17,2,LEN(AG17)-2),RIGHT(AG17,LEN(AG17)-1)),IF(RIGHT(AG17,1)="_",LEFT(AG17,LEN(AG17)-1),AG17)))</f>
+        <f>IF(AG17="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG17,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI17" s="4">
-        <f>IF(OR(LOWER(TRIM(P17))="",LOWER(TRIM(P17))="nan",LOWER(TRIM(P17))="none",LOWER(TRIM(P17))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P17))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ17" s="4">
-        <f>IF(AI17="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI17,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK17" s="4">
-        <f>IF(OR(AJ17="",AJ17="_"),"",IF(LEFT(AJ17,1)="_",IF(RIGHT(AJ17,1)="_",MID(AJ17,2,LEN(AJ17)-2),RIGHT(AJ17,LEN(AJ17)-1)),IF(RIGHT(AJ17,1)="_",LEFT(AJ17,LEN(AJ17)-1),AJ17)))</f>
-        <v/>
-      </c>
-      <c r="AL17" s="4">
-        <f>IF(OR(LOWER(TRIM(Q17))="",LOWER(TRIM(Q17))="nan",LOWER(TRIM(Q17))="none",LOWER(TRIM(Q17))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q17))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM17" s="4">
-        <f>IF(AL17="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL17,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN17" s="4">
-        <f>IF(OR(AM17="",AM17="_"),"",IF(LEFT(AM17,1)="_",IF(RIGHT(AM17,1)="_",MID(AM17,2,LEN(AM17)-2),RIGHT(AM17,LEN(AM17)-1)),IF(RIGHT(AM17,1)="_",LEFT(AM17,LEN(AM17)-1),AM17)))</f>
-        <v/>
-      </c>
-      <c r="AO17" s="4">
-        <f>IF(OR(LOWER(TRIM(R17))="",LOWER(TRIM(R17))="nan",LOWER(TRIM(R17))="none",LOWER(TRIM(R17))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R17))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP17" s="4">
-        <f>IF(AO17="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO17,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ17" s="4">
-        <f>IF(OR(AP17="",AP17="_"),"",IF(LEFT(AP17,1)="_",IF(RIGHT(AP17,1)="_",MID(AP17,2,LEN(AP17)-2),RIGHT(AP17,LEN(AP17)-1)),IF(RIGHT(AP17,1)="_",LEFT(AP17,LEN(AP17)-1),AP17)))</f>
+        <f>IF(OR(AH17="",AH17="_"),"",IF(LEFT(AH17,1)="_",IF(RIGHT(AH17,1)="_",MID(AH17,2,LEN(AH17)-2),RIGHT(AH17,LEN(AH17)-1)),IF(RIGHT(AH17,1)="_",LEFT(AH17,LEN(AH17)-1),AH17)))</f>
         <v/>
       </c>
     </row>
@@ -2453,7 +2086,7 @@
       <c r="J18" s="4" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="4">
-        <f>IF(AE18&lt;&gt;"",AE18,"")&amp;IF(AH18&lt;&gt;"",IF(AE18&lt;&gt;"","_"&amp;AH18,AH18),"")&amp;IF(AK18&lt;&gt;"",IF(AE18&lt;&gt;"","_"&amp;AK18,AK18),"")&amp;IF(AN18&lt;&gt;"",IF(AE18&lt;&gt;"","_"&amp;AN18,AN18),"")&amp;IF(AQ18&lt;&gt;"",IF(AE18&lt;&gt;"","_"&amp;AQ18,AQ18),"")</f>
+        <f>IF(AC18&lt;&gt;"",AC18,"")&amp;IF(AF18&lt;&gt;"",IF(AC18&lt;&gt;"","_"&amp;AF18,AF18),"")&amp;IF(AI18&lt;&gt;"",IF(AC18&lt;&gt;"","_"&amp;AI18,AI18),"")</f>
         <v/>
       </c>
       <c r="M18" s="4">
@@ -2474,68 +2107,42 @@
       <c r="V18" s="4" t="inlineStr"/>
       <c r="W18" s="4" t="inlineStr"/>
       <c r="X18" s="4" t="inlineStr"/>
-      <c r="Y18" s="4" t="inlineStr"/>
-      <c r="Z18" s="4" t="inlineStr"/>
-      <c r="AA18" s="4" t="n"/>
-      <c r="AB18" s="4" t="n"/>
+      <c r="Y18" s="4" t="n"/>
+      <c r="Z18" s="4" t="n"/>
+      <c r="AA18" s="4">
+        <f>IF(OR(LOWER(TRIM(A18))="",LOWER(TRIM(A18))="nan",LOWER(TRIM(A18))="none",LOWER(TRIM(A18))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A18))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB18" s="4">
+        <f>IF(AA18="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA18,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC18" s="4">
-        <f>IF(OR(LOWER(TRIM(A18))="",LOWER(TRIM(A18))="nan",LOWER(TRIM(A18))="none",LOWER(TRIM(A18))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A18))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB18="",AB18="_"),"",IF(LEFT(AB18,1)="_",IF(RIGHT(AB18,1)="_",MID(AB18,2,LEN(AB18)-2),RIGHT(AB18,LEN(AB18)-1)),IF(RIGHT(AB18,1)="_",LEFT(AB18,LEN(AB18)-1),AB18)))</f>
         <v/>
       </c>
       <c r="AD18" s="4">
-        <f>IF(AC18="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC18,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O18))="",LOWER(TRIM(O18))="nan",LOWER(TRIM(O18))="none",LOWER(TRIM(O18))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O18))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE18" s="4">
-        <f>IF(OR(AD18="",AD18="_"),"",IF(LEFT(AD18,1)="_",IF(RIGHT(AD18,1)="_",MID(AD18,2,LEN(AD18)-2),RIGHT(AD18,LEN(AD18)-1)),IF(RIGHT(AD18,1)="_",LEFT(AD18,LEN(AD18)-1),AD18)))</f>
+        <f>IF(AD18="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD18,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF18" s="4">
-        <f>IF(OR(LOWER(TRIM(O18))="",LOWER(TRIM(O18))="nan",LOWER(TRIM(O18))="none",LOWER(TRIM(O18))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O18))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE18="",AE18="_"),"",IF(LEFT(AE18,1)="_",IF(RIGHT(AE18,1)="_",MID(AE18,2,LEN(AE18)-2),RIGHT(AE18,LEN(AE18)-1)),IF(RIGHT(AE18,1)="_",LEFT(AE18,LEN(AE18)-1),AE18)))</f>
         <v/>
       </c>
       <c r="AG18" s="4">
-        <f>IF(AF18="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF18,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P18))="",LOWER(TRIM(P18))="nan",LOWER(TRIM(P18))="none",LOWER(TRIM(P18))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P18))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH18" s="4">
-        <f>IF(OR(AG18="",AG18="_"),"",IF(LEFT(AG18,1)="_",IF(RIGHT(AG18,1)="_",MID(AG18,2,LEN(AG18)-2),RIGHT(AG18,LEN(AG18)-1)),IF(RIGHT(AG18,1)="_",LEFT(AG18,LEN(AG18)-1),AG18)))</f>
+        <f>IF(AG18="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG18,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI18" s="4">
-        <f>IF(OR(LOWER(TRIM(P18))="",LOWER(TRIM(P18))="nan",LOWER(TRIM(P18))="none",LOWER(TRIM(P18))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P18))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ18" s="4">
-        <f>IF(AI18="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI18,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK18" s="4">
-        <f>IF(OR(AJ18="",AJ18="_"),"",IF(LEFT(AJ18,1)="_",IF(RIGHT(AJ18,1)="_",MID(AJ18,2,LEN(AJ18)-2),RIGHT(AJ18,LEN(AJ18)-1)),IF(RIGHT(AJ18,1)="_",LEFT(AJ18,LEN(AJ18)-1),AJ18)))</f>
-        <v/>
-      </c>
-      <c r="AL18" s="4">
-        <f>IF(OR(LOWER(TRIM(Q18))="",LOWER(TRIM(Q18))="nan",LOWER(TRIM(Q18))="none",LOWER(TRIM(Q18))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q18))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM18" s="4">
-        <f>IF(AL18="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL18,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN18" s="4">
-        <f>IF(OR(AM18="",AM18="_"),"",IF(LEFT(AM18,1)="_",IF(RIGHT(AM18,1)="_",MID(AM18,2,LEN(AM18)-2),RIGHT(AM18,LEN(AM18)-1)),IF(RIGHT(AM18,1)="_",LEFT(AM18,LEN(AM18)-1),AM18)))</f>
-        <v/>
-      </c>
-      <c r="AO18" s="4">
-        <f>IF(OR(LOWER(TRIM(R18))="",LOWER(TRIM(R18))="nan",LOWER(TRIM(R18))="none",LOWER(TRIM(R18))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R18))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP18" s="4">
-        <f>IF(AO18="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO18,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ18" s="4">
-        <f>IF(OR(AP18="",AP18="_"),"",IF(LEFT(AP18,1)="_",IF(RIGHT(AP18,1)="_",MID(AP18,2,LEN(AP18)-2),RIGHT(AP18,LEN(AP18)-1)),IF(RIGHT(AP18,1)="_",LEFT(AP18,LEN(AP18)-1),AP18)))</f>
+        <f>IF(OR(AH18="",AH18="_"),"",IF(LEFT(AH18,1)="_",IF(RIGHT(AH18,1)="_",MID(AH18,2,LEN(AH18)-2),RIGHT(AH18,LEN(AH18)-1)),IF(RIGHT(AH18,1)="_",LEFT(AH18,LEN(AH18)-1),AH18)))</f>
         <v/>
       </c>
     </row>
@@ -2552,7 +2159,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="4">
-        <f>IF(AE19&lt;&gt;"",AE19,"")&amp;IF(AH19&lt;&gt;"",IF(AE19&lt;&gt;"","_"&amp;AH19,AH19),"")&amp;IF(AK19&lt;&gt;"",IF(AE19&lt;&gt;"","_"&amp;AK19,AK19),"")&amp;IF(AN19&lt;&gt;"",IF(AE19&lt;&gt;"","_"&amp;AN19,AN19),"")&amp;IF(AQ19&lt;&gt;"",IF(AE19&lt;&gt;"","_"&amp;AQ19,AQ19),"")</f>
+        <f>IF(AC19&lt;&gt;"",AC19,"")&amp;IF(AF19&lt;&gt;"",IF(AC19&lt;&gt;"","_"&amp;AF19,AF19),"")&amp;IF(AI19&lt;&gt;"",IF(AC19&lt;&gt;"","_"&amp;AI19,AI19),"")</f>
         <v/>
       </c>
       <c r="M19" s="4">
@@ -2573,68 +2180,42 @@
       <c r="V19" s="4" t="inlineStr"/>
       <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="inlineStr"/>
-      <c r="Y19" s="4" t="inlineStr"/>
-      <c r="Z19" s="4" t="inlineStr"/>
-      <c r="AA19" s="4" t="n"/>
-      <c r="AB19" s="4" t="n"/>
+      <c r="Y19" s="4" t="n"/>
+      <c r="Z19" s="4" t="n"/>
+      <c r="AA19" s="4">
+        <f>IF(OR(LOWER(TRIM(A19))="",LOWER(TRIM(A19))="nan",LOWER(TRIM(A19))="none",LOWER(TRIM(A19))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A19))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB19" s="4">
+        <f>IF(AA19="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA19,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC19" s="4">
-        <f>IF(OR(LOWER(TRIM(A19))="",LOWER(TRIM(A19))="nan",LOWER(TRIM(A19))="none",LOWER(TRIM(A19))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A19))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB19="",AB19="_"),"",IF(LEFT(AB19,1)="_",IF(RIGHT(AB19,1)="_",MID(AB19,2,LEN(AB19)-2),RIGHT(AB19,LEN(AB19)-1)),IF(RIGHT(AB19,1)="_",LEFT(AB19,LEN(AB19)-1),AB19)))</f>
         <v/>
       </c>
       <c r="AD19" s="4">
-        <f>IF(AC19="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC19,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O19))="",LOWER(TRIM(O19))="nan",LOWER(TRIM(O19))="none",LOWER(TRIM(O19))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O19))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE19" s="4">
-        <f>IF(OR(AD19="",AD19="_"),"",IF(LEFT(AD19,1)="_",IF(RIGHT(AD19,1)="_",MID(AD19,2,LEN(AD19)-2),RIGHT(AD19,LEN(AD19)-1)),IF(RIGHT(AD19,1)="_",LEFT(AD19,LEN(AD19)-1),AD19)))</f>
+        <f>IF(AD19="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD19,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF19" s="4">
-        <f>IF(OR(LOWER(TRIM(O19))="",LOWER(TRIM(O19))="nan",LOWER(TRIM(O19))="none",LOWER(TRIM(O19))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O19))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE19="",AE19="_"),"",IF(LEFT(AE19,1)="_",IF(RIGHT(AE19,1)="_",MID(AE19,2,LEN(AE19)-2),RIGHT(AE19,LEN(AE19)-1)),IF(RIGHT(AE19,1)="_",LEFT(AE19,LEN(AE19)-1),AE19)))</f>
         <v/>
       </c>
       <c r="AG19" s="4">
-        <f>IF(AF19="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF19,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P19))="",LOWER(TRIM(P19))="nan",LOWER(TRIM(P19))="none",LOWER(TRIM(P19))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P19))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH19" s="4">
-        <f>IF(OR(AG19="",AG19="_"),"",IF(LEFT(AG19,1)="_",IF(RIGHT(AG19,1)="_",MID(AG19,2,LEN(AG19)-2),RIGHT(AG19,LEN(AG19)-1)),IF(RIGHT(AG19,1)="_",LEFT(AG19,LEN(AG19)-1),AG19)))</f>
+        <f>IF(AG19="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG19,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI19" s="4">
-        <f>IF(OR(LOWER(TRIM(P19))="",LOWER(TRIM(P19))="nan",LOWER(TRIM(P19))="none",LOWER(TRIM(P19))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P19))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ19" s="4">
-        <f>IF(AI19="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI19,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK19" s="4">
-        <f>IF(OR(AJ19="",AJ19="_"),"",IF(LEFT(AJ19,1)="_",IF(RIGHT(AJ19,1)="_",MID(AJ19,2,LEN(AJ19)-2),RIGHT(AJ19,LEN(AJ19)-1)),IF(RIGHT(AJ19,1)="_",LEFT(AJ19,LEN(AJ19)-1),AJ19)))</f>
-        <v/>
-      </c>
-      <c r="AL19" s="4">
-        <f>IF(OR(LOWER(TRIM(Q19))="",LOWER(TRIM(Q19))="nan",LOWER(TRIM(Q19))="none",LOWER(TRIM(Q19))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q19))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM19" s="4">
-        <f>IF(AL19="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL19,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN19" s="4">
-        <f>IF(OR(AM19="",AM19="_"),"",IF(LEFT(AM19,1)="_",IF(RIGHT(AM19,1)="_",MID(AM19,2,LEN(AM19)-2),RIGHT(AM19,LEN(AM19)-1)),IF(RIGHT(AM19,1)="_",LEFT(AM19,LEN(AM19)-1),AM19)))</f>
-        <v/>
-      </c>
-      <c r="AO19" s="4">
-        <f>IF(OR(LOWER(TRIM(R19))="",LOWER(TRIM(R19))="nan",LOWER(TRIM(R19))="none",LOWER(TRIM(R19))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R19))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP19" s="4">
-        <f>IF(AO19="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO19,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ19" s="4">
-        <f>IF(OR(AP19="",AP19="_"),"",IF(LEFT(AP19,1)="_",IF(RIGHT(AP19,1)="_",MID(AP19,2,LEN(AP19)-2),RIGHT(AP19,LEN(AP19)-1)),IF(RIGHT(AP19,1)="_",LEFT(AP19,LEN(AP19)-1),AP19)))</f>
+        <f>IF(OR(AH19="",AH19="_"),"",IF(LEFT(AH19,1)="_",IF(RIGHT(AH19,1)="_",MID(AH19,2,LEN(AH19)-2),RIGHT(AH19,LEN(AH19)-1)),IF(RIGHT(AH19,1)="_",LEFT(AH19,LEN(AH19)-1),AH19)))</f>
         <v/>
       </c>
     </row>
@@ -2651,7 +2232,7 @@
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="4">
-        <f>IF(AE20&lt;&gt;"",AE20,"")&amp;IF(AH20&lt;&gt;"",IF(AE20&lt;&gt;"","_"&amp;AH20,AH20),"")&amp;IF(AK20&lt;&gt;"",IF(AE20&lt;&gt;"","_"&amp;AK20,AK20),"")&amp;IF(AN20&lt;&gt;"",IF(AE20&lt;&gt;"","_"&amp;AN20,AN20),"")&amp;IF(AQ20&lt;&gt;"",IF(AE20&lt;&gt;"","_"&amp;AQ20,AQ20),"")</f>
+        <f>IF(AC20&lt;&gt;"",AC20,"")&amp;IF(AF20&lt;&gt;"",IF(AC20&lt;&gt;"","_"&amp;AF20,AF20),"")&amp;IF(AI20&lt;&gt;"",IF(AC20&lt;&gt;"","_"&amp;AI20,AI20),"")</f>
         <v/>
       </c>
       <c r="M20" s="4">
@@ -2672,68 +2253,42 @@
       <c r="V20" s="4" t="inlineStr"/>
       <c r="W20" s="4" t="inlineStr"/>
       <c r="X20" s="4" t="inlineStr"/>
-      <c r="Y20" s="4" t="inlineStr"/>
-      <c r="Z20" s="4" t="inlineStr"/>
-      <c r="AA20" s="4" t="n"/>
-      <c r="AB20" s="4" t="n"/>
+      <c r="Y20" s="4" t="n"/>
+      <c r="Z20" s="4" t="n"/>
+      <c r="AA20" s="4">
+        <f>IF(OR(LOWER(TRIM(A20))="",LOWER(TRIM(A20))="nan",LOWER(TRIM(A20))="none",LOWER(TRIM(A20))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A20))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB20" s="4">
+        <f>IF(AA20="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA20,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC20" s="4">
-        <f>IF(OR(LOWER(TRIM(A20))="",LOWER(TRIM(A20))="nan",LOWER(TRIM(A20))="none",LOWER(TRIM(A20))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A20))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB20="",AB20="_"),"",IF(LEFT(AB20,1)="_",IF(RIGHT(AB20,1)="_",MID(AB20,2,LEN(AB20)-2),RIGHT(AB20,LEN(AB20)-1)),IF(RIGHT(AB20,1)="_",LEFT(AB20,LEN(AB20)-1),AB20)))</f>
         <v/>
       </c>
       <c r="AD20" s="4">
-        <f>IF(AC20="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC20,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O20))="",LOWER(TRIM(O20))="nan",LOWER(TRIM(O20))="none",LOWER(TRIM(O20))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O20))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE20" s="4">
-        <f>IF(OR(AD20="",AD20="_"),"",IF(LEFT(AD20,1)="_",IF(RIGHT(AD20,1)="_",MID(AD20,2,LEN(AD20)-2),RIGHT(AD20,LEN(AD20)-1)),IF(RIGHT(AD20,1)="_",LEFT(AD20,LEN(AD20)-1),AD20)))</f>
+        <f>IF(AD20="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD20,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF20" s="4">
-        <f>IF(OR(LOWER(TRIM(O20))="",LOWER(TRIM(O20))="nan",LOWER(TRIM(O20))="none",LOWER(TRIM(O20))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O20))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE20="",AE20="_"),"",IF(LEFT(AE20,1)="_",IF(RIGHT(AE20,1)="_",MID(AE20,2,LEN(AE20)-2),RIGHT(AE20,LEN(AE20)-1)),IF(RIGHT(AE20,1)="_",LEFT(AE20,LEN(AE20)-1),AE20)))</f>
         <v/>
       </c>
       <c r="AG20" s="4">
-        <f>IF(AF20="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF20,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P20))="",LOWER(TRIM(P20))="nan",LOWER(TRIM(P20))="none",LOWER(TRIM(P20))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P20))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH20" s="4">
-        <f>IF(OR(AG20="",AG20="_"),"",IF(LEFT(AG20,1)="_",IF(RIGHT(AG20,1)="_",MID(AG20,2,LEN(AG20)-2),RIGHT(AG20,LEN(AG20)-1)),IF(RIGHT(AG20,1)="_",LEFT(AG20,LEN(AG20)-1),AG20)))</f>
+        <f>IF(AG20="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG20,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI20" s="4">
-        <f>IF(OR(LOWER(TRIM(P20))="",LOWER(TRIM(P20))="nan",LOWER(TRIM(P20))="none",LOWER(TRIM(P20))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P20))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ20" s="4">
-        <f>IF(AI20="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI20,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK20" s="4">
-        <f>IF(OR(AJ20="",AJ20="_"),"",IF(LEFT(AJ20,1)="_",IF(RIGHT(AJ20,1)="_",MID(AJ20,2,LEN(AJ20)-2),RIGHT(AJ20,LEN(AJ20)-1)),IF(RIGHT(AJ20,1)="_",LEFT(AJ20,LEN(AJ20)-1),AJ20)))</f>
-        <v/>
-      </c>
-      <c r="AL20" s="4">
-        <f>IF(OR(LOWER(TRIM(Q20))="",LOWER(TRIM(Q20))="nan",LOWER(TRIM(Q20))="none",LOWER(TRIM(Q20))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q20))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM20" s="4">
-        <f>IF(AL20="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL20,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN20" s="4">
-        <f>IF(OR(AM20="",AM20="_"),"",IF(LEFT(AM20,1)="_",IF(RIGHT(AM20,1)="_",MID(AM20,2,LEN(AM20)-2),RIGHT(AM20,LEN(AM20)-1)),IF(RIGHT(AM20,1)="_",LEFT(AM20,LEN(AM20)-1),AM20)))</f>
-        <v/>
-      </c>
-      <c r="AO20" s="4">
-        <f>IF(OR(LOWER(TRIM(R20))="",LOWER(TRIM(R20))="nan",LOWER(TRIM(R20))="none",LOWER(TRIM(R20))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R20))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP20" s="4">
-        <f>IF(AO20="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO20,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ20" s="4">
-        <f>IF(OR(AP20="",AP20="_"),"",IF(LEFT(AP20,1)="_",IF(RIGHT(AP20,1)="_",MID(AP20,2,LEN(AP20)-2),RIGHT(AP20,LEN(AP20)-1)),IF(RIGHT(AP20,1)="_",LEFT(AP20,LEN(AP20)-1),AP20)))</f>
+        <f>IF(OR(AH20="",AH20="_"),"",IF(LEFT(AH20,1)="_",IF(RIGHT(AH20,1)="_",MID(AH20,2,LEN(AH20)-2),RIGHT(AH20,LEN(AH20)-1)),IF(RIGHT(AH20,1)="_",LEFT(AH20,LEN(AH20)-1),AH20)))</f>
         <v/>
       </c>
     </row>
@@ -2750,7 +2305,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="4">
-        <f>IF(AE21&lt;&gt;"",AE21,"")&amp;IF(AH21&lt;&gt;"",IF(AE21&lt;&gt;"","_"&amp;AH21,AH21),"")&amp;IF(AK21&lt;&gt;"",IF(AE21&lt;&gt;"","_"&amp;AK21,AK21),"")&amp;IF(AN21&lt;&gt;"",IF(AE21&lt;&gt;"","_"&amp;AN21,AN21),"")&amp;IF(AQ21&lt;&gt;"",IF(AE21&lt;&gt;"","_"&amp;AQ21,AQ21),"")</f>
+        <f>IF(AC21&lt;&gt;"",AC21,"")&amp;IF(AF21&lt;&gt;"",IF(AC21&lt;&gt;"","_"&amp;AF21,AF21),"")&amp;IF(AI21&lt;&gt;"",IF(AC21&lt;&gt;"","_"&amp;AI21,AI21),"")</f>
         <v/>
       </c>
       <c r="M21" s="4">
@@ -2771,68 +2326,42 @@
       <c r="V21" s="4" t="inlineStr"/>
       <c r="W21" s="4" t="inlineStr"/>
       <c r="X21" s="4" t="inlineStr"/>
-      <c r="Y21" s="4" t="inlineStr"/>
-      <c r="Z21" s="4" t="inlineStr"/>
-      <c r="AA21" s="4" t="n"/>
-      <c r="AB21" s="4" t="n"/>
+      <c r="Y21" s="4" t="n"/>
+      <c r="Z21" s="4" t="n"/>
+      <c r="AA21" s="4">
+        <f>IF(OR(LOWER(TRIM(A21))="",LOWER(TRIM(A21))="nan",LOWER(TRIM(A21))="none",LOWER(TRIM(A21))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A21))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB21" s="4">
+        <f>IF(AA21="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA21,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC21" s="4">
-        <f>IF(OR(LOWER(TRIM(A21))="",LOWER(TRIM(A21))="nan",LOWER(TRIM(A21))="none",LOWER(TRIM(A21))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A21))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB21="",AB21="_"),"",IF(LEFT(AB21,1)="_",IF(RIGHT(AB21,1)="_",MID(AB21,2,LEN(AB21)-2),RIGHT(AB21,LEN(AB21)-1)),IF(RIGHT(AB21,1)="_",LEFT(AB21,LEN(AB21)-1),AB21)))</f>
         <v/>
       </c>
       <c r="AD21" s="4">
-        <f>IF(AC21="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC21,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O21))="",LOWER(TRIM(O21))="nan",LOWER(TRIM(O21))="none",LOWER(TRIM(O21))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O21))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE21" s="4">
-        <f>IF(OR(AD21="",AD21="_"),"",IF(LEFT(AD21,1)="_",IF(RIGHT(AD21,1)="_",MID(AD21,2,LEN(AD21)-2),RIGHT(AD21,LEN(AD21)-1)),IF(RIGHT(AD21,1)="_",LEFT(AD21,LEN(AD21)-1),AD21)))</f>
+        <f>IF(AD21="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD21,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF21" s="4">
-        <f>IF(OR(LOWER(TRIM(O21))="",LOWER(TRIM(O21))="nan",LOWER(TRIM(O21))="none",LOWER(TRIM(O21))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O21))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE21="",AE21="_"),"",IF(LEFT(AE21,1)="_",IF(RIGHT(AE21,1)="_",MID(AE21,2,LEN(AE21)-2),RIGHT(AE21,LEN(AE21)-1)),IF(RIGHT(AE21,1)="_",LEFT(AE21,LEN(AE21)-1),AE21)))</f>
         <v/>
       </c>
       <c r="AG21" s="4">
-        <f>IF(AF21="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF21,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P21))="",LOWER(TRIM(P21))="nan",LOWER(TRIM(P21))="none",LOWER(TRIM(P21))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P21))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH21" s="4">
-        <f>IF(OR(AG21="",AG21="_"),"",IF(LEFT(AG21,1)="_",IF(RIGHT(AG21,1)="_",MID(AG21,2,LEN(AG21)-2),RIGHT(AG21,LEN(AG21)-1)),IF(RIGHT(AG21,1)="_",LEFT(AG21,LEN(AG21)-1),AG21)))</f>
+        <f>IF(AG21="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG21,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI21" s="4">
-        <f>IF(OR(LOWER(TRIM(P21))="",LOWER(TRIM(P21))="nan",LOWER(TRIM(P21))="none",LOWER(TRIM(P21))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P21))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ21" s="4">
-        <f>IF(AI21="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI21,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK21" s="4">
-        <f>IF(OR(AJ21="",AJ21="_"),"",IF(LEFT(AJ21,1)="_",IF(RIGHT(AJ21,1)="_",MID(AJ21,2,LEN(AJ21)-2),RIGHT(AJ21,LEN(AJ21)-1)),IF(RIGHT(AJ21,1)="_",LEFT(AJ21,LEN(AJ21)-1),AJ21)))</f>
-        <v/>
-      </c>
-      <c r="AL21" s="4">
-        <f>IF(OR(LOWER(TRIM(Q21))="",LOWER(TRIM(Q21))="nan",LOWER(TRIM(Q21))="none",LOWER(TRIM(Q21))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q21))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM21" s="4">
-        <f>IF(AL21="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL21,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN21" s="4">
-        <f>IF(OR(AM21="",AM21="_"),"",IF(LEFT(AM21,1)="_",IF(RIGHT(AM21,1)="_",MID(AM21,2,LEN(AM21)-2),RIGHT(AM21,LEN(AM21)-1)),IF(RIGHT(AM21,1)="_",LEFT(AM21,LEN(AM21)-1),AM21)))</f>
-        <v/>
-      </c>
-      <c r="AO21" s="4">
-        <f>IF(OR(LOWER(TRIM(R21))="",LOWER(TRIM(R21))="nan",LOWER(TRIM(R21))="none",LOWER(TRIM(R21))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R21))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP21" s="4">
-        <f>IF(AO21="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO21,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ21" s="4">
-        <f>IF(OR(AP21="",AP21="_"),"",IF(LEFT(AP21,1)="_",IF(RIGHT(AP21,1)="_",MID(AP21,2,LEN(AP21)-2),RIGHT(AP21,LEN(AP21)-1)),IF(RIGHT(AP21,1)="_",LEFT(AP21,LEN(AP21)-1),AP21)))</f>
+        <f>IF(OR(AH21="",AH21="_"),"",IF(LEFT(AH21,1)="_",IF(RIGHT(AH21,1)="_",MID(AH21,2,LEN(AH21)-2),RIGHT(AH21,LEN(AH21)-1)),IF(RIGHT(AH21,1)="_",LEFT(AH21,LEN(AH21)-1),AH21)))</f>
         <v/>
       </c>
     </row>
@@ -2849,7 +2378,7 @@
       <c r="J22" s="4" t="inlineStr"/>
       <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="4">
-        <f>IF(AE22&lt;&gt;"",AE22,"")&amp;IF(AH22&lt;&gt;"",IF(AE22&lt;&gt;"","_"&amp;AH22,AH22),"")&amp;IF(AK22&lt;&gt;"",IF(AE22&lt;&gt;"","_"&amp;AK22,AK22),"")&amp;IF(AN22&lt;&gt;"",IF(AE22&lt;&gt;"","_"&amp;AN22,AN22),"")&amp;IF(AQ22&lt;&gt;"",IF(AE22&lt;&gt;"","_"&amp;AQ22,AQ22),"")</f>
+        <f>IF(AC22&lt;&gt;"",AC22,"")&amp;IF(AF22&lt;&gt;"",IF(AC22&lt;&gt;"","_"&amp;AF22,AF22),"")&amp;IF(AI22&lt;&gt;"",IF(AC22&lt;&gt;"","_"&amp;AI22,AI22),"")</f>
         <v/>
       </c>
       <c r="M22" s="4">
@@ -2870,68 +2399,42 @@
       <c r="V22" s="4" t="inlineStr"/>
       <c r="W22" s="4" t="inlineStr"/>
       <c r="X22" s="4" t="inlineStr"/>
-      <c r="Y22" s="4" t="inlineStr"/>
-      <c r="Z22" s="4" t="inlineStr"/>
-      <c r="AA22" s="4" t="n"/>
-      <c r="AB22" s="4" t="n"/>
+      <c r="Y22" s="4" t="n"/>
+      <c r="Z22" s="4" t="n"/>
+      <c r="AA22" s="4">
+        <f>IF(OR(LOWER(TRIM(A22))="",LOWER(TRIM(A22))="nan",LOWER(TRIM(A22))="none",LOWER(TRIM(A22))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A22))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB22" s="4">
+        <f>IF(AA22="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA22,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC22" s="4">
-        <f>IF(OR(LOWER(TRIM(A22))="",LOWER(TRIM(A22))="nan",LOWER(TRIM(A22))="none",LOWER(TRIM(A22))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A22))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB22="",AB22="_"),"",IF(LEFT(AB22,1)="_",IF(RIGHT(AB22,1)="_",MID(AB22,2,LEN(AB22)-2),RIGHT(AB22,LEN(AB22)-1)),IF(RIGHT(AB22,1)="_",LEFT(AB22,LEN(AB22)-1),AB22)))</f>
         <v/>
       </c>
       <c r="AD22" s="4">
-        <f>IF(AC22="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC22,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O22))="",LOWER(TRIM(O22))="nan",LOWER(TRIM(O22))="none",LOWER(TRIM(O22))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O22))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE22" s="4">
-        <f>IF(OR(AD22="",AD22="_"),"",IF(LEFT(AD22,1)="_",IF(RIGHT(AD22,1)="_",MID(AD22,2,LEN(AD22)-2),RIGHT(AD22,LEN(AD22)-1)),IF(RIGHT(AD22,1)="_",LEFT(AD22,LEN(AD22)-1),AD22)))</f>
+        <f>IF(AD22="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD22,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF22" s="4">
-        <f>IF(OR(LOWER(TRIM(O22))="",LOWER(TRIM(O22))="nan",LOWER(TRIM(O22))="none",LOWER(TRIM(O22))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O22))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE22="",AE22="_"),"",IF(LEFT(AE22,1)="_",IF(RIGHT(AE22,1)="_",MID(AE22,2,LEN(AE22)-2),RIGHT(AE22,LEN(AE22)-1)),IF(RIGHT(AE22,1)="_",LEFT(AE22,LEN(AE22)-1),AE22)))</f>
         <v/>
       </c>
       <c r="AG22" s="4">
-        <f>IF(AF22="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF22,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P22))="",LOWER(TRIM(P22))="nan",LOWER(TRIM(P22))="none",LOWER(TRIM(P22))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P22))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH22" s="4">
-        <f>IF(OR(AG22="",AG22="_"),"",IF(LEFT(AG22,1)="_",IF(RIGHT(AG22,1)="_",MID(AG22,2,LEN(AG22)-2),RIGHT(AG22,LEN(AG22)-1)),IF(RIGHT(AG22,1)="_",LEFT(AG22,LEN(AG22)-1),AG22)))</f>
+        <f>IF(AG22="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG22,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI22" s="4">
-        <f>IF(OR(LOWER(TRIM(P22))="",LOWER(TRIM(P22))="nan",LOWER(TRIM(P22))="none",LOWER(TRIM(P22))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P22))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ22" s="4">
-        <f>IF(AI22="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI22,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK22" s="4">
-        <f>IF(OR(AJ22="",AJ22="_"),"",IF(LEFT(AJ22,1)="_",IF(RIGHT(AJ22,1)="_",MID(AJ22,2,LEN(AJ22)-2),RIGHT(AJ22,LEN(AJ22)-1)),IF(RIGHT(AJ22,1)="_",LEFT(AJ22,LEN(AJ22)-1),AJ22)))</f>
-        <v/>
-      </c>
-      <c r="AL22" s="4">
-        <f>IF(OR(LOWER(TRIM(Q22))="",LOWER(TRIM(Q22))="nan",LOWER(TRIM(Q22))="none",LOWER(TRIM(Q22))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q22))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM22" s="4">
-        <f>IF(AL22="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL22,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN22" s="4">
-        <f>IF(OR(AM22="",AM22="_"),"",IF(LEFT(AM22,1)="_",IF(RIGHT(AM22,1)="_",MID(AM22,2,LEN(AM22)-2),RIGHT(AM22,LEN(AM22)-1)),IF(RIGHT(AM22,1)="_",LEFT(AM22,LEN(AM22)-1),AM22)))</f>
-        <v/>
-      </c>
-      <c r="AO22" s="4">
-        <f>IF(OR(LOWER(TRIM(R22))="",LOWER(TRIM(R22))="nan",LOWER(TRIM(R22))="none",LOWER(TRIM(R22))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R22))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP22" s="4">
-        <f>IF(AO22="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO22,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ22" s="4">
-        <f>IF(OR(AP22="",AP22="_"),"",IF(LEFT(AP22,1)="_",IF(RIGHT(AP22,1)="_",MID(AP22,2,LEN(AP22)-2),RIGHT(AP22,LEN(AP22)-1)),IF(RIGHT(AP22,1)="_",LEFT(AP22,LEN(AP22)-1),AP22)))</f>
+        <f>IF(OR(AH22="",AH22="_"),"",IF(LEFT(AH22,1)="_",IF(RIGHT(AH22,1)="_",MID(AH22,2,LEN(AH22)-2),RIGHT(AH22,LEN(AH22)-1)),IF(RIGHT(AH22,1)="_",LEFT(AH22,LEN(AH22)-1),AH22)))</f>
         <v/>
       </c>
     </row>
@@ -2948,7 +2451,7 @@
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="4">
-        <f>IF(AE23&lt;&gt;"",AE23,"")&amp;IF(AH23&lt;&gt;"",IF(AE23&lt;&gt;"","_"&amp;AH23,AH23),"")&amp;IF(AK23&lt;&gt;"",IF(AE23&lt;&gt;"","_"&amp;AK23,AK23),"")&amp;IF(AN23&lt;&gt;"",IF(AE23&lt;&gt;"","_"&amp;AN23,AN23),"")&amp;IF(AQ23&lt;&gt;"",IF(AE23&lt;&gt;"","_"&amp;AQ23,AQ23),"")</f>
+        <f>IF(AC23&lt;&gt;"",AC23,"")&amp;IF(AF23&lt;&gt;"",IF(AC23&lt;&gt;"","_"&amp;AF23,AF23),"")&amp;IF(AI23&lt;&gt;"",IF(AC23&lt;&gt;"","_"&amp;AI23,AI23),"")</f>
         <v/>
       </c>
       <c r="M23" s="4">
@@ -2969,68 +2472,42 @@
       <c r="V23" s="4" t="inlineStr"/>
       <c r="W23" s="4" t="inlineStr"/>
       <c r="X23" s="4" t="inlineStr"/>
-      <c r="Y23" s="4" t="inlineStr"/>
-      <c r="Z23" s="4" t="inlineStr"/>
-      <c r="AA23" s="4" t="n"/>
-      <c r="AB23" s="4" t="n"/>
+      <c r="Y23" s="4" t="n"/>
+      <c r="Z23" s="4" t="n"/>
+      <c r="AA23" s="4">
+        <f>IF(OR(LOWER(TRIM(A23))="",LOWER(TRIM(A23))="nan",LOWER(TRIM(A23))="none",LOWER(TRIM(A23))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A23))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB23" s="4">
+        <f>IF(AA23="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA23,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC23" s="4">
-        <f>IF(OR(LOWER(TRIM(A23))="",LOWER(TRIM(A23))="nan",LOWER(TRIM(A23))="none",LOWER(TRIM(A23))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A23))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB23="",AB23="_"),"",IF(LEFT(AB23,1)="_",IF(RIGHT(AB23,1)="_",MID(AB23,2,LEN(AB23)-2),RIGHT(AB23,LEN(AB23)-1)),IF(RIGHT(AB23,1)="_",LEFT(AB23,LEN(AB23)-1),AB23)))</f>
         <v/>
       </c>
       <c r="AD23" s="4">
-        <f>IF(AC23="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC23,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O23))="",LOWER(TRIM(O23))="nan",LOWER(TRIM(O23))="none",LOWER(TRIM(O23))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O23))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE23" s="4">
-        <f>IF(OR(AD23="",AD23="_"),"",IF(LEFT(AD23,1)="_",IF(RIGHT(AD23,1)="_",MID(AD23,2,LEN(AD23)-2),RIGHT(AD23,LEN(AD23)-1)),IF(RIGHT(AD23,1)="_",LEFT(AD23,LEN(AD23)-1),AD23)))</f>
+        <f>IF(AD23="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD23,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF23" s="4">
-        <f>IF(OR(LOWER(TRIM(O23))="",LOWER(TRIM(O23))="nan",LOWER(TRIM(O23))="none",LOWER(TRIM(O23))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O23))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE23="",AE23="_"),"",IF(LEFT(AE23,1)="_",IF(RIGHT(AE23,1)="_",MID(AE23,2,LEN(AE23)-2),RIGHT(AE23,LEN(AE23)-1)),IF(RIGHT(AE23,1)="_",LEFT(AE23,LEN(AE23)-1),AE23)))</f>
         <v/>
       </c>
       <c r="AG23" s="4">
-        <f>IF(AF23="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF23,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P23))="",LOWER(TRIM(P23))="nan",LOWER(TRIM(P23))="none",LOWER(TRIM(P23))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P23))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH23" s="4">
-        <f>IF(OR(AG23="",AG23="_"),"",IF(LEFT(AG23,1)="_",IF(RIGHT(AG23,1)="_",MID(AG23,2,LEN(AG23)-2),RIGHT(AG23,LEN(AG23)-1)),IF(RIGHT(AG23,1)="_",LEFT(AG23,LEN(AG23)-1),AG23)))</f>
+        <f>IF(AG23="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG23,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI23" s="4">
-        <f>IF(OR(LOWER(TRIM(P23))="",LOWER(TRIM(P23))="nan",LOWER(TRIM(P23))="none",LOWER(TRIM(P23))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P23))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ23" s="4">
-        <f>IF(AI23="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI23,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK23" s="4">
-        <f>IF(OR(AJ23="",AJ23="_"),"",IF(LEFT(AJ23,1)="_",IF(RIGHT(AJ23,1)="_",MID(AJ23,2,LEN(AJ23)-2),RIGHT(AJ23,LEN(AJ23)-1)),IF(RIGHT(AJ23,1)="_",LEFT(AJ23,LEN(AJ23)-1),AJ23)))</f>
-        <v/>
-      </c>
-      <c r="AL23" s="4">
-        <f>IF(OR(LOWER(TRIM(Q23))="",LOWER(TRIM(Q23))="nan",LOWER(TRIM(Q23))="none",LOWER(TRIM(Q23))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q23))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM23" s="4">
-        <f>IF(AL23="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL23,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN23" s="4">
-        <f>IF(OR(AM23="",AM23="_"),"",IF(LEFT(AM23,1)="_",IF(RIGHT(AM23,1)="_",MID(AM23,2,LEN(AM23)-2),RIGHT(AM23,LEN(AM23)-1)),IF(RIGHT(AM23,1)="_",LEFT(AM23,LEN(AM23)-1),AM23)))</f>
-        <v/>
-      </c>
-      <c r="AO23" s="4">
-        <f>IF(OR(LOWER(TRIM(R23))="",LOWER(TRIM(R23))="nan",LOWER(TRIM(R23))="none",LOWER(TRIM(R23))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R23))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP23" s="4">
-        <f>IF(AO23="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO23,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ23" s="4">
-        <f>IF(OR(AP23="",AP23="_"),"",IF(LEFT(AP23,1)="_",IF(RIGHT(AP23,1)="_",MID(AP23,2,LEN(AP23)-2),RIGHT(AP23,LEN(AP23)-1)),IF(RIGHT(AP23,1)="_",LEFT(AP23,LEN(AP23)-1),AP23)))</f>
+        <f>IF(OR(AH23="",AH23="_"),"",IF(LEFT(AH23,1)="_",IF(RIGHT(AH23,1)="_",MID(AH23,2,LEN(AH23)-2),RIGHT(AH23,LEN(AH23)-1)),IF(RIGHT(AH23,1)="_",LEFT(AH23,LEN(AH23)-1),AH23)))</f>
         <v/>
       </c>
     </row>
@@ -3047,7 +2524,7 @@
       <c r="J24" s="4" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="4">
-        <f>IF(AE24&lt;&gt;"",AE24,"")&amp;IF(AH24&lt;&gt;"",IF(AE24&lt;&gt;"","_"&amp;AH24,AH24),"")&amp;IF(AK24&lt;&gt;"",IF(AE24&lt;&gt;"","_"&amp;AK24,AK24),"")&amp;IF(AN24&lt;&gt;"",IF(AE24&lt;&gt;"","_"&amp;AN24,AN24),"")&amp;IF(AQ24&lt;&gt;"",IF(AE24&lt;&gt;"","_"&amp;AQ24,AQ24),"")</f>
+        <f>IF(AC24&lt;&gt;"",AC24,"")&amp;IF(AF24&lt;&gt;"",IF(AC24&lt;&gt;"","_"&amp;AF24,AF24),"")&amp;IF(AI24&lt;&gt;"",IF(AC24&lt;&gt;"","_"&amp;AI24,AI24),"")</f>
         <v/>
       </c>
       <c r="M24" s="4">
@@ -3068,68 +2545,42 @@
       <c r="V24" s="4" t="inlineStr"/>
       <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
-      <c r="Y24" s="4" t="inlineStr"/>
-      <c r="Z24" s="4" t="inlineStr"/>
-      <c r="AA24" s="4" t="n"/>
-      <c r="AB24" s="4" t="n"/>
+      <c r="Y24" s="4" t="n"/>
+      <c r="Z24" s="4" t="n"/>
+      <c r="AA24" s="4">
+        <f>IF(OR(LOWER(TRIM(A24))="",LOWER(TRIM(A24))="nan",LOWER(TRIM(A24))="none",LOWER(TRIM(A24))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A24))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB24" s="4">
+        <f>IF(AA24="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA24,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC24" s="4">
-        <f>IF(OR(LOWER(TRIM(A24))="",LOWER(TRIM(A24))="nan",LOWER(TRIM(A24))="none",LOWER(TRIM(A24))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A24))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB24="",AB24="_"),"",IF(LEFT(AB24,1)="_",IF(RIGHT(AB24,1)="_",MID(AB24,2,LEN(AB24)-2),RIGHT(AB24,LEN(AB24)-1)),IF(RIGHT(AB24,1)="_",LEFT(AB24,LEN(AB24)-1),AB24)))</f>
         <v/>
       </c>
       <c r="AD24" s="4">
-        <f>IF(AC24="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC24,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O24))="",LOWER(TRIM(O24))="nan",LOWER(TRIM(O24))="none",LOWER(TRIM(O24))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O24))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE24" s="4">
-        <f>IF(OR(AD24="",AD24="_"),"",IF(LEFT(AD24,1)="_",IF(RIGHT(AD24,1)="_",MID(AD24,2,LEN(AD24)-2),RIGHT(AD24,LEN(AD24)-1)),IF(RIGHT(AD24,1)="_",LEFT(AD24,LEN(AD24)-1),AD24)))</f>
+        <f>IF(AD24="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD24,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF24" s="4">
-        <f>IF(OR(LOWER(TRIM(O24))="",LOWER(TRIM(O24))="nan",LOWER(TRIM(O24))="none",LOWER(TRIM(O24))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O24))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE24="",AE24="_"),"",IF(LEFT(AE24,1)="_",IF(RIGHT(AE24,1)="_",MID(AE24,2,LEN(AE24)-2),RIGHT(AE24,LEN(AE24)-1)),IF(RIGHT(AE24,1)="_",LEFT(AE24,LEN(AE24)-1),AE24)))</f>
         <v/>
       </c>
       <c r="AG24" s="4">
-        <f>IF(AF24="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF24,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P24))="",LOWER(TRIM(P24))="nan",LOWER(TRIM(P24))="none",LOWER(TRIM(P24))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P24))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH24" s="4">
-        <f>IF(OR(AG24="",AG24="_"),"",IF(LEFT(AG24,1)="_",IF(RIGHT(AG24,1)="_",MID(AG24,2,LEN(AG24)-2),RIGHT(AG24,LEN(AG24)-1)),IF(RIGHT(AG24,1)="_",LEFT(AG24,LEN(AG24)-1),AG24)))</f>
+        <f>IF(AG24="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG24,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI24" s="4">
-        <f>IF(OR(LOWER(TRIM(P24))="",LOWER(TRIM(P24))="nan",LOWER(TRIM(P24))="none",LOWER(TRIM(P24))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P24))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ24" s="4">
-        <f>IF(AI24="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI24,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK24" s="4">
-        <f>IF(OR(AJ24="",AJ24="_"),"",IF(LEFT(AJ24,1)="_",IF(RIGHT(AJ24,1)="_",MID(AJ24,2,LEN(AJ24)-2),RIGHT(AJ24,LEN(AJ24)-1)),IF(RIGHT(AJ24,1)="_",LEFT(AJ24,LEN(AJ24)-1),AJ24)))</f>
-        <v/>
-      </c>
-      <c r="AL24" s="4">
-        <f>IF(OR(LOWER(TRIM(Q24))="",LOWER(TRIM(Q24))="nan",LOWER(TRIM(Q24))="none",LOWER(TRIM(Q24))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q24))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM24" s="4">
-        <f>IF(AL24="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL24,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN24" s="4">
-        <f>IF(OR(AM24="",AM24="_"),"",IF(LEFT(AM24,1)="_",IF(RIGHT(AM24,1)="_",MID(AM24,2,LEN(AM24)-2),RIGHT(AM24,LEN(AM24)-1)),IF(RIGHT(AM24,1)="_",LEFT(AM24,LEN(AM24)-1),AM24)))</f>
-        <v/>
-      </c>
-      <c r="AO24" s="4">
-        <f>IF(OR(LOWER(TRIM(R24))="",LOWER(TRIM(R24))="nan",LOWER(TRIM(R24))="none",LOWER(TRIM(R24))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R24))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP24" s="4">
-        <f>IF(AO24="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO24,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ24" s="4">
-        <f>IF(OR(AP24="",AP24="_"),"",IF(LEFT(AP24,1)="_",IF(RIGHT(AP24,1)="_",MID(AP24,2,LEN(AP24)-2),RIGHT(AP24,LEN(AP24)-1)),IF(RIGHT(AP24,1)="_",LEFT(AP24,LEN(AP24)-1),AP24)))</f>
+        <f>IF(OR(AH24="",AH24="_"),"",IF(LEFT(AH24,1)="_",IF(RIGHT(AH24,1)="_",MID(AH24,2,LEN(AH24)-2),RIGHT(AH24,LEN(AH24)-1)),IF(RIGHT(AH24,1)="_",LEFT(AH24,LEN(AH24)-1),AH24)))</f>
         <v/>
       </c>
     </row>
@@ -3146,7 +2597,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="4">
-        <f>IF(AE25&lt;&gt;"",AE25,"")&amp;IF(AH25&lt;&gt;"",IF(AE25&lt;&gt;"","_"&amp;AH25,AH25),"")&amp;IF(AK25&lt;&gt;"",IF(AE25&lt;&gt;"","_"&amp;AK25,AK25),"")&amp;IF(AN25&lt;&gt;"",IF(AE25&lt;&gt;"","_"&amp;AN25,AN25),"")&amp;IF(AQ25&lt;&gt;"",IF(AE25&lt;&gt;"","_"&amp;AQ25,AQ25),"")</f>
+        <f>IF(AC25&lt;&gt;"",AC25,"")&amp;IF(AF25&lt;&gt;"",IF(AC25&lt;&gt;"","_"&amp;AF25,AF25),"")&amp;IF(AI25&lt;&gt;"",IF(AC25&lt;&gt;"","_"&amp;AI25,AI25),"")</f>
         <v/>
       </c>
       <c r="M25" s="4">
@@ -3167,68 +2618,42 @@
       <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="inlineStr"/>
       <c r="X25" s="4" t="inlineStr"/>
-      <c r="Y25" s="4" t="inlineStr"/>
-      <c r="Z25" s="4" t="inlineStr"/>
-      <c r="AA25" s="4" t="n"/>
-      <c r="AB25" s="4" t="n"/>
+      <c r="Y25" s="4" t="n"/>
+      <c r="Z25" s="4" t="n"/>
+      <c r="AA25" s="4">
+        <f>IF(OR(LOWER(TRIM(A25))="",LOWER(TRIM(A25))="nan",LOWER(TRIM(A25))="none",LOWER(TRIM(A25))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A25))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB25" s="4">
+        <f>IF(AA25="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA25,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC25" s="4">
-        <f>IF(OR(LOWER(TRIM(A25))="",LOWER(TRIM(A25))="nan",LOWER(TRIM(A25))="none",LOWER(TRIM(A25))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A25))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB25="",AB25="_"),"",IF(LEFT(AB25,1)="_",IF(RIGHT(AB25,1)="_",MID(AB25,2,LEN(AB25)-2),RIGHT(AB25,LEN(AB25)-1)),IF(RIGHT(AB25,1)="_",LEFT(AB25,LEN(AB25)-1),AB25)))</f>
         <v/>
       </c>
       <c r="AD25" s="4">
-        <f>IF(AC25="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC25,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O25))="",LOWER(TRIM(O25))="nan",LOWER(TRIM(O25))="none",LOWER(TRIM(O25))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O25))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE25" s="4">
-        <f>IF(OR(AD25="",AD25="_"),"",IF(LEFT(AD25,1)="_",IF(RIGHT(AD25,1)="_",MID(AD25,2,LEN(AD25)-2),RIGHT(AD25,LEN(AD25)-1)),IF(RIGHT(AD25,1)="_",LEFT(AD25,LEN(AD25)-1),AD25)))</f>
+        <f>IF(AD25="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD25,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF25" s="4">
-        <f>IF(OR(LOWER(TRIM(O25))="",LOWER(TRIM(O25))="nan",LOWER(TRIM(O25))="none",LOWER(TRIM(O25))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O25))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE25="",AE25="_"),"",IF(LEFT(AE25,1)="_",IF(RIGHT(AE25,1)="_",MID(AE25,2,LEN(AE25)-2),RIGHT(AE25,LEN(AE25)-1)),IF(RIGHT(AE25,1)="_",LEFT(AE25,LEN(AE25)-1),AE25)))</f>
         <v/>
       </c>
       <c r="AG25" s="4">
-        <f>IF(AF25="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF25,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P25))="",LOWER(TRIM(P25))="nan",LOWER(TRIM(P25))="none",LOWER(TRIM(P25))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P25))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH25" s="4">
-        <f>IF(OR(AG25="",AG25="_"),"",IF(LEFT(AG25,1)="_",IF(RIGHT(AG25,1)="_",MID(AG25,2,LEN(AG25)-2),RIGHT(AG25,LEN(AG25)-1)),IF(RIGHT(AG25,1)="_",LEFT(AG25,LEN(AG25)-1),AG25)))</f>
+        <f>IF(AG25="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG25,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI25" s="4">
-        <f>IF(OR(LOWER(TRIM(P25))="",LOWER(TRIM(P25))="nan",LOWER(TRIM(P25))="none",LOWER(TRIM(P25))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P25))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ25" s="4">
-        <f>IF(AI25="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI25,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK25" s="4">
-        <f>IF(OR(AJ25="",AJ25="_"),"",IF(LEFT(AJ25,1)="_",IF(RIGHT(AJ25,1)="_",MID(AJ25,2,LEN(AJ25)-2),RIGHT(AJ25,LEN(AJ25)-1)),IF(RIGHT(AJ25,1)="_",LEFT(AJ25,LEN(AJ25)-1),AJ25)))</f>
-        <v/>
-      </c>
-      <c r="AL25" s="4">
-        <f>IF(OR(LOWER(TRIM(Q25))="",LOWER(TRIM(Q25))="nan",LOWER(TRIM(Q25))="none",LOWER(TRIM(Q25))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q25))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM25" s="4">
-        <f>IF(AL25="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL25,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN25" s="4">
-        <f>IF(OR(AM25="",AM25="_"),"",IF(LEFT(AM25,1)="_",IF(RIGHT(AM25,1)="_",MID(AM25,2,LEN(AM25)-2),RIGHT(AM25,LEN(AM25)-1)),IF(RIGHT(AM25,1)="_",LEFT(AM25,LEN(AM25)-1),AM25)))</f>
-        <v/>
-      </c>
-      <c r="AO25" s="4">
-        <f>IF(OR(LOWER(TRIM(R25))="",LOWER(TRIM(R25))="nan",LOWER(TRIM(R25))="none",LOWER(TRIM(R25))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R25))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP25" s="4">
-        <f>IF(AO25="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO25,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ25" s="4">
-        <f>IF(OR(AP25="",AP25="_"),"",IF(LEFT(AP25,1)="_",IF(RIGHT(AP25,1)="_",MID(AP25,2,LEN(AP25)-2),RIGHT(AP25,LEN(AP25)-1)),IF(RIGHT(AP25,1)="_",LEFT(AP25,LEN(AP25)-1),AP25)))</f>
+        <f>IF(OR(AH25="",AH25="_"),"",IF(LEFT(AH25,1)="_",IF(RIGHT(AH25,1)="_",MID(AH25,2,LEN(AH25)-2),RIGHT(AH25,LEN(AH25)-1)),IF(RIGHT(AH25,1)="_",LEFT(AH25,LEN(AH25)-1),AH25)))</f>
         <v/>
       </c>
     </row>
@@ -3245,7 +2670,7 @@
       <c r="J26" s="4" t="inlineStr"/>
       <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="4">
-        <f>IF(AE26&lt;&gt;"",AE26,"")&amp;IF(AH26&lt;&gt;"",IF(AE26&lt;&gt;"","_"&amp;AH26,AH26),"")&amp;IF(AK26&lt;&gt;"",IF(AE26&lt;&gt;"","_"&amp;AK26,AK26),"")&amp;IF(AN26&lt;&gt;"",IF(AE26&lt;&gt;"","_"&amp;AN26,AN26),"")&amp;IF(AQ26&lt;&gt;"",IF(AE26&lt;&gt;"","_"&amp;AQ26,AQ26),"")</f>
+        <f>IF(AC26&lt;&gt;"",AC26,"")&amp;IF(AF26&lt;&gt;"",IF(AC26&lt;&gt;"","_"&amp;AF26,AF26),"")&amp;IF(AI26&lt;&gt;"",IF(AC26&lt;&gt;"","_"&amp;AI26,AI26),"")</f>
         <v/>
       </c>
       <c r="M26" s="4">
@@ -3266,68 +2691,42 @@
       <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="4" t="inlineStr"/>
       <c r="X26" s="4" t="inlineStr"/>
-      <c r="Y26" s="4" t="inlineStr"/>
-      <c r="Z26" s="4" t="inlineStr"/>
-      <c r="AA26" s="4" t="n"/>
-      <c r="AB26" s="4" t="n"/>
+      <c r="Y26" s="4" t="n"/>
+      <c r="Z26" s="4" t="n"/>
+      <c r="AA26" s="4">
+        <f>IF(OR(LOWER(TRIM(A26))="",LOWER(TRIM(A26))="nan",LOWER(TRIM(A26))="none",LOWER(TRIM(A26))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A26))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB26" s="4">
+        <f>IF(AA26="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA26,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC26" s="4">
-        <f>IF(OR(LOWER(TRIM(A26))="",LOWER(TRIM(A26))="nan",LOWER(TRIM(A26))="none",LOWER(TRIM(A26))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A26))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB26="",AB26="_"),"",IF(LEFT(AB26,1)="_",IF(RIGHT(AB26,1)="_",MID(AB26,2,LEN(AB26)-2),RIGHT(AB26,LEN(AB26)-1)),IF(RIGHT(AB26,1)="_",LEFT(AB26,LEN(AB26)-1),AB26)))</f>
         <v/>
       </c>
       <c r="AD26" s="4">
-        <f>IF(AC26="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC26,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O26))="",LOWER(TRIM(O26))="nan",LOWER(TRIM(O26))="none",LOWER(TRIM(O26))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O26))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE26" s="4">
-        <f>IF(OR(AD26="",AD26="_"),"",IF(LEFT(AD26,1)="_",IF(RIGHT(AD26,1)="_",MID(AD26,2,LEN(AD26)-2),RIGHT(AD26,LEN(AD26)-1)),IF(RIGHT(AD26,1)="_",LEFT(AD26,LEN(AD26)-1),AD26)))</f>
+        <f>IF(AD26="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD26,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF26" s="4">
-        <f>IF(OR(LOWER(TRIM(O26))="",LOWER(TRIM(O26))="nan",LOWER(TRIM(O26))="none",LOWER(TRIM(O26))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O26))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE26="",AE26="_"),"",IF(LEFT(AE26,1)="_",IF(RIGHT(AE26,1)="_",MID(AE26,2,LEN(AE26)-2),RIGHT(AE26,LEN(AE26)-1)),IF(RIGHT(AE26,1)="_",LEFT(AE26,LEN(AE26)-1),AE26)))</f>
         <v/>
       </c>
       <c r="AG26" s="4">
-        <f>IF(AF26="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF26,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P26))="",LOWER(TRIM(P26))="nan",LOWER(TRIM(P26))="none",LOWER(TRIM(P26))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P26))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH26" s="4">
-        <f>IF(OR(AG26="",AG26="_"),"",IF(LEFT(AG26,1)="_",IF(RIGHT(AG26,1)="_",MID(AG26,2,LEN(AG26)-2),RIGHT(AG26,LEN(AG26)-1)),IF(RIGHT(AG26,1)="_",LEFT(AG26,LEN(AG26)-1),AG26)))</f>
+        <f>IF(AG26="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG26,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI26" s="4">
-        <f>IF(OR(LOWER(TRIM(P26))="",LOWER(TRIM(P26))="nan",LOWER(TRIM(P26))="none",LOWER(TRIM(P26))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P26))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ26" s="4">
-        <f>IF(AI26="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI26,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK26" s="4">
-        <f>IF(OR(AJ26="",AJ26="_"),"",IF(LEFT(AJ26,1)="_",IF(RIGHT(AJ26,1)="_",MID(AJ26,2,LEN(AJ26)-2),RIGHT(AJ26,LEN(AJ26)-1)),IF(RIGHT(AJ26,1)="_",LEFT(AJ26,LEN(AJ26)-1),AJ26)))</f>
-        <v/>
-      </c>
-      <c r="AL26" s="4">
-        <f>IF(OR(LOWER(TRIM(Q26))="",LOWER(TRIM(Q26))="nan",LOWER(TRIM(Q26))="none",LOWER(TRIM(Q26))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q26))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM26" s="4">
-        <f>IF(AL26="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL26,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN26" s="4">
-        <f>IF(OR(AM26="",AM26="_"),"",IF(LEFT(AM26,1)="_",IF(RIGHT(AM26,1)="_",MID(AM26,2,LEN(AM26)-2),RIGHT(AM26,LEN(AM26)-1)),IF(RIGHT(AM26,1)="_",LEFT(AM26,LEN(AM26)-1),AM26)))</f>
-        <v/>
-      </c>
-      <c r="AO26" s="4">
-        <f>IF(OR(LOWER(TRIM(R26))="",LOWER(TRIM(R26))="nan",LOWER(TRIM(R26))="none",LOWER(TRIM(R26))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R26))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP26" s="4">
-        <f>IF(AO26="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO26,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ26" s="4">
-        <f>IF(OR(AP26="",AP26="_"),"",IF(LEFT(AP26,1)="_",IF(RIGHT(AP26,1)="_",MID(AP26,2,LEN(AP26)-2),RIGHT(AP26,LEN(AP26)-1)),IF(RIGHT(AP26,1)="_",LEFT(AP26,LEN(AP26)-1),AP26)))</f>
+        <f>IF(OR(AH26="",AH26="_"),"",IF(LEFT(AH26,1)="_",IF(RIGHT(AH26,1)="_",MID(AH26,2,LEN(AH26)-2),RIGHT(AH26,LEN(AH26)-1)),IF(RIGHT(AH26,1)="_",LEFT(AH26,LEN(AH26)-1),AH26)))</f>
         <v/>
       </c>
     </row>
@@ -3344,7 +2743,7 @@
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="4">
-        <f>IF(AE27&lt;&gt;"",AE27,"")&amp;IF(AH27&lt;&gt;"",IF(AE27&lt;&gt;"","_"&amp;AH27,AH27),"")&amp;IF(AK27&lt;&gt;"",IF(AE27&lt;&gt;"","_"&amp;AK27,AK27),"")&amp;IF(AN27&lt;&gt;"",IF(AE27&lt;&gt;"","_"&amp;AN27,AN27),"")&amp;IF(AQ27&lt;&gt;"",IF(AE27&lt;&gt;"","_"&amp;AQ27,AQ27),"")</f>
+        <f>IF(AC27&lt;&gt;"",AC27,"")&amp;IF(AF27&lt;&gt;"",IF(AC27&lt;&gt;"","_"&amp;AF27,AF27),"")&amp;IF(AI27&lt;&gt;"",IF(AC27&lt;&gt;"","_"&amp;AI27,AI27),"")</f>
         <v/>
       </c>
       <c r="M27" s="4">
@@ -3365,68 +2764,42 @@
       <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
-      <c r="Y27" s="4" t="inlineStr"/>
-      <c r="Z27" s="4" t="inlineStr"/>
-      <c r="AA27" s="4" t="n"/>
-      <c r="AB27" s="4" t="n"/>
+      <c r="Y27" s="4" t="n"/>
+      <c r="Z27" s="4" t="n"/>
+      <c r="AA27" s="4">
+        <f>IF(OR(LOWER(TRIM(A27))="",LOWER(TRIM(A27))="nan",LOWER(TRIM(A27))="none",LOWER(TRIM(A27))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A27))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB27" s="4">
+        <f>IF(AA27="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA27,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC27" s="4">
-        <f>IF(OR(LOWER(TRIM(A27))="",LOWER(TRIM(A27))="nan",LOWER(TRIM(A27))="none",LOWER(TRIM(A27))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A27))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB27="",AB27="_"),"",IF(LEFT(AB27,1)="_",IF(RIGHT(AB27,1)="_",MID(AB27,2,LEN(AB27)-2),RIGHT(AB27,LEN(AB27)-1)),IF(RIGHT(AB27,1)="_",LEFT(AB27,LEN(AB27)-1),AB27)))</f>
         <v/>
       </c>
       <c r="AD27" s="4">
-        <f>IF(AC27="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC27,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O27))="",LOWER(TRIM(O27))="nan",LOWER(TRIM(O27))="none",LOWER(TRIM(O27))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O27))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE27" s="4">
-        <f>IF(OR(AD27="",AD27="_"),"",IF(LEFT(AD27,1)="_",IF(RIGHT(AD27,1)="_",MID(AD27,2,LEN(AD27)-2),RIGHT(AD27,LEN(AD27)-1)),IF(RIGHT(AD27,1)="_",LEFT(AD27,LEN(AD27)-1),AD27)))</f>
+        <f>IF(AD27="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD27,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF27" s="4">
-        <f>IF(OR(LOWER(TRIM(O27))="",LOWER(TRIM(O27))="nan",LOWER(TRIM(O27))="none",LOWER(TRIM(O27))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O27))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE27="",AE27="_"),"",IF(LEFT(AE27,1)="_",IF(RIGHT(AE27,1)="_",MID(AE27,2,LEN(AE27)-2),RIGHT(AE27,LEN(AE27)-1)),IF(RIGHT(AE27,1)="_",LEFT(AE27,LEN(AE27)-1),AE27)))</f>
         <v/>
       </c>
       <c r="AG27" s="4">
-        <f>IF(AF27="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF27,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P27))="",LOWER(TRIM(P27))="nan",LOWER(TRIM(P27))="none",LOWER(TRIM(P27))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P27))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH27" s="4">
-        <f>IF(OR(AG27="",AG27="_"),"",IF(LEFT(AG27,1)="_",IF(RIGHT(AG27,1)="_",MID(AG27,2,LEN(AG27)-2),RIGHT(AG27,LEN(AG27)-1)),IF(RIGHT(AG27,1)="_",LEFT(AG27,LEN(AG27)-1),AG27)))</f>
+        <f>IF(AG27="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG27,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI27" s="4">
-        <f>IF(OR(LOWER(TRIM(P27))="",LOWER(TRIM(P27))="nan",LOWER(TRIM(P27))="none",LOWER(TRIM(P27))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P27))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ27" s="4">
-        <f>IF(AI27="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI27,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK27" s="4">
-        <f>IF(OR(AJ27="",AJ27="_"),"",IF(LEFT(AJ27,1)="_",IF(RIGHT(AJ27,1)="_",MID(AJ27,2,LEN(AJ27)-2),RIGHT(AJ27,LEN(AJ27)-1)),IF(RIGHT(AJ27,1)="_",LEFT(AJ27,LEN(AJ27)-1),AJ27)))</f>
-        <v/>
-      </c>
-      <c r="AL27" s="4">
-        <f>IF(OR(LOWER(TRIM(Q27))="",LOWER(TRIM(Q27))="nan",LOWER(TRIM(Q27))="none",LOWER(TRIM(Q27))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q27))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM27" s="4">
-        <f>IF(AL27="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL27,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN27" s="4">
-        <f>IF(OR(AM27="",AM27="_"),"",IF(LEFT(AM27,1)="_",IF(RIGHT(AM27,1)="_",MID(AM27,2,LEN(AM27)-2),RIGHT(AM27,LEN(AM27)-1)),IF(RIGHT(AM27,1)="_",LEFT(AM27,LEN(AM27)-1),AM27)))</f>
-        <v/>
-      </c>
-      <c r="AO27" s="4">
-        <f>IF(OR(LOWER(TRIM(R27))="",LOWER(TRIM(R27))="nan",LOWER(TRIM(R27))="none",LOWER(TRIM(R27))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R27))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP27" s="4">
-        <f>IF(AO27="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO27,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ27" s="4">
-        <f>IF(OR(AP27="",AP27="_"),"",IF(LEFT(AP27,1)="_",IF(RIGHT(AP27,1)="_",MID(AP27,2,LEN(AP27)-2),RIGHT(AP27,LEN(AP27)-1)),IF(RIGHT(AP27,1)="_",LEFT(AP27,LEN(AP27)-1),AP27)))</f>
+        <f>IF(OR(AH27="",AH27="_"),"",IF(LEFT(AH27,1)="_",IF(RIGHT(AH27,1)="_",MID(AH27,2,LEN(AH27)-2),RIGHT(AH27,LEN(AH27)-1)),IF(RIGHT(AH27,1)="_",LEFT(AH27,LEN(AH27)-1),AH27)))</f>
         <v/>
       </c>
     </row>
@@ -3443,7 +2816,7 @@
       <c r="J28" s="4" t="inlineStr"/>
       <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="4">
-        <f>IF(AE28&lt;&gt;"",AE28,"")&amp;IF(AH28&lt;&gt;"",IF(AE28&lt;&gt;"","_"&amp;AH28,AH28),"")&amp;IF(AK28&lt;&gt;"",IF(AE28&lt;&gt;"","_"&amp;AK28,AK28),"")&amp;IF(AN28&lt;&gt;"",IF(AE28&lt;&gt;"","_"&amp;AN28,AN28),"")&amp;IF(AQ28&lt;&gt;"",IF(AE28&lt;&gt;"","_"&amp;AQ28,AQ28),"")</f>
+        <f>IF(AC28&lt;&gt;"",AC28,"")&amp;IF(AF28&lt;&gt;"",IF(AC28&lt;&gt;"","_"&amp;AF28,AF28),"")&amp;IF(AI28&lt;&gt;"",IF(AC28&lt;&gt;"","_"&amp;AI28,AI28),"")</f>
         <v/>
       </c>
       <c r="M28" s="4">
@@ -3464,68 +2837,42 @@
       <c r="V28" s="4" t="inlineStr"/>
       <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
-      <c r="Y28" s="4" t="inlineStr"/>
-      <c r="Z28" s="4" t="inlineStr"/>
-      <c r="AA28" s="4" t="n"/>
-      <c r="AB28" s="4" t="n"/>
+      <c r="Y28" s="4" t="n"/>
+      <c r="Z28" s="4" t="n"/>
+      <c r="AA28" s="4">
+        <f>IF(OR(LOWER(TRIM(A28))="",LOWER(TRIM(A28))="nan",LOWER(TRIM(A28))="none",LOWER(TRIM(A28))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A28))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB28" s="4">
+        <f>IF(AA28="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA28,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC28" s="4">
-        <f>IF(OR(LOWER(TRIM(A28))="",LOWER(TRIM(A28))="nan",LOWER(TRIM(A28))="none",LOWER(TRIM(A28))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A28))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB28="",AB28="_"),"",IF(LEFT(AB28,1)="_",IF(RIGHT(AB28,1)="_",MID(AB28,2,LEN(AB28)-2),RIGHT(AB28,LEN(AB28)-1)),IF(RIGHT(AB28,1)="_",LEFT(AB28,LEN(AB28)-1),AB28)))</f>
         <v/>
       </c>
       <c r="AD28" s="4">
-        <f>IF(AC28="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC28,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O28))="",LOWER(TRIM(O28))="nan",LOWER(TRIM(O28))="none",LOWER(TRIM(O28))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O28))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE28" s="4">
-        <f>IF(OR(AD28="",AD28="_"),"",IF(LEFT(AD28,1)="_",IF(RIGHT(AD28,1)="_",MID(AD28,2,LEN(AD28)-2),RIGHT(AD28,LEN(AD28)-1)),IF(RIGHT(AD28,1)="_",LEFT(AD28,LEN(AD28)-1),AD28)))</f>
+        <f>IF(AD28="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD28,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF28" s="4">
-        <f>IF(OR(LOWER(TRIM(O28))="",LOWER(TRIM(O28))="nan",LOWER(TRIM(O28))="none",LOWER(TRIM(O28))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O28))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE28="",AE28="_"),"",IF(LEFT(AE28,1)="_",IF(RIGHT(AE28,1)="_",MID(AE28,2,LEN(AE28)-2),RIGHT(AE28,LEN(AE28)-1)),IF(RIGHT(AE28,1)="_",LEFT(AE28,LEN(AE28)-1),AE28)))</f>
         <v/>
       </c>
       <c r="AG28" s="4">
-        <f>IF(AF28="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF28,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P28))="",LOWER(TRIM(P28))="nan",LOWER(TRIM(P28))="none",LOWER(TRIM(P28))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P28))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH28" s="4">
-        <f>IF(OR(AG28="",AG28="_"),"",IF(LEFT(AG28,1)="_",IF(RIGHT(AG28,1)="_",MID(AG28,2,LEN(AG28)-2),RIGHT(AG28,LEN(AG28)-1)),IF(RIGHT(AG28,1)="_",LEFT(AG28,LEN(AG28)-1),AG28)))</f>
+        <f>IF(AG28="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG28,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI28" s="4">
-        <f>IF(OR(LOWER(TRIM(P28))="",LOWER(TRIM(P28))="nan",LOWER(TRIM(P28))="none",LOWER(TRIM(P28))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P28))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ28" s="4">
-        <f>IF(AI28="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI28,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK28" s="4">
-        <f>IF(OR(AJ28="",AJ28="_"),"",IF(LEFT(AJ28,1)="_",IF(RIGHT(AJ28,1)="_",MID(AJ28,2,LEN(AJ28)-2),RIGHT(AJ28,LEN(AJ28)-1)),IF(RIGHT(AJ28,1)="_",LEFT(AJ28,LEN(AJ28)-1),AJ28)))</f>
-        <v/>
-      </c>
-      <c r="AL28" s="4">
-        <f>IF(OR(LOWER(TRIM(Q28))="",LOWER(TRIM(Q28))="nan",LOWER(TRIM(Q28))="none",LOWER(TRIM(Q28))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q28))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM28" s="4">
-        <f>IF(AL28="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL28,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN28" s="4">
-        <f>IF(OR(AM28="",AM28="_"),"",IF(LEFT(AM28,1)="_",IF(RIGHT(AM28,1)="_",MID(AM28,2,LEN(AM28)-2),RIGHT(AM28,LEN(AM28)-1)),IF(RIGHT(AM28,1)="_",LEFT(AM28,LEN(AM28)-1),AM28)))</f>
-        <v/>
-      </c>
-      <c r="AO28" s="4">
-        <f>IF(OR(LOWER(TRIM(R28))="",LOWER(TRIM(R28))="nan",LOWER(TRIM(R28))="none",LOWER(TRIM(R28))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R28))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP28" s="4">
-        <f>IF(AO28="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO28,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ28" s="4">
-        <f>IF(OR(AP28="",AP28="_"),"",IF(LEFT(AP28,1)="_",IF(RIGHT(AP28,1)="_",MID(AP28,2,LEN(AP28)-2),RIGHT(AP28,LEN(AP28)-1)),IF(RIGHT(AP28,1)="_",LEFT(AP28,LEN(AP28)-1),AP28)))</f>
+        <f>IF(OR(AH28="",AH28="_"),"",IF(LEFT(AH28,1)="_",IF(RIGHT(AH28,1)="_",MID(AH28,2,LEN(AH28)-2),RIGHT(AH28,LEN(AH28)-1)),IF(RIGHT(AH28,1)="_",LEFT(AH28,LEN(AH28)-1),AH28)))</f>
         <v/>
       </c>
     </row>
@@ -3542,7 +2889,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="4">
-        <f>IF(AE29&lt;&gt;"",AE29,"")&amp;IF(AH29&lt;&gt;"",IF(AE29&lt;&gt;"","_"&amp;AH29,AH29),"")&amp;IF(AK29&lt;&gt;"",IF(AE29&lt;&gt;"","_"&amp;AK29,AK29),"")&amp;IF(AN29&lt;&gt;"",IF(AE29&lt;&gt;"","_"&amp;AN29,AN29),"")&amp;IF(AQ29&lt;&gt;"",IF(AE29&lt;&gt;"","_"&amp;AQ29,AQ29),"")</f>
+        <f>IF(AC29&lt;&gt;"",AC29,"")&amp;IF(AF29&lt;&gt;"",IF(AC29&lt;&gt;"","_"&amp;AF29,AF29),"")&amp;IF(AI29&lt;&gt;"",IF(AC29&lt;&gt;"","_"&amp;AI29,AI29),"")</f>
         <v/>
       </c>
       <c r="M29" s="4">
@@ -3563,68 +2910,42 @@
       <c r="V29" s="4" t="inlineStr"/>
       <c r="W29" s="4" t="inlineStr"/>
       <c r="X29" s="4" t="inlineStr"/>
-      <c r="Y29" s="4" t="inlineStr"/>
-      <c r="Z29" s="4" t="inlineStr"/>
-      <c r="AA29" s="4" t="n"/>
-      <c r="AB29" s="4" t="n"/>
+      <c r="Y29" s="4" t="n"/>
+      <c r="Z29" s="4" t="n"/>
+      <c r="AA29" s="4">
+        <f>IF(OR(LOWER(TRIM(A29))="",LOWER(TRIM(A29))="nan",LOWER(TRIM(A29))="none",LOWER(TRIM(A29))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A29))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB29" s="4">
+        <f>IF(AA29="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA29,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC29" s="4">
-        <f>IF(OR(LOWER(TRIM(A29))="",LOWER(TRIM(A29))="nan",LOWER(TRIM(A29))="none",LOWER(TRIM(A29))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A29))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB29="",AB29="_"),"",IF(LEFT(AB29,1)="_",IF(RIGHT(AB29,1)="_",MID(AB29,2,LEN(AB29)-2),RIGHT(AB29,LEN(AB29)-1)),IF(RIGHT(AB29,1)="_",LEFT(AB29,LEN(AB29)-1),AB29)))</f>
         <v/>
       </c>
       <c r="AD29" s="4">
-        <f>IF(AC29="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC29,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O29))="",LOWER(TRIM(O29))="nan",LOWER(TRIM(O29))="none",LOWER(TRIM(O29))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O29))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE29" s="4">
-        <f>IF(OR(AD29="",AD29="_"),"",IF(LEFT(AD29,1)="_",IF(RIGHT(AD29,1)="_",MID(AD29,2,LEN(AD29)-2),RIGHT(AD29,LEN(AD29)-1)),IF(RIGHT(AD29,1)="_",LEFT(AD29,LEN(AD29)-1),AD29)))</f>
+        <f>IF(AD29="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD29,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF29" s="4">
-        <f>IF(OR(LOWER(TRIM(O29))="",LOWER(TRIM(O29))="nan",LOWER(TRIM(O29))="none",LOWER(TRIM(O29))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O29))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE29="",AE29="_"),"",IF(LEFT(AE29,1)="_",IF(RIGHT(AE29,1)="_",MID(AE29,2,LEN(AE29)-2),RIGHT(AE29,LEN(AE29)-1)),IF(RIGHT(AE29,1)="_",LEFT(AE29,LEN(AE29)-1),AE29)))</f>
         <v/>
       </c>
       <c r="AG29" s="4">
-        <f>IF(AF29="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF29,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P29))="",LOWER(TRIM(P29))="nan",LOWER(TRIM(P29))="none",LOWER(TRIM(P29))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P29))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH29" s="4">
-        <f>IF(OR(AG29="",AG29="_"),"",IF(LEFT(AG29,1)="_",IF(RIGHT(AG29,1)="_",MID(AG29,2,LEN(AG29)-2),RIGHT(AG29,LEN(AG29)-1)),IF(RIGHT(AG29,1)="_",LEFT(AG29,LEN(AG29)-1),AG29)))</f>
+        <f>IF(AG29="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG29,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI29" s="4">
-        <f>IF(OR(LOWER(TRIM(P29))="",LOWER(TRIM(P29))="nan",LOWER(TRIM(P29))="none",LOWER(TRIM(P29))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P29))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ29" s="4">
-        <f>IF(AI29="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI29,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK29" s="4">
-        <f>IF(OR(AJ29="",AJ29="_"),"",IF(LEFT(AJ29,1)="_",IF(RIGHT(AJ29,1)="_",MID(AJ29,2,LEN(AJ29)-2),RIGHT(AJ29,LEN(AJ29)-1)),IF(RIGHT(AJ29,1)="_",LEFT(AJ29,LEN(AJ29)-1),AJ29)))</f>
-        <v/>
-      </c>
-      <c r="AL29" s="4">
-        <f>IF(OR(LOWER(TRIM(Q29))="",LOWER(TRIM(Q29))="nan",LOWER(TRIM(Q29))="none",LOWER(TRIM(Q29))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q29))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM29" s="4">
-        <f>IF(AL29="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL29,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN29" s="4">
-        <f>IF(OR(AM29="",AM29="_"),"",IF(LEFT(AM29,1)="_",IF(RIGHT(AM29,1)="_",MID(AM29,2,LEN(AM29)-2),RIGHT(AM29,LEN(AM29)-1)),IF(RIGHT(AM29,1)="_",LEFT(AM29,LEN(AM29)-1),AM29)))</f>
-        <v/>
-      </c>
-      <c r="AO29" s="4">
-        <f>IF(OR(LOWER(TRIM(R29))="",LOWER(TRIM(R29))="nan",LOWER(TRIM(R29))="none",LOWER(TRIM(R29))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R29))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP29" s="4">
-        <f>IF(AO29="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO29,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ29" s="4">
-        <f>IF(OR(AP29="",AP29="_"),"",IF(LEFT(AP29,1)="_",IF(RIGHT(AP29,1)="_",MID(AP29,2,LEN(AP29)-2),RIGHT(AP29,LEN(AP29)-1)),IF(RIGHT(AP29,1)="_",LEFT(AP29,LEN(AP29)-1),AP29)))</f>
+        <f>IF(OR(AH29="",AH29="_"),"",IF(LEFT(AH29,1)="_",IF(RIGHT(AH29,1)="_",MID(AH29,2,LEN(AH29)-2),RIGHT(AH29,LEN(AH29)-1)),IF(RIGHT(AH29,1)="_",LEFT(AH29,LEN(AH29)-1),AH29)))</f>
         <v/>
       </c>
     </row>
@@ -3641,7 +2962,7 @@
       <c r="J30" s="4" t="inlineStr"/>
       <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="4">
-        <f>IF(AE30&lt;&gt;"",AE30,"")&amp;IF(AH30&lt;&gt;"",IF(AE30&lt;&gt;"","_"&amp;AH30,AH30),"")&amp;IF(AK30&lt;&gt;"",IF(AE30&lt;&gt;"","_"&amp;AK30,AK30),"")&amp;IF(AN30&lt;&gt;"",IF(AE30&lt;&gt;"","_"&amp;AN30,AN30),"")&amp;IF(AQ30&lt;&gt;"",IF(AE30&lt;&gt;"","_"&amp;AQ30,AQ30),"")</f>
+        <f>IF(AC30&lt;&gt;"",AC30,"")&amp;IF(AF30&lt;&gt;"",IF(AC30&lt;&gt;"","_"&amp;AF30,AF30),"")&amp;IF(AI30&lt;&gt;"",IF(AC30&lt;&gt;"","_"&amp;AI30,AI30),"")</f>
         <v/>
       </c>
       <c r="M30" s="4">
@@ -3662,68 +2983,42 @@
       <c r="V30" s="4" t="inlineStr"/>
       <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
-      <c r="Y30" s="4" t="inlineStr"/>
-      <c r="Z30" s="4" t="inlineStr"/>
-      <c r="AA30" s="4" t="n"/>
-      <c r="AB30" s="4" t="n"/>
+      <c r="Y30" s="4" t="n"/>
+      <c r="Z30" s="4" t="n"/>
+      <c r="AA30" s="4">
+        <f>IF(OR(LOWER(TRIM(A30))="",LOWER(TRIM(A30))="nan",LOWER(TRIM(A30))="none",LOWER(TRIM(A30))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A30))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB30" s="4">
+        <f>IF(AA30="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA30,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC30" s="4">
-        <f>IF(OR(LOWER(TRIM(A30))="",LOWER(TRIM(A30))="nan",LOWER(TRIM(A30))="none",LOWER(TRIM(A30))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A30))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB30="",AB30="_"),"",IF(LEFT(AB30,1)="_",IF(RIGHT(AB30,1)="_",MID(AB30,2,LEN(AB30)-2),RIGHT(AB30,LEN(AB30)-1)),IF(RIGHT(AB30,1)="_",LEFT(AB30,LEN(AB30)-1),AB30)))</f>
         <v/>
       </c>
       <c r="AD30" s="4">
-        <f>IF(AC30="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC30,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O30))="",LOWER(TRIM(O30))="nan",LOWER(TRIM(O30))="none",LOWER(TRIM(O30))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O30))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE30" s="4">
-        <f>IF(OR(AD30="",AD30="_"),"",IF(LEFT(AD30,1)="_",IF(RIGHT(AD30,1)="_",MID(AD30,2,LEN(AD30)-2),RIGHT(AD30,LEN(AD30)-1)),IF(RIGHT(AD30,1)="_",LEFT(AD30,LEN(AD30)-1),AD30)))</f>
+        <f>IF(AD30="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD30,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF30" s="4">
-        <f>IF(OR(LOWER(TRIM(O30))="",LOWER(TRIM(O30))="nan",LOWER(TRIM(O30))="none",LOWER(TRIM(O30))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O30))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE30="",AE30="_"),"",IF(LEFT(AE30,1)="_",IF(RIGHT(AE30,1)="_",MID(AE30,2,LEN(AE30)-2),RIGHT(AE30,LEN(AE30)-1)),IF(RIGHT(AE30,1)="_",LEFT(AE30,LEN(AE30)-1),AE30)))</f>
         <v/>
       </c>
       <c r="AG30" s="4">
-        <f>IF(AF30="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF30,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P30))="",LOWER(TRIM(P30))="nan",LOWER(TRIM(P30))="none",LOWER(TRIM(P30))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P30))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH30" s="4">
-        <f>IF(OR(AG30="",AG30="_"),"",IF(LEFT(AG30,1)="_",IF(RIGHT(AG30,1)="_",MID(AG30,2,LEN(AG30)-2),RIGHT(AG30,LEN(AG30)-1)),IF(RIGHT(AG30,1)="_",LEFT(AG30,LEN(AG30)-1),AG30)))</f>
+        <f>IF(AG30="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG30,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI30" s="4">
-        <f>IF(OR(LOWER(TRIM(P30))="",LOWER(TRIM(P30))="nan",LOWER(TRIM(P30))="none",LOWER(TRIM(P30))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P30))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ30" s="4">
-        <f>IF(AI30="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI30,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK30" s="4">
-        <f>IF(OR(AJ30="",AJ30="_"),"",IF(LEFT(AJ30,1)="_",IF(RIGHT(AJ30,1)="_",MID(AJ30,2,LEN(AJ30)-2),RIGHT(AJ30,LEN(AJ30)-1)),IF(RIGHT(AJ30,1)="_",LEFT(AJ30,LEN(AJ30)-1),AJ30)))</f>
-        <v/>
-      </c>
-      <c r="AL30" s="4">
-        <f>IF(OR(LOWER(TRIM(Q30))="",LOWER(TRIM(Q30))="nan",LOWER(TRIM(Q30))="none",LOWER(TRIM(Q30))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q30))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM30" s="4">
-        <f>IF(AL30="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL30,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN30" s="4">
-        <f>IF(OR(AM30="",AM30="_"),"",IF(LEFT(AM30,1)="_",IF(RIGHT(AM30,1)="_",MID(AM30,2,LEN(AM30)-2),RIGHT(AM30,LEN(AM30)-1)),IF(RIGHT(AM30,1)="_",LEFT(AM30,LEN(AM30)-1),AM30)))</f>
-        <v/>
-      </c>
-      <c r="AO30" s="4">
-        <f>IF(OR(LOWER(TRIM(R30))="",LOWER(TRIM(R30))="nan",LOWER(TRIM(R30))="none",LOWER(TRIM(R30))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R30))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP30" s="4">
-        <f>IF(AO30="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO30,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ30" s="4">
-        <f>IF(OR(AP30="",AP30="_"),"",IF(LEFT(AP30,1)="_",IF(RIGHT(AP30,1)="_",MID(AP30,2,LEN(AP30)-2),RIGHT(AP30,LEN(AP30)-1)),IF(RIGHT(AP30,1)="_",LEFT(AP30,LEN(AP30)-1),AP30)))</f>
+        <f>IF(OR(AH30="",AH30="_"),"",IF(LEFT(AH30,1)="_",IF(RIGHT(AH30,1)="_",MID(AH30,2,LEN(AH30)-2),RIGHT(AH30,LEN(AH30)-1)),IF(RIGHT(AH30,1)="_",LEFT(AH30,LEN(AH30)-1),AH30)))</f>
         <v/>
       </c>
     </row>
@@ -3740,7 +3035,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="4">
-        <f>IF(AE31&lt;&gt;"",AE31,"")&amp;IF(AH31&lt;&gt;"",IF(AE31&lt;&gt;"","_"&amp;AH31,AH31),"")&amp;IF(AK31&lt;&gt;"",IF(AE31&lt;&gt;"","_"&amp;AK31,AK31),"")&amp;IF(AN31&lt;&gt;"",IF(AE31&lt;&gt;"","_"&amp;AN31,AN31),"")&amp;IF(AQ31&lt;&gt;"",IF(AE31&lt;&gt;"","_"&amp;AQ31,AQ31),"")</f>
+        <f>IF(AC31&lt;&gt;"",AC31,"")&amp;IF(AF31&lt;&gt;"",IF(AC31&lt;&gt;"","_"&amp;AF31,AF31),"")&amp;IF(AI31&lt;&gt;"",IF(AC31&lt;&gt;"","_"&amp;AI31,AI31),"")</f>
         <v/>
       </c>
       <c r="M31" s="4">
@@ -3761,68 +3056,42 @@
       <c r="V31" s="4" t="inlineStr"/>
       <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
-      <c r="Y31" s="4" t="inlineStr"/>
-      <c r="Z31" s="4" t="inlineStr"/>
-      <c r="AA31" s="4" t="n"/>
-      <c r="AB31" s="4" t="n"/>
+      <c r="Y31" s="4" t="n"/>
+      <c r="Z31" s="4" t="n"/>
+      <c r="AA31" s="4">
+        <f>IF(OR(LOWER(TRIM(A31))="",LOWER(TRIM(A31))="nan",LOWER(TRIM(A31))="none",LOWER(TRIM(A31))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A31))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <v/>
+      </c>
+      <c r="AB31" s="4">
+        <f>IF(AA31="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA31,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
       <c r="AC31" s="4">
-        <f>IF(OR(LOWER(TRIM(A31))="",LOWER(TRIM(A31))="nan",LOWER(TRIM(A31))="none",LOWER(TRIM(A31))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A31))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AB31="",AB31="_"),"",IF(LEFT(AB31,1)="_",IF(RIGHT(AB31,1)="_",MID(AB31,2,LEN(AB31)-2),RIGHT(AB31,LEN(AB31)-1)),IF(RIGHT(AB31,1)="_",LEFT(AB31,LEN(AB31)-1),AB31)))</f>
         <v/>
       </c>
       <c r="AD31" s="4">
-        <f>IF(AC31="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC31,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(O31))="",LOWER(TRIM(O31))="nan",LOWER(TRIM(O31))="none",LOWER(TRIM(O31))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O31))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AE31" s="4">
-        <f>IF(OR(AD31="",AD31="_"),"",IF(LEFT(AD31,1)="_",IF(RIGHT(AD31,1)="_",MID(AD31,2,LEN(AD31)-2),RIGHT(AD31,LEN(AD31)-1)),IF(RIGHT(AD31,1)="_",LEFT(AD31,LEN(AD31)-1),AD31)))</f>
+        <f>IF(AD31="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD31,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AF31" s="4">
-        <f>IF(OR(LOWER(TRIM(O31))="",LOWER(TRIM(O31))="nan",LOWER(TRIM(O31))="none",LOWER(TRIM(O31))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O31))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
+        <f>IF(OR(AE31="",AE31="_"),"",IF(LEFT(AE31,1)="_",IF(RIGHT(AE31,1)="_",MID(AE31,2,LEN(AE31)-2),RIGHT(AE31,LEN(AE31)-1)),IF(RIGHT(AE31,1)="_",LEFT(AE31,LEN(AE31)-1),AE31)))</f>
         <v/>
       </c>
       <c r="AG31" s="4">
-        <f>IF(AF31="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF31,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <f>IF(OR(LOWER(TRIM(P31))="",LOWER(TRIM(P31))="nan",LOWER(TRIM(P31))="none",LOWER(TRIM(P31))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P31))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
       <c r="AH31" s="4">
-        <f>IF(OR(AG31="",AG31="_"),"",IF(LEFT(AG31,1)="_",IF(RIGHT(AG31,1)="_",MID(AG31,2,LEN(AG31)-2),RIGHT(AG31,LEN(AG31)-1)),IF(RIGHT(AG31,1)="_",LEFT(AG31,LEN(AG31)-1),AG31)))</f>
+        <f>IF(AG31="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG31,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
         <v/>
       </c>
       <c r="AI31" s="4">
-        <f>IF(OR(LOWER(TRIM(P31))="",LOWER(TRIM(P31))="nan",LOWER(TRIM(P31))="none",LOWER(TRIM(P31))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P31))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AJ31" s="4">
-        <f>IF(AI31="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI31,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AK31" s="4">
-        <f>IF(OR(AJ31="",AJ31="_"),"",IF(LEFT(AJ31,1)="_",IF(RIGHT(AJ31,1)="_",MID(AJ31,2,LEN(AJ31)-2),RIGHT(AJ31,LEN(AJ31)-1)),IF(RIGHT(AJ31,1)="_",LEFT(AJ31,LEN(AJ31)-1),AJ31)))</f>
-        <v/>
-      </c>
-      <c r="AL31" s="4">
-        <f>IF(OR(LOWER(TRIM(Q31))="",LOWER(TRIM(Q31))="nan",LOWER(TRIM(Q31))="none",LOWER(TRIM(Q31))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(Q31))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AM31" s="4">
-        <f>IF(AL31="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AL31,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AN31" s="4">
-        <f>IF(OR(AM31="",AM31="_"),"",IF(LEFT(AM31,1)="_",IF(RIGHT(AM31,1)="_",MID(AM31,2,LEN(AM31)-2),RIGHT(AM31,LEN(AM31)-1)),IF(RIGHT(AM31,1)="_",LEFT(AM31,LEN(AM31)-1),AM31)))</f>
-        <v/>
-      </c>
-      <c r="AO31" s="4">
-        <f>IF(OR(LOWER(TRIM(R31))="",LOWER(TRIM(R31))="nan",LOWER(TRIM(R31))="none",LOWER(TRIM(R31))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(R31))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
-        <v/>
-      </c>
-      <c r="AP31" s="4">
-        <f>IF(AO31="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AO31,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AQ31" s="4">
-        <f>IF(OR(AP31="",AP31="_"),"",IF(LEFT(AP31,1)="_",IF(RIGHT(AP31,1)="_",MID(AP31,2,LEN(AP31)-2),RIGHT(AP31,LEN(AP31)-1)),IF(RIGHT(AP31,1)="_",LEFT(AP31,LEN(AP31)-1),AP31)))</f>
+        <f>IF(OR(AH31="",AH31="_"),"",IF(LEFT(AH31,1)="_",IF(RIGHT(AH31,1)="_",MID(AH31,2,LEN(AH31)-2),RIGHT(AH31,LEN(AH31)-1)),IF(RIGHT(AH31,1)="_",LEFT(AH31,LEN(AH31)-1),AH31)))</f>
         <v/>
       </c>
     </row>
@@ -3838,32 +3107,29 @@
       <formula>N8="Ready"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="9">
+  <dataValidations count="8">
     <dataValidation sqref="C8:C31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="activity_ownership" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="activity_ownership" prompt="Select an approved value." type="list">
-      <formula1>"earned,owned,paid,external_event"</formula1>
+      <formula1>"paid,owned,earned,external_event"</formula1>
     </dataValidation>
     <dataValidation sqref="D8:D31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="intended_model_role" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="intended_model_role" prompt="Select an approved value." type="list">
-      <formula1>"event,demand_capture,intervention,mediator,control"</formula1>
+      <formula1>"mediator,event,demand_capture,control,intervention"</formula1>
     </dataValidation>
     <dataValidation sqref="G8:G31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="economic_treatment" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="economic_treatment" prompt="Select an approved value." type="list">
-      <formula1>"not_applicable,campaign_cost,paid_media_cost,response_only,fully_loaded_cost"</formula1>
+      <formula1>"paid_media_cost,fully_loaded_cost,not_applicable,response_only,campaign_cost"</formula1>
     </dataValidation>
     <dataValidation sqref="H8:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="planning_eligibility" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="planning_eligibility" prompt="Select an approved value." type="list">
-      <formula1>"excluded,scenario_only,optimisable,fixed"</formula1>
+      <formula1>"optimisable,excluded,fixed,scenario_only"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q8:Q31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="search_platform" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="search_platform" prompt="Select an approved value." type="list">
-      <formula1>"google,bing"</formula1>
+    <dataValidation sqref="R8:R31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="funnel_stage" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="funnel_stage" prompt="Select an approved value." type="list">
+      <formula1>"brand_upper,mid_funnel,performance_lower,cross_funnel,not_applicable,unclassified"</formula1>
     </dataValidation>
-    <dataValidation sqref="R8:R31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="search_intent_group_id" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="search_intent_group_id" prompt="Select an approved value." type="list">
-      <formula1>"brand_search,non_brand_search"</formula1>
-    </dataValidation>
-    <dataValidation sqref="T8:T31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="funnel_stage" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="funnel_stage" prompt="Select an approved value." type="list">
-      <formula1>"brand_upper,mid_funnel,performance_lower,cross_funnel,not_applicable,unclassified"</formula1>
+    <dataValidation sqref="O8:O31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="platform" prompt="Choose a suggestion, or type your own text -- this field is not a closed list in the app." type="list">
+      <formula1>"Google,Bing"</formula1>
     </dataValidation>
     <dataValidation sqref="P8:P31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="campaign_type" prompt="Choose a suggestion, or type your own text -- this field is not a closed list in the app." type="list">
       <formula1>"Brand,Non-Brand"</formula1>
     </dataValidation>
-    <dataValidation sqref="U8:U31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="marketing_objective" prompt="Choose a suggestion, or type your own text -- this field is not a closed list in the app." type="list">
+    <dataValidation sqref="S8:S31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="marketing_objective" prompt="Choose a suggestion, or type your own text -- this field is not a closed list in the app." type="list">
       <formula1>"brand awareness,consideration,acquisition/performance,retention/lifecycle,promotion,winback,service/transactional,other"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4048,7 +3314,7 @@
         <v/>
       </c>
       <c r="C2">
-        <f>'BUILDER'!S8</f>
+        <f>'BUILDER'!Q8</f>
         <v/>
       </c>
       <c r="D2">
@@ -4064,19 +3330,19 @@
         <v/>
       </c>
       <c r="G2">
+        <f>IF(TRIM('BUILDER'!S8)&lt;&gt;"",'BUILDER'!S8,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>IF(TRIM('BUILDER'!R8)&lt;&gt;"",'BUILDER'!R8,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>IF(TRIM('BUILDER'!T8)&lt;&gt;"",'BUILDER'!T8,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J2">
         <f>IF(TRIM('BUILDER'!U8)&lt;&gt;"",'BUILDER'!U8,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H2">
-        <f>IF(TRIM('BUILDER'!T8)&lt;&gt;"",'BUILDER'!T8,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I2">
-        <f>IF(TRIM('BUILDER'!V8)&lt;&gt;"",'BUILDER'!V8,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J2">
-        <f>IF(TRIM('BUILDER'!W8)&lt;&gt;"",'BUILDER'!W8,"not specified")</f>
         <v/>
       </c>
       <c r="K2">
@@ -4113,15 +3379,15 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2">
+        <f>'BUILDER'!V8</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>'BUILDER'!W8</f>
+        <v/>
+      </c>
+      <c r="Y2">
         <f>'BUILDER'!X8</f>
-        <v/>
-      </c>
-      <c r="X2">
-        <f>'BUILDER'!Y8</f>
-        <v/>
-      </c>
-      <c r="Y2">
-        <f>'BUILDER'!Z8</f>
         <v/>
       </c>
     </row>
@@ -4135,7 +3401,7 @@
         <v/>
       </c>
       <c r="C3">
-        <f>'BUILDER'!S9</f>
+        <f>'BUILDER'!Q9</f>
         <v/>
       </c>
       <c r="D3">
@@ -4151,19 +3417,19 @@
         <v/>
       </c>
       <c r="G3">
+        <f>IF(TRIM('BUILDER'!S9)&lt;&gt;"",'BUILDER'!S9,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>IF(TRIM('BUILDER'!R9)&lt;&gt;"",'BUILDER'!R9,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(TRIM('BUILDER'!T9)&lt;&gt;"",'BUILDER'!T9,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J3">
         <f>IF(TRIM('BUILDER'!U9)&lt;&gt;"",'BUILDER'!U9,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H3">
-        <f>IF(TRIM('BUILDER'!T9)&lt;&gt;"",'BUILDER'!T9,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I3">
-        <f>IF(TRIM('BUILDER'!V9)&lt;&gt;"",'BUILDER'!V9,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J3">
-        <f>IF(TRIM('BUILDER'!W9)&lt;&gt;"",'BUILDER'!W9,"not specified")</f>
         <v/>
       </c>
       <c r="K3">
@@ -4200,15 +3466,15 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3">
+        <f>'BUILDER'!V9</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>'BUILDER'!W9</f>
+        <v/>
+      </c>
+      <c r="Y3">
         <f>'BUILDER'!X9</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>'BUILDER'!Y9</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>'BUILDER'!Z9</f>
         <v/>
       </c>
     </row>
@@ -4222,7 +3488,7 @@
         <v/>
       </c>
       <c r="C4">
-        <f>'BUILDER'!S10</f>
+        <f>'BUILDER'!Q10</f>
         <v/>
       </c>
       <c r="D4">
@@ -4238,19 +3504,19 @@
         <v/>
       </c>
       <c r="G4">
+        <f>IF(TRIM('BUILDER'!S10)&lt;&gt;"",'BUILDER'!S10,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>IF(TRIM('BUILDER'!R10)&lt;&gt;"",'BUILDER'!R10,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(TRIM('BUILDER'!T10)&lt;&gt;"",'BUILDER'!T10,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J4">
         <f>IF(TRIM('BUILDER'!U10)&lt;&gt;"",'BUILDER'!U10,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H4">
-        <f>IF(TRIM('BUILDER'!T10)&lt;&gt;"",'BUILDER'!T10,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I4">
-        <f>IF(TRIM('BUILDER'!V10)&lt;&gt;"",'BUILDER'!V10,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J4">
-        <f>IF(TRIM('BUILDER'!W10)&lt;&gt;"",'BUILDER'!W10,"not specified")</f>
         <v/>
       </c>
       <c r="K4">
@@ -4287,15 +3553,15 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4">
+        <f>'BUILDER'!V10</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>'BUILDER'!W10</f>
+        <v/>
+      </c>
+      <c r="Y4">
         <f>'BUILDER'!X10</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>'BUILDER'!Y10</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>'BUILDER'!Z10</f>
         <v/>
       </c>
     </row>
@@ -4309,7 +3575,7 @@
         <v/>
       </c>
       <c r="C5">
-        <f>'BUILDER'!S11</f>
+        <f>'BUILDER'!Q11</f>
         <v/>
       </c>
       <c r="D5">
@@ -4325,19 +3591,19 @@
         <v/>
       </c>
       <c r="G5">
+        <f>IF(TRIM('BUILDER'!S11)&lt;&gt;"",'BUILDER'!S11,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>IF(TRIM('BUILDER'!R11)&lt;&gt;"",'BUILDER'!R11,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(TRIM('BUILDER'!T11)&lt;&gt;"",'BUILDER'!T11,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J5">
         <f>IF(TRIM('BUILDER'!U11)&lt;&gt;"",'BUILDER'!U11,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H5">
-        <f>IF(TRIM('BUILDER'!T11)&lt;&gt;"",'BUILDER'!T11,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I5">
-        <f>IF(TRIM('BUILDER'!V11)&lt;&gt;"",'BUILDER'!V11,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J5">
-        <f>IF(TRIM('BUILDER'!W11)&lt;&gt;"",'BUILDER'!W11,"not specified")</f>
         <v/>
       </c>
       <c r="K5">
@@ -4374,15 +3640,15 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5">
+        <f>'BUILDER'!V11</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>'BUILDER'!W11</f>
+        <v/>
+      </c>
+      <c r="Y5">
         <f>'BUILDER'!X11</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>'BUILDER'!Y11</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>'BUILDER'!Z11</f>
         <v/>
       </c>
     </row>
@@ -4396,7 +3662,7 @@
         <v/>
       </c>
       <c r="C6">
-        <f>'BUILDER'!S12</f>
+        <f>'BUILDER'!Q12</f>
         <v/>
       </c>
       <c r="D6">
@@ -4412,19 +3678,19 @@
         <v/>
       </c>
       <c r="G6">
+        <f>IF(TRIM('BUILDER'!S12)&lt;&gt;"",'BUILDER'!S12,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>IF(TRIM('BUILDER'!R12)&lt;&gt;"",'BUILDER'!R12,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(TRIM('BUILDER'!T12)&lt;&gt;"",'BUILDER'!T12,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J6">
         <f>IF(TRIM('BUILDER'!U12)&lt;&gt;"",'BUILDER'!U12,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H6">
-        <f>IF(TRIM('BUILDER'!T12)&lt;&gt;"",'BUILDER'!T12,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I6">
-        <f>IF(TRIM('BUILDER'!V12)&lt;&gt;"",'BUILDER'!V12,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J6">
-        <f>IF(TRIM('BUILDER'!W12)&lt;&gt;"",'BUILDER'!W12,"not specified")</f>
         <v/>
       </c>
       <c r="K6">
@@ -4461,15 +3727,15 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6">
+        <f>'BUILDER'!V12</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>'BUILDER'!W12</f>
+        <v/>
+      </c>
+      <c r="Y6">
         <f>'BUILDER'!X12</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>'BUILDER'!Y12</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>'BUILDER'!Z12</f>
         <v/>
       </c>
     </row>
@@ -4483,7 +3749,7 @@
         <v/>
       </c>
       <c r="C7">
-        <f>'BUILDER'!S13</f>
+        <f>'BUILDER'!Q13</f>
         <v/>
       </c>
       <c r="D7">
@@ -4499,19 +3765,19 @@
         <v/>
       </c>
       <c r="G7">
+        <f>IF(TRIM('BUILDER'!S13)&lt;&gt;"",'BUILDER'!S13,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>IF(TRIM('BUILDER'!R13)&lt;&gt;"",'BUILDER'!R13,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(TRIM('BUILDER'!T13)&lt;&gt;"",'BUILDER'!T13,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J7">
         <f>IF(TRIM('BUILDER'!U13)&lt;&gt;"",'BUILDER'!U13,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H7">
-        <f>IF(TRIM('BUILDER'!T13)&lt;&gt;"",'BUILDER'!T13,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I7">
-        <f>IF(TRIM('BUILDER'!V13)&lt;&gt;"",'BUILDER'!V13,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J7">
-        <f>IF(TRIM('BUILDER'!W13)&lt;&gt;"",'BUILDER'!W13,"not specified")</f>
         <v/>
       </c>
       <c r="K7">
@@ -4548,15 +3814,15 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7">
+        <f>'BUILDER'!V13</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>'BUILDER'!W13</f>
+        <v/>
+      </c>
+      <c r="Y7">
         <f>'BUILDER'!X13</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>'BUILDER'!Y13</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>'BUILDER'!Z13</f>
         <v/>
       </c>
     </row>
@@ -4570,7 +3836,7 @@
         <v/>
       </c>
       <c r="C8">
-        <f>'BUILDER'!S14</f>
+        <f>'BUILDER'!Q14</f>
         <v/>
       </c>
       <c r="D8">
@@ -4586,19 +3852,19 @@
         <v/>
       </c>
       <c r="G8">
+        <f>IF(TRIM('BUILDER'!S14)&lt;&gt;"",'BUILDER'!S14,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IF(TRIM('BUILDER'!R14)&lt;&gt;"",'BUILDER'!R14,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(TRIM('BUILDER'!T14)&lt;&gt;"",'BUILDER'!T14,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J8">
         <f>IF(TRIM('BUILDER'!U14)&lt;&gt;"",'BUILDER'!U14,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H8">
-        <f>IF(TRIM('BUILDER'!T14)&lt;&gt;"",'BUILDER'!T14,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I8">
-        <f>IF(TRIM('BUILDER'!V14)&lt;&gt;"",'BUILDER'!V14,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J8">
-        <f>IF(TRIM('BUILDER'!W14)&lt;&gt;"",'BUILDER'!W14,"not specified")</f>
         <v/>
       </c>
       <c r="K8">
@@ -4635,15 +3901,15 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8">
+        <f>'BUILDER'!V14</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>'BUILDER'!W14</f>
+        <v/>
+      </c>
+      <c r="Y8">
         <f>'BUILDER'!X14</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>'BUILDER'!Y14</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>'BUILDER'!Z14</f>
         <v/>
       </c>
     </row>
@@ -4657,7 +3923,7 @@
         <v/>
       </c>
       <c r="C9">
-        <f>'BUILDER'!S15</f>
+        <f>'BUILDER'!Q15</f>
         <v/>
       </c>
       <c r="D9">
@@ -4673,19 +3939,19 @@
         <v/>
       </c>
       <c r="G9">
+        <f>IF(TRIM('BUILDER'!S15)&lt;&gt;"",'BUILDER'!S15,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>IF(TRIM('BUILDER'!R15)&lt;&gt;"",'BUILDER'!R15,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(TRIM('BUILDER'!T15)&lt;&gt;"",'BUILDER'!T15,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J9">
         <f>IF(TRIM('BUILDER'!U15)&lt;&gt;"",'BUILDER'!U15,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H9">
-        <f>IF(TRIM('BUILDER'!T15)&lt;&gt;"",'BUILDER'!T15,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I9">
-        <f>IF(TRIM('BUILDER'!V15)&lt;&gt;"",'BUILDER'!V15,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J9">
-        <f>IF(TRIM('BUILDER'!W15)&lt;&gt;"",'BUILDER'!W15,"not specified")</f>
         <v/>
       </c>
       <c r="K9">
@@ -4722,15 +3988,15 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9">
+        <f>'BUILDER'!V15</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>'BUILDER'!W15</f>
+        <v/>
+      </c>
+      <c r="Y9">
         <f>'BUILDER'!X15</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>'BUILDER'!Y15</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>'BUILDER'!Z15</f>
         <v/>
       </c>
     </row>
@@ -4744,7 +4010,7 @@
         <v/>
       </c>
       <c r="C10">
-        <f>'BUILDER'!S16</f>
+        <f>'BUILDER'!Q16</f>
         <v/>
       </c>
       <c r="D10">
@@ -4760,19 +4026,19 @@
         <v/>
       </c>
       <c r="G10">
+        <f>IF(TRIM('BUILDER'!S16)&lt;&gt;"",'BUILDER'!S16,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>IF(TRIM('BUILDER'!R16)&lt;&gt;"",'BUILDER'!R16,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(TRIM('BUILDER'!T16)&lt;&gt;"",'BUILDER'!T16,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J10">
         <f>IF(TRIM('BUILDER'!U16)&lt;&gt;"",'BUILDER'!U16,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>IF(TRIM('BUILDER'!T16)&lt;&gt;"",'BUILDER'!T16,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I10">
-        <f>IF(TRIM('BUILDER'!V16)&lt;&gt;"",'BUILDER'!V16,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J10">
-        <f>IF(TRIM('BUILDER'!W16)&lt;&gt;"",'BUILDER'!W16,"not specified")</f>
         <v/>
       </c>
       <c r="K10">
@@ -4809,15 +4075,15 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10">
+        <f>'BUILDER'!V16</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>'BUILDER'!W16</f>
+        <v/>
+      </c>
+      <c r="Y10">
         <f>'BUILDER'!X16</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>'BUILDER'!Y16</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>'BUILDER'!Z16</f>
         <v/>
       </c>
     </row>
@@ -4831,7 +4097,7 @@
         <v/>
       </c>
       <c r="C11">
-        <f>'BUILDER'!S17</f>
+        <f>'BUILDER'!Q17</f>
         <v/>
       </c>
       <c r="D11">
@@ -4847,19 +4113,19 @@
         <v/>
       </c>
       <c r="G11">
+        <f>IF(TRIM('BUILDER'!S17)&lt;&gt;"",'BUILDER'!S17,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>IF(TRIM('BUILDER'!R17)&lt;&gt;"",'BUILDER'!R17,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(TRIM('BUILDER'!T17)&lt;&gt;"",'BUILDER'!T17,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J11">
         <f>IF(TRIM('BUILDER'!U17)&lt;&gt;"",'BUILDER'!U17,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H11">
-        <f>IF(TRIM('BUILDER'!T17)&lt;&gt;"",'BUILDER'!T17,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I11">
-        <f>IF(TRIM('BUILDER'!V17)&lt;&gt;"",'BUILDER'!V17,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J11">
-        <f>IF(TRIM('BUILDER'!W17)&lt;&gt;"",'BUILDER'!W17,"not specified")</f>
         <v/>
       </c>
       <c r="K11">
@@ -4896,15 +4162,15 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11">
+        <f>'BUILDER'!V17</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>'BUILDER'!W17</f>
+        <v/>
+      </c>
+      <c r="Y11">
         <f>'BUILDER'!X17</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>'BUILDER'!Y17</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>'BUILDER'!Z17</f>
         <v/>
       </c>
     </row>
@@ -4918,7 +4184,7 @@
         <v/>
       </c>
       <c r="C12">
-        <f>'BUILDER'!S18</f>
+        <f>'BUILDER'!Q18</f>
         <v/>
       </c>
       <c r="D12">
@@ -4934,19 +4200,19 @@
         <v/>
       </c>
       <c r="G12">
+        <f>IF(TRIM('BUILDER'!S18)&lt;&gt;"",'BUILDER'!S18,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>IF(TRIM('BUILDER'!R18)&lt;&gt;"",'BUILDER'!R18,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(TRIM('BUILDER'!T18)&lt;&gt;"",'BUILDER'!T18,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J12">
         <f>IF(TRIM('BUILDER'!U18)&lt;&gt;"",'BUILDER'!U18,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>IF(TRIM('BUILDER'!T18)&lt;&gt;"",'BUILDER'!T18,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I12">
-        <f>IF(TRIM('BUILDER'!V18)&lt;&gt;"",'BUILDER'!V18,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J12">
-        <f>IF(TRIM('BUILDER'!W18)&lt;&gt;"",'BUILDER'!W18,"not specified")</f>
         <v/>
       </c>
       <c r="K12">
@@ -4983,15 +4249,15 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12">
+        <f>'BUILDER'!V18</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>'BUILDER'!W18</f>
+        <v/>
+      </c>
+      <c r="Y12">
         <f>'BUILDER'!X18</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>'BUILDER'!Y18</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>'BUILDER'!Z18</f>
         <v/>
       </c>
     </row>
@@ -5005,7 +4271,7 @@
         <v/>
       </c>
       <c r="C13">
-        <f>'BUILDER'!S19</f>
+        <f>'BUILDER'!Q19</f>
         <v/>
       </c>
       <c r="D13">
@@ -5021,19 +4287,19 @@
         <v/>
       </c>
       <c r="G13">
+        <f>IF(TRIM('BUILDER'!S19)&lt;&gt;"",'BUILDER'!S19,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>IF(TRIM('BUILDER'!R19)&lt;&gt;"",'BUILDER'!R19,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(TRIM('BUILDER'!T19)&lt;&gt;"",'BUILDER'!T19,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J13">
         <f>IF(TRIM('BUILDER'!U19)&lt;&gt;"",'BUILDER'!U19,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>IF(TRIM('BUILDER'!T19)&lt;&gt;"",'BUILDER'!T19,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I13">
-        <f>IF(TRIM('BUILDER'!V19)&lt;&gt;"",'BUILDER'!V19,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J13">
-        <f>IF(TRIM('BUILDER'!W19)&lt;&gt;"",'BUILDER'!W19,"not specified")</f>
         <v/>
       </c>
       <c r="K13">
@@ -5070,15 +4336,15 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13">
+        <f>'BUILDER'!V19</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>'BUILDER'!W19</f>
+        <v/>
+      </c>
+      <c r="Y13">
         <f>'BUILDER'!X19</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>'BUILDER'!Y19</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>'BUILDER'!Z19</f>
         <v/>
       </c>
     </row>
@@ -5092,7 +4358,7 @@
         <v/>
       </c>
       <c r="C14">
-        <f>'BUILDER'!S20</f>
+        <f>'BUILDER'!Q20</f>
         <v/>
       </c>
       <c r="D14">
@@ -5108,19 +4374,19 @@
         <v/>
       </c>
       <c r="G14">
+        <f>IF(TRIM('BUILDER'!S20)&lt;&gt;"",'BUILDER'!S20,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>IF(TRIM('BUILDER'!R20)&lt;&gt;"",'BUILDER'!R20,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(TRIM('BUILDER'!T20)&lt;&gt;"",'BUILDER'!T20,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J14">
         <f>IF(TRIM('BUILDER'!U20)&lt;&gt;"",'BUILDER'!U20,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>IF(TRIM('BUILDER'!T20)&lt;&gt;"",'BUILDER'!T20,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I14">
-        <f>IF(TRIM('BUILDER'!V20)&lt;&gt;"",'BUILDER'!V20,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J14">
-        <f>IF(TRIM('BUILDER'!W20)&lt;&gt;"",'BUILDER'!W20,"not specified")</f>
         <v/>
       </c>
       <c r="K14">
@@ -5157,15 +4423,15 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14">
+        <f>'BUILDER'!V20</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>'BUILDER'!W20</f>
+        <v/>
+      </c>
+      <c r="Y14">
         <f>'BUILDER'!X20</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>'BUILDER'!Y20</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>'BUILDER'!Z20</f>
         <v/>
       </c>
     </row>
@@ -5179,7 +4445,7 @@
         <v/>
       </c>
       <c r="C15">
-        <f>'BUILDER'!S21</f>
+        <f>'BUILDER'!Q21</f>
         <v/>
       </c>
       <c r="D15">
@@ -5195,19 +4461,19 @@
         <v/>
       </c>
       <c r="G15">
+        <f>IF(TRIM('BUILDER'!S21)&lt;&gt;"",'BUILDER'!S21,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>IF(TRIM('BUILDER'!R21)&lt;&gt;"",'BUILDER'!R21,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(TRIM('BUILDER'!T21)&lt;&gt;"",'BUILDER'!T21,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J15">
         <f>IF(TRIM('BUILDER'!U21)&lt;&gt;"",'BUILDER'!U21,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H15">
-        <f>IF(TRIM('BUILDER'!T21)&lt;&gt;"",'BUILDER'!T21,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I15">
-        <f>IF(TRIM('BUILDER'!V21)&lt;&gt;"",'BUILDER'!V21,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J15">
-        <f>IF(TRIM('BUILDER'!W21)&lt;&gt;"",'BUILDER'!W21,"not specified")</f>
         <v/>
       </c>
       <c r="K15">
@@ -5244,15 +4510,15 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15">
+        <f>'BUILDER'!V21</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>'BUILDER'!W21</f>
+        <v/>
+      </c>
+      <c r="Y15">
         <f>'BUILDER'!X21</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>'BUILDER'!Y21</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>'BUILDER'!Z21</f>
         <v/>
       </c>
     </row>
@@ -5266,7 +4532,7 @@
         <v/>
       </c>
       <c r="C16">
-        <f>'BUILDER'!S22</f>
+        <f>'BUILDER'!Q22</f>
         <v/>
       </c>
       <c r="D16">
@@ -5282,19 +4548,19 @@
         <v/>
       </c>
       <c r="G16">
+        <f>IF(TRIM('BUILDER'!S22)&lt;&gt;"",'BUILDER'!S22,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H16">
+        <f>IF(TRIM('BUILDER'!R22)&lt;&gt;"",'BUILDER'!R22,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(TRIM('BUILDER'!T22)&lt;&gt;"",'BUILDER'!T22,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J16">
         <f>IF(TRIM('BUILDER'!U22)&lt;&gt;"",'BUILDER'!U22,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H16">
-        <f>IF(TRIM('BUILDER'!T22)&lt;&gt;"",'BUILDER'!T22,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I16">
-        <f>IF(TRIM('BUILDER'!V22)&lt;&gt;"",'BUILDER'!V22,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J16">
-        <f>IF(TRIM('BUILDER'!W22)&lt;&gt;"",'BUILDER'!W22,"not specified")</f>
         <v/>
       </c>
       <c r="K16">
@@ -5331,15 +4597,15 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16">
+        <f>'BUILDER'!V22</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>'BUILDER'!W22</f>
+        <v/>
+      </c>
+      <c r="Y16">
         <f>'BUILDER'!X22</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>'BUILDER'!Y22</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>'BUILDER'!Z22</f>
         <v/>
       </c>
     </row>
@@ -5353,7 +4619,7 @@
         <v/>
       </c>
       <c r="C17">
-        <f>'BUILDER'!S23</f>
+        <f>'BUILDER'!Q23</f>
         <v/>
       </c>
       <c r="D17">
@@ -5369,19 +4635,19 @@
         <v/>
       </c>
       <c r="G17">
+        <f>IF(TRIM('BUILDER'!S23)&lt;&gt;"",'BUILDER'!S23,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H17">
+        <f>IF(TRIM('BUILDER'!R23)&lt;&gt;"",'BUILDER'!R23,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(TRIM('BUILDER'!T23)&lt;&gt;"",'BUILDER'!T23,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J17">
         <f>IF(TRIM('BUILDER'!U23)&lt;&gt;"",'BUILDER'!U23,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H17">
-        <f>IF(TRIM('BUILDER'!T23)&lt;&gt;"",'BUILDER'!T23,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I17">
-        <f>IF(TRIM('BUILDER'!V23)&lt;&gt;"",'BUILDER'!V23,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J17">
-        <f>IF(TRIM('BUILDER'!W23)&lt;&gt;"",'BUILDER'!W23,"not specified")</f>
         <v/>
       </c>
       <c r="K17">
@@ -5418,15 +4684,15 @@
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17">
+        <f>'BUILDER'!V23</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>'BUILDER'!W23</f>
+        <v/>
+      </c>
+      <c r="Y17">
         <f>'BUILDER'!X23</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>'BUILDER'!Y23</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>'BUILDER'!Z23</f>
         <v/>
       </c>
     </row>
@@ -5440,7 +4706,7 @@
         <v/>
       </c>
       <c r="C18">
-        <f>'BUILDER'!S24</f>
+        <f>'BUILDER'!Q24</f>
         <v/>
       </c>
       <c r="D18">
@@ -5456,19 +4722,19 @@
         <v/>
       </c>
       <c r="G18">
+        <f>IF(TRIM('BUILDER'!S24)&lt;&gt;"",'BUILDER'!S24,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>IF(TRIM('BUILDER'!R24)&lt;&gt;"",'BUILDER'!R24,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(TRIM('BUILDER'!T24)&lt;&gt;"",'BUILDER'!T24,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J18">
         <f>IF(TRIM('BUILDER'!U24)&lt;&gt;"",'BUILDER'!U24,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H18">
-        <f>IF(TRIM('BUILDER'!T24)&lt;&gt;"",'BUILDER'!T24,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I18">
-        <f>IF(TRIM('BUILDER'!V24)&lt;&gt;"",'BUILDER'!V24,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J18">
-        <f>IF(TRIM('BUILDER'!W24)&lt;&gt;"",'BUILDER'!W24,"not specified")</f>
         <v/>
       </c>
       <c r="K18">
@@ -5505,15 +4771,15 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18">
+        <f>'BUILDER'!V24</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>'BUILDER'!W24</f>
+        <v/>
+      </c>
+      <c r="Y18">
         <f>'BUILDER'!X24</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>'BUILDER'!Y24</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>'BUILDER'!Z24</f>
         <v/>
       </c>
     </row>
@@ -5527,7 +4793,7 @@
         <v/>
       </c>
       <c r="C19">
-        <f>'BUILDER'!S25</f>
+        <f>'BUILDER'!Q25</f>
         <v/>
       </c>
       <c r="D19">
@@ -5543,19 +4809,19 @@
         <v/>
       </c>
       <c r="G19">
+        <f>IF(TRIM('BUILDER'!S25)&lt;&gt;"",'BUILDER'!S25,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>IF(TRIM('BUILDER'!R25)&lt;&gt;"",'BUILDER'!R25,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(TRIM('BUILDER'!T25)&lt;&gt;"",'BUILDER'!T25,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J19">
         <f>IF(TRIM('BUILDER'!U25)&lt;&gt;"",'BUILDER'!U25,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H19">
-        <f>IF(TRIM('BUILDER'!T25)&lt;&gt;"",'BUILDER'!T25,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I19">
-        <f>IF(TRIM('BUILDER'!V25)&lt;&gt;"",'BUILDER'!V25,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J19">
-        <f>IF(TRIM('BUILDER'!W25)&lt;&gt;"",'BUILDER'!W25,"not specified")</f>
         <v/>
       </c>
       <c r="K19">
@@ -5592,15 +4858,15 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19">
+        <f>'BUILDER'!V25</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>'BUILDER'!W25</f>
+        <v/>
+      </c>
+      <c r="Y19">
         <f>'BUILDER'!X25</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>'BUILDER'!Y25</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>'BUILDER'!Z25</f>
         <v/>
       </c>
     </row>
@@ -5614,7 +4880,7 @@
         <v/>
       </c>
       <c r="C20">
-        <f>'BUILDER'!S26</f>
+        <f>'BUILDER'!Q26</f>
         <v/>
       </c>
       <c r="D20">
@@ -5630,19 +4896,19 @@
         <v/>
       </c>
       <c r="G20">
+        <f>IF(TRIM('BUILDER'!S26)&lt;&gt;"",'BUILDER'!S26,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>IF(TRIM('BUILDER'!R26)&lt;&gt;"",'BUILDER'!R26,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(TRIM('BUILDER'!T26)&lt;&gt;"",'BUILDER'!T26,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J20">
         <f>IF(TRIM('BUILDER'!U26)&lt;&gt;"",'BUILDER'!U26,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H20">
-        <f>IF(TRIM('BUILDER'!T26)&lt;&gt;"",'BUILDER'!T26,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I20">
-        <f>IF(TRIM('BUILDER'!V26)&lt;&gt;"",'BUILDER'!V26,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J20">
-        <f>IF(TRIM('BUILDER'!W26)&lt;&gt;"",'BUILDER'!W26,"not specified")</f>
         <v/>
       </c>
       <c r="K20">
@@ -5679,15 +4945,15 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20">
+        <f>'BUILDER'!V26</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>'BUILDER'!W26</f>
+        <v/>
+      </c>
+      <c r="Y20">
         <f>'BUILDER'!X26</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>'BUILDER'!Y26</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>'BUILDER'!Z26</f>
         <v/>
       </c>
     </row>
@@ -5701,7 +4967,7 @@
         <v/>
       </c>
       <c r="C21">
-        <f>'BUILDER'!S27</f>
+        <f>'BUILDER'!Q27</f>
         <v/>
       </c>
       <c r="D21">
@@ -5717,19 +4983,19 @@
         <v/>
       </c>
       <c r="G21">
+        <f>IF(TRIM('BUILDER'!S27)&lt;&gt;"",'BUILDER'!S27,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H21">
+        <f>IF(TRIM('BUILDER'!R27)&lt;&gt;"",'BUILDER'!R27,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(TRIM('BUILDER'!T27)&lt;&gt;"",'BUILDER'!T27,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J21">
         <f>IF(TRIM('BUILDER'!U27)&lt;&gt;"",'BUILDER'!U27,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H21">
-        <f>IF(TRIM('BUILDER'!T27)&lt;&gt;"",'BUILDER'!T27,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I21">
-        <f>IF(TRIM('BUILDER'!V27)&lt;&gt;"",'BUILDER'!V27,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J21">
-        <f>IF(TRIM('BUILDER'!W27)&lt;&gt;"",'BUILDER'!W27,"not specified")</f>
         <v/>
       </c>
       <c r="K21">
@@ -5766,15 +5032,15 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21">
+        <f>'BUILDER'!V27</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>'BUILDER'!W27</f>
+        <v/>
+      </c>
+      <c r="Y21">
         <f>'BUILDER'!X27</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>'BUILDER'!Y27</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>'BUILDER'!Z27</f>
         <v/>
       </c>
     </row>
@@ -5788,7 +5054,7 @@
         <v/>
       </c>
       <c r="C22">
-        <f>'BUILDER'!S28</f>
+        <f>'BUILDER'!Q28</f>
         <v/>
       </c>
       <c r="D22">
@@ -5804,19 +5070,19 @@
         <v/>
       </c>
       <c r="G22">
+        <f>IF(TRIM('BUILDER'!S28)&lt;&gt;"",'BUILDER'!S28,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H22">
+        <f>IF(TRIM('BUILDER'!R28)&lt;&gt;"",'BUILDER'!R28,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(TRIM('BUILDER'!T28)&lt;&gt;"",'BUILDER'!T28,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J22">
         <f>IF(TRIM('BUILDER'!U28)&lt;&gt;"",'BUILDER'!U28,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H22">
-        <f>IF(TRIM('BUILDER'!T28)&lt;&gt;"",'BUILDER'!T28,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I22">
-        <f>IF(TRIM('BUILDER'!V28)&lt;&gt;"",'BUILDER'!V28,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J22">
-        <f>IF(TRIM('BUILDER'!W28)&lt;&gt;"",'BUILDER'!W28,"not specified")</f>
         <v/>
       </c>
       <c r="K22">
@@ -5853,15 +5119,15 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22">
+        <f>'BUILDER'!V28</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>'BUILDER'!W28</f>
+        <v/>
+      </c>
+      <c r="Y22">
         <f>'BUILDER'!X28</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>'BUILDER'!Y28</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>'BUILDER'!Z28</f>
         <v/>
       </c>
     </row>
@@ -5875,7 +5141,7 @@
         <v/>
       </c>
       <c r="C23">
-        <f>'BUILDER'!S29</f>
+        <f>'BUILDER'!Q29</f>
         <v/>
       </c>
       <c r="D23">
@@ -5891,19 +5157,19 @@
         <v/>
       </c>
       <c r="G23">
+        <f>IF(TRIM('BUILDER'!S29)&lt;&gt;"",'BUILDER'!S29,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H23">
+        <f>IF(TRIM('BUILDER'!R29)&lt;&gt;"",'BUILDER'!R29,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(TRIM('BUILDER'!T29)&lt;&gt;"",'BUILDER'!T29,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J23">
         <f>IF(TRIM('BUILDER'!U29)&lt;&gt;"",'BUILDER'!U29,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H23">
-        <f>IF(TRIM('BUILDER'!T29)&lt;&gt;"",'BUILDER'!T29,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I23">
-        <f>IF(TRIM('BUILDER'!V29)&lt;&gt;"",'BUILDER'!V29,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J23">
-        <f>IF(TRIM('BUILDER'!W29)&lt;&gt;"",'BUILDER'!W29,"not specified")</f>
         <v/>
       </c>
       <c r="K23">
@@ -5940,15 +5206,15 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23">
+        <f>'BUILDER'!V29</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>'BUILDER'!W29</f>
+        <v/>
+      </c>
+      <c r="Y23">
         <f>'BUILDER'!X29</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>'BUILDER'!Y29</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>'BUILDER'!Z29</f>
         <v/>
       </c>
     </row>
@@ -5962,7 +5228,7 @@
         <v/>
       </c>
       <c r="C24">
-        <f>'BUILDER'!S30</f>
+        <f>'BUILDER'!Q30</f>
         <v/>
       </c>
       <c r="D24">
@@ -5978,19 +5244,19 @@
         <v/>
       </c>
       <c r="G24">
+        <f>IF(TRIM('BUILDER'!S30)&lt;&gt;"",'BUILDER'!S30,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>IF(TRIM('BUILDER'!R30)&lt;&gt;"",'BUILDER'!R30,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(TRIM('BUILDER'!T30)&lt;&gt;"",'BUILDER'!T30,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J24">
         <f>IF(TRIM('BUILDER'!U30)&lt;&gt;"",'BUILDER'!U30,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H24">
-        <f>IF(TRIM('BUILDER'!T30)&lt;&gt;"",'BUILDER'!T30,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I24">
-        <f>IF(TRIM('BUILDER'!V30)&lt;&gt;"",'BUILDER'!V30,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J24">
-        <f>IF(TRIM('BUILDER'!W30)&lt;&gt;"",'BUILDER'!W30,"not specified")</f>
         <v/>
       </c>
       <c r="K24">
@@ -6027,15 +5293,15 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24">
+        <f>'BUILDER'!V30</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>'BUILDER'!W30</f>
+        <v/>
+      </c>
+      <c r="Y24">
         <f>'BUILDER'!X30</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>'BUILDER'!Y30</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>'BUILDER'!Z30</f>
         <v/>
       </c>
     </row>
@@ -6049,7 +5315,7 @@
         <v/>
       </c>
       <c r="C25">
-        <f>'BUILDER'!S31</f>
+        <f>'BUILDER'!Q31</f>
         <v/>
       </c>
       <c r="D25">
@@ -6065,19 +5331,19 @@
         <v/>
       </c>
       <c r="G25">
+        <f>IF(TRIM('BUILDER'!S31)&lt;&gt;"",'BUILDER'!S31,"not specified")</f>
+        <v/>
+      </c>
+      <c r="H25">
+        <f>IF(TRIM('BUILDER'!R31)&lt;&gt;"",'BUILDER'!R31,"unclassified")</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(TRIM('BUILDER'!T31)&lt;&gt;"",'BUILDER'!T31,"not specified")</f>
+        <v/>
+      </c>
+      <c r="J25">
         <f>IF(TRIM('BUILDER'!U31)&lt;&gt;"",'BUILDER'!U31,"not specified")</f>
-        <v/>
-      </c>
-      <c r="H25">
-        <f>IF(TRIM('BUILDER'!T31)&lt;&gt;"",'BUILDER'!T31,"unclassified")</f>
-        <v/>
-      </c>
-      <c r="I25">
-        <f>IF(TRIM('BUILDER'!V31)&lt;&gt;"",'BUILDER'!V31,"not specified")</f>
-        <v/>
-      </c>
-      <c r="J25">
-        <f>IF(TRIM('BUILDER'!W31)&lt;&gt;"",'BUILDER'!W31,"not specified")</f>
         <v/>
       </c>
       <c r="K25">
@@ -6114,15 +5380,15 @@
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25">
+        <f>'BUILDER'!V31</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>'BUILDER'!W31</f>
+        <v/>
+      </c>
+      <c r="Y25">
         <f>'BUILDER'!X31</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>'BUILDER'!Y31</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>'BUILDER'!Z31</f>
         <v/>
       </c>
     </row>
@@ -6140,7 +5406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6179,7 +5445,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>earned</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -6223,7 +5489,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>earned</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -6267,7 +5533,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>mediator</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -6289,7 +5555,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>demand_capture</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -6311,7 +5577,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>intervention</t>
+          <t>demand_capture</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -6333,7 +5599,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>mediator</t>
+          <t>control</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -6355,7 +5621,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>intervention</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -6377,7 +5643,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>paid_media_cost</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -6399,7 +5665,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>campaign_cost</t>
+          <t>fully_loaded_cost</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -6421,7 +5687,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>paid_media_cost</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -6465,7 +5731,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>fully_loaded_cost</t>
+          <t>campaign_cost</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -6487,7 +5753,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>excluded</t>
+          <t>optimisable</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -6509,7 +5775,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>scenario_only</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -6531,7 +5797,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>optimisable</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -6553,7 +5819,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>scenario_only</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -6702,139 +5968,139 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>search_platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>Google / Bing</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Governed platform axis for Paid Search identity.</t>
+          <t>Suggested values only -- not a closed enum in the app.</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Only for Paid Search activities you want split by platform.</t>
+          <t>Free text is also accepted; use whatever platform actually applies, including non-Search channels like TV or a broadcaster name.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>search_platform</t>
+          <t>campaign_type</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>bing</t>
+          <t>Brand / Non-Brand</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Governed platform axis for Paid Search identity.</t>
+          <t>Suggested values only -- not a closed enum in the app.</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Only for Paid Search activities you want split by platform.</t>
+          <t>Free text is also accepted; the app never rejects an unrecognised value.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>search_intent_group_id</t>
+          <t>marketing_objective</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>brand_search</t>
+          <t>brand awareness, consideration, acquisition/performance, retention/lifecycle, promotion, winback, service/transactional, other</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Brand Search intent.</t>
+          <t>Suggested values only -- not a closed enum in the app.</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Only for Paid Search activities you want split by Brand/Non-Brand.</t>
+          <t>Free text is also accepted.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>search_intent_group_id</t>
+          <t>search_platform / search_intent_group_id</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>non_brand_search</t>
+          <t>Not offered by this builder</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Non-Brand Search intent.</t>
+          <t>Not activity_dictionary columns today -- the standard upload doesn't map them.</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Only for Paid Search activities you want split by Brand/Non-Brand.</t>
+          <t>Configured separately, after upload, in the governed Search-taxonomy admin mapping. Use platform and campaign_type above to keep your activity_id readable in the meantime.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>campaign_type</t>
+          <t>channel</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Brand / Non-Brand</t>
+          <t>Free text — no fixed list</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Suggested values only -- not a closed enum in the app.</t>
+          <t>Not a governed enum.</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Free text is also accepted; the app never rejects an unrecognised value.</t>
+          <t>Enter as plain text; there is no dropdown.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>marketing_objective</t>
+          <t>market</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>brand awareness, consideration, acquisition/performance, retention/lifecycle, promotion, winback, service/transactional, other</t>
+          <t>Free text — no fixed list</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Suggested values only -- not a closed enum in the app.</t>
+          <t>Not a governed enum.</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Free text is also accepted.</t>
+          <t>Enter as plain text; there is no dropdown.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>source</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -6856,7 +6122,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>market</t>
+          <t>model_input_measure</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -6878,7 +6144,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>product_advertised</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -6900,7 +6166,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>model_input_measure</t>
+          <t>message_type</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -6922,7 +6188,7 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>product_advertised</t>
+          <t>pooling_group_id</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -6944,7 +6210,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>message_type</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -6966,7 +6232,7 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>pooling_group_id</t>
+          <t>effective_from</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -6988,7 +6254,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>effective_to</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -7007,52 +6273,8 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>effective_from</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Free text — no fixed list</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Not a governed enum.</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Enter as plain text; there is no dropdown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>effective_to</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Free text — no fixed list</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Not a governed enum.</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Enter as plain text; there is no dropdown.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D41"/>
+  <autoFilter ref="A1:D39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/Ancestry_MMM_Activity_Dictionary_Builder.xlsx
+++ b/docs/Ancestry_MMM_Activity_Dictionary_Builder.xlsx
@@ -14,7 +14,7 @@
     <sheet name="EXAMPLES" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ALLOWED_VALUES'!$A$1:$D$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ALLOWED_VALUES'!$A$1:$D$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -202,9 +202,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ActivityCandidates" displayName="ActivityCandidates" ref="A7:X31" headerRowCount="1">
-  <autoFilter ref="A7:X31"/>
-  <tableColumns count="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ActivityCandidates" displayName="ActivityCandidates" ref="A7:Z31" headerRowCount="1">
+  <autoFilter ref="A7:Z31"/>
+  <tableColumns count="26">
     <tableColumn id="1" name="channel"/>
     <tableColumn id="2" name="market"/>
     <tableColumn id="3" name="activity_ownership"/>
@@ -221,23 +221,25 @@
     <tableColumn id="14" name="Row status"/>
     <tableColumn id="15" name="platform"/>
     <tableColumn id="16" name="campaign_type"/>
-    <tableColumn id="17" name="pooling_group_id"/>
-    <tableColumn id="18" name="funnel_stage"/>
-    <tableColumn id="19" name="marketing_objective"/>
-    <tableColumn id="20" name="product_advertised"/>
-    <tableColumn id="21" name="message_type"/>
-    <tableColumn id="22" name="currency"/>
-    <tableColumn id="23" name="effective_from"/>
-    <tableColumn id="24" name="effective_to"/>
+    <tableColumn id="17" name="search_intent_group_id"/>
+    <tableColumn id="18" name="search_platform"/>
+    <tableColumn id="19" name="pooling_group_id"/>
+    <tableColumn id="20" name="funnel_stage"/>
+    <tableColumn id="21" name="marketing_objective"/>
+    <tableColumn id="22" name="product_advertised"/>
+    <tableColumn id="23" name="message_type"/>
+    <tableColumn id="24" name="currency"/>
+    <tableColumn id="25" name="effective_from"/>
+    <tableColumn id="26" name="effective_to"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DictionaryOutput" displayName="DictionaryOutput" ref="A1:Y25" headerRowCount="1">
-  <autoFilter ref="A1:Y25"/>
-  <tableColumns count="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DictionaryOutput" displayName="DictionaryOutput" ref="A1:AA25" headerRowCount="1">
+  <autoFilter ref="A1:AA25"/>
+  <tableColumns count="27">
     <tableColumn id="1" name="activity_id"/>
     <tableColumn id="2" name="market"/>
     <tableColumn id="3" name="pooling_group_id"/>
@@ -263,6 +265,8 @@
     <tableColumn id="23" name="currency"/>
     <tableColumn id="24" name="effective_from"/>
     <tableColumn id="25" name="effective_to"/>
+    <tableColumn id="26" name="search_intent_group_id"/>
+    <tableColumn id="27" name="search_platform"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -557,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -678,7 +682,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Conditional (amber columns): platform, campaign_type -- fill these in when they help distinguish one activity from another (Google vs Bing, Brand vs Non-Brand); the upload does currently reject a truly empty cell, so a blank one defaults to not specified in DICTIONARY_OUTPUT.</t>
+          <t>Conditional (amber columns): platform, campaign_type, search_intent_group_id, search_platform -- fill these in when they help distinguish one activity from another (Google vs Bing, Brand vs Non-Brand); platform/campaign_type default to not specified when left blank, while search_intent_group_id/search_platform stay genuinely blank (unclassified) -- a non-Search activity, or a Search activity whose history only supports an aggregate Brand/Non-Brand view without a platform split, should leave them blank rather than guessing.</t>
         </is>
       </c>
     </row>
@@ -696,64 +700,57 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Also not asked at all: search_platform and search_intent_group_id. They are not activity_dictionary columns today -- activity_definitions_from_dictionary still doesn't map them from a standard workbook -- so this builder does not pretend they are ordinary fields. The governed Search-taxonomy mapping (Brand/Non-Brand, Google/Bing at the ActivityDefinition level) is configured separately, after upload, until that mapping gap is closed. Use platform and campaign_type above to keep your activity_id readable in the meantime.</t>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>How dropdowns work</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>How dropdowns work</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>activity_ownership, intended_model_role, economic_treatment, planning_eligibility, and funnel_stage are dropdowns built from the app's own governed lists. campaign_type and marketing_objective offer suggestions but also accept free text, matching how the app actually treats them. See the ALLOWED_VALUES sheet for the full, current set with plain-English explanations.</t>
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>How validation works</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>How validation works</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>The Row status column recalculates automatically as you type. It tells you in plain English whether a row is Ready, missing a required field, or a duplicate activity_id -- fix the thing it names, then check again.</t>
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Where the final dictionary output goes</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Where the final dictionary output goes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Select every data row of the DICTIONARY_OUTPUT sheet, copy, and Paste Special &gt; Values into the activity_dictionary sheet of the standard Activity and Media upload workbook.</t>
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Where the actual weekly activity numbers go</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Where the actual weekly activity numbers go</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>This builder never asks for your weekly spend, clicks, or impressions. Those go in the activity_data sheet of the same upload workbook, one row per period_start x market x activity_id.</t>
         </is>
@@ -770,7 +767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AI31"/>
+  <dimension ref="A1:AK31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -797,8 +794,8 @@
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
-    <col hidden="1" width="2" customWidth="1" min="27" max="27"/>
-    <col hidden="1" width="2" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
     <col hidden="1" width="2" customWidth="1" min="29" max="29"/>
     <col hidden="1" width="2" customWidth="1" min="30" max="30"/>
     <col hidden="1" width="2" customWidth="1" min="31" max="31"/>
@@ -806,6 +803,8 @@
     <col hidden="1" width="2" customWidth="1" min="33" max="33"/>
     <col hidden="1" width="2" customWidth="1" min="34" max="34"/>
     <col hidden="1" width="2" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="2" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="2" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -844,6 +843,8 @@
       <c r="AG1" s="4" t="n"/>
       <c r="AH1" s="4" t="n"/>
       <c r="AI1" s="4" t="n"/>
+      <c r="AJ1" s="4" t="n"/>
+      <c r="AK1" s="4" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr"/>
@@ -881,6 +882,8 @@
       <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="4" t="n"/>
       <c r="AI2" s="4" t="n"/>
+      <c r="AJ2" s="4" t="n"/>
+      <c r="AK2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr"/>
@@ -918,6 +921,8 @@
       <c r="AG3" s="4" t="n"/>
       <c r="AH3" s="4" t="n"/>
       <c r="AI3" s="4" t="n"/>
+      <c r="AJ3" s="4" t="n"/>
+      <c r="AK3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr"/>
@@ -955,6 +960,8 @@
       <c r="AG4" s="4" t="n"/>
       <c r="AH4" s="4" t="n"/>
       <c r="AI4" s="4" t="n"/>
+      <c r="AJ4" s="4" t="n"/>
+      <c r="AK4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr"/>
@@ -992,6 +999,8 @@
       <c r="AG5" s="4" t="n"/>
       <c r="AH5" s="4" t="n"/>
       <c r="AI5" s="4" t="n"/>
+      <c r="AJ5" s="4" t="n"/>
+      <c r="AK5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr"/>
@@ -1029,6 +1038,8 @@
       <c r="AG6" s="4" t="n"/>
       <c r="AH6" s="4" t="n"/>
       <c r="AI6" s="4" t="n"/>
+      <c r="AJ6" s="4" t="n"/>
+      <c r="AK6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1111,89 +1122,99 @@
           <t>campaign_type</t>
         </is>
       </c>
-      <c r="Q7" s="7" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>search_intent_group_id</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>search_platform</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>pooling_group_id</t>
         </is>
       </c>
-      <c r="R7" s="7" t="inlineStr">
+      <c r="T7" s="7" t="inlineStr">
         <is>
           <t>funnel_stage</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="U7" s="7" t="inlineStr">
         <is>
           <t>marketing_objective</t>
         </is>
       </c>
-      <c r="T7" s="7" t="inlineStr">
+      <c r="V7" s="7" t="inlineStr">
         <is>
           <t>product_advertised</t>
         </is>
       </c>
-      <c r="U7" s="7" t="inlineStr">
+      <c r="W7" s="7" t="inlineStr">
         <is>
           <t>message_type</t>
         </is>
       </c>
-      <c r="V7" s="7" t="inlineStr">
+      <c r="X7" s="7" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="W7" s="7" t="inlineStr">
+      <c r="Y7" s="7" t="inlineStr">
         <is>
           <t>effective_from</t>
         </is>
       </c>
-      <c r="X7" s="7" t="inlineStr">
+      <c r="Z7" s="7" t="inlineStr">
         <is>
           <t>effective_to</t>
         </is>
       </c>
-      <c r="Y7" s="5" t="n"/>
-      <c r="Z7" s="5" t="n"/>
-      <c r="AA7" s="5" t="inlineStr">
+      <c r="AA7" s="5" t="n"/>
+      <c r="AB7" s="5" t="n"/>
+      <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>_A_clean</t>
         </is>
       </c>
-      <c r="AB7" s="5" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>_A_collapsed</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr">
         <is>
           <t>_A_token</t>
         </is>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
+      <c r="AF7" s="5" t="inlineStr">
         <is>
           <t>_O_clean</t>
         </is>
       </c>
-      <c r="AE7" s="5" t="inlineStr">
+      <c r="AG7" s="5" t="inlineStr">
         <is>
           <t>_O_collapsed</t>
         </is>
       </c>
-      <c r="AF7" s="5" t="inlineStr">
+      <c r="AH7" s="5" t="inlineStr">
         <is>
           <t>_O_token</t>
         </is>
       </c>
-      <c r="AG7" s="5" t="inlineStr">
+      <c r="AI7" s="5" t="inlineStr">
         <is>
           <t>_P_clean</t>
         </is>
       </c>
-      <c r="AH7" s="5" t="inlineStr">
+      <c r="AJ7" s="5" t="inlineStr">
         <is>
           <t>_P_collapsed</t>
         </is>
       </c>
-      <c r="AI7" s="5" t="inlineStr">
+      <c r="AK7" s="5" t="inlineStr">
         <is>
           <t>_P_token</t>
         </is>
@@ -1244,7 +1265,7 @@
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4">
-        <f>IF(AC8&lt;&gt;"",AC8,"")&amp;IF(AF8&lt;&gt;"",IF(AC8&lt;&gt;"","_"&amp;AF8,AF8),"")&amp;IF(AI8&lt;&gt;"",IF(AC8&lt;&gt;"","_"&amp;AI8,AI8),"")</f>
+        <f>IF(AE8&lt;&gt;"",AE8,"")&amp;IF(AH8&lt;&gt;"",IF(AE8&lt;&gt;"","_"&amp;AH8,AH8),"")&amp;IF(AK8&lt;&gt;"",IF(AE8&lt;&gt;"","_"&amp;AK8,AK8),"")</f>
         <v/>
       </c>
       <c r="M8" s="4">
@@ -1265,50 +1286,60 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>brand_search</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="4" t="inlineStr"/>
       <c r="U8" s="4" t="inlineStr"/>
       <c r="V8" s="4" t="inlineStr"/>
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="n"/>
-      <c r="Z8" s="4" t="n"/>
-      <c r="AA8" s="4">
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="AA8" s="4" t="n"/>
+      <c r="AB8" s="4" t="n"/>
+      <c r="AC8" s="4">
         <f>IF(OR(LOWER(TRIM(A8))="",LOWER(TRIM(A8))="nan",LOWER(TRIM(A8))="none",LOWER(TRIM(A8))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A8))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB8" s="4">
-        <f>IF(AA8="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA8,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC8" s="4">
-        <f>IF(OR(AB8="",AB8="_"),"",IF(LEFT(AB8,1)="_",IF(RIGHT(AB8,1)="_",MID(AB8,2,LEN(AB8)-2),RIGHT(AB8,LEN(AB8)-1)),IF(RIGHT(AB8,1)="_",LEFT(AB8,LEN(AB8)-1),AB8)))</f>
-        <v/>
-      </c>
       <c r="AD8" s="4">
+        <f>IF(AC8="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC8,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE8" s="4">
+        <f>IF(OR(AD8="",AD8="_"),"",IF(LEFT(AD8,1)="_",IF(RIGHT(AD8,1)="_",MID(AD8,2,LEN(AD8)-2),RIGHT(AD8,LEN(AD8)-1)),IF(RIGHT(AD8,1)="_",LEFT(AD8,LEN(AD8)-1),AD8)))</f>
+        <v/>
+      </c>
+      <c r="AF8" s="4">
         <f>IF(OR(LOWER(TRIM(O8))="",LOWER(TRIM(O8))="nan",LOWER(TRIM(O8))="none",LOWER(TRIM(O8))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O8))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE8" s="4">
-        <f>IF(AD8="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD8,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF8" s="4">
-        <f>IF(OR(AE8="",AE8="_"),"",IF(LEFT(AE8,1)="_",IF(RIGHT(AE8,1)="_",MID(AE8,2,LEN(AE8)-2),RIGHT(AE8,LEN(AE8)-1)),IF(RIGHT(AE8,1)="_",LEFT(AE8,LEN(AE8)-1),AE8)))</f>
-        <v/>
-      </c>
       <c r="AG8" s="4">
+        <f>IF(AF8="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF8,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH8" s="4">
+        <f>IF(OR(AG8="",AG8="_"),"",IF(LEFT(AG8,1)="_",IF(RIGHT(AG8,1)="_",MID(AG8,2,LEN(AG8)-2),RIGHT(AG8,LEN(AG8)-1)),IF(RIGHT(AG8,1)="_",LEFT(AG8,LEN(AG8)-1),AG8)))</f>
+        <v/>
+      </c>
+      <c r="AI8" s="4">
         <f>IF(OR(LOWER(TRIM(P8))="",LOWER(TRIM(P8))="nan",LOWER(TRIM(P8))="none",LOWER(TRIM(P8))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P8))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH8" s="4">
-        <f>IF(AG8="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG8,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI8" s="4">
-        <f>IF(OR(AH8="",AH8="_"),"",IF(LEFT(AH8,1)="_",IF(RIGHT(AH8,1)="_",MID(AH8,2,LEN(AH8)-2),RIGHT(AH8,LEN(AH8)-1)),IF(RIGHT(AH8,1)="_",LEFT(AH8,LEN(AH8)-1),AH8)))</f>
+      <c r="AJ8" s="4">
+        <f>IF(AI8="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI8,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK8" s="4">
+        <f>IF(OR(AJ8="",AJ8="_"),"",IF(LEFT(AJ8,1)="_",IF(RIGHT(AJ8,1)="_",MID(AJ8,2,LEN(AJ8)-2),RIGHT(AJ8,LEN(AJ8)-1)),IF(RIGHT(AJ8,1)="_",LEFT(AJ8,LEN(AJ8)-1),AJ8)))</f>
         <v/>
       </c>
     </row>
@@ -1357,7 +1388,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4">
-        <f>IF(AC9&lt;&gt;"",AC9,"")&amp;IF(AF9&lt;&gt;"",IF(AC9&lt;&gt;"","_"&amp;AF9,AF9),"")&amp;IF(AI9&lt;&gt;"",IF(AC9&lt;&gt;"","_"&amp;AI9,AI9),"")</f>
+        <f>IF(AE9&lt;&gt;"",AE9,"")&amp;IF(AH9&lt;&gt;"",IF(AE9&lt;&gt;"","_"&amp;AH9,AH9),"")&amp;IF(AK9&lt;&gt;"",IF(AE9&lt;&gt;"","_"&amp;AK9,AK9),"")</f>
         <v/>
       </c>
       <c r="M9" s="4">
@@ -1378,50 +1409,60 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>brand_search</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>bing</t>
+        </is>
+      </c>
       <c r="S9" s="4" t="inlineStr"/>
       <c r="T9" s="4" t="inlineStr"/>
       <c r="U9" s="4" t="inlineStr"/>
       <c r="V9" s="4" t="inlineStr"/>
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="4" t="n"/>
-      <c r="Z9" s="4" t="n"/>
-      <c r="AA9" s="4">
+      <c r="Y9" s="4" t="inlineStr"/>
+      <c r="Z9" s="4" t="inlineStr"/>
+      <c r="AA9" s="4" t="n"/>
+      <c r="AB9" s="4" t="n"/>
+      <c r="AC9" s="4">
         <f>IF(OR(LOWER(TRIM(A9))="",LOWER(TRIM(A9))="nan",LOWER(TRIM(A9))="none",LOWER(TRIM(A9))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A9))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB9" s="4">
-        <f>IF(AA9="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA9,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC9" s="4">
-        <f>IF(OR(AB9="",AB9="_"),"",IF(LEFT(AB9,1)="_",IF(RIGHT(AB9,1)="_",MID(AB9,2,LEN(AB9)-2),RIGHT(AB9,LEN(AB9)-1)),IF(RIGHT(AB9,1)="_",LEFT(AB9,LEN(AB9)-1),AB9)))</f>
-        <v/>
-      </c>
       <c r="AD9" s="4">
+        <f>IF(AC9="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC9,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="4">
+        <f>IF(OR(AD9="",AD9="_"),"",IF(LEFT(AD9,1)="_",IF(RIGHT(AD9,1)="_",MID(AD9,2,LEN(AD9)-2),RIGHT(AD9,LEN(AD9)-1)),IF(RIGHT(AD9,1)="_",LEFT(AD9,LEN(AD9)-1),AD9)))</f>
+        <v/>
+      </c>
+      <c r="AF9" s="4">
         <f>IF(OR(LOWER(TRIM(O9))="",LOWER(TRIM(O9))="nan",LOWER(TRIM(O9))="none",LOWER(TRIM(O9))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O9))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE9" s="4">
-        <f>IF(AD9="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD9,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF9" s="4">
-        <f>IF(OR(AE9="",AE9="_"),"",IF(LEFT(AE9,1)="_",IF(RIGHT(AE9,1)="_",MID(AE9,2,LEN(AE9)-2),RIGHT(AE9,LEN(AE9)-1)),IF(RIGHT(AE9,1)="_",LEFT(AE9,LEN(AE9)-1),AE9)))</f>
-        <v/>
-      </c>
       <c r="AG9" s="4">
+        <f>IF(AF9="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF9,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH9" s="4">
+        <f>IF(OR(AG9="",AG9="_"),"",IF(LEFT(AG9,1)="_",IF(RIGHT(AG9,1)="_",MID(AG9,2,LEN(AG9)-2),RIGHT(AG9,LEN(AG9)-1)),IF(RIGHT(AG9,1)="_",LEFT(AG9,LEN(AG9)-1),AG9)))</f>
+        <v/>
+      </c>
+      <c r="AI9" s="4">
         <f>IF(OR(LOWER(TRIM(P9))="",LOWER(TRIM(P9))="nan",LOWER(TRIM(P9))="none",LOWER(TRIM(P9))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P9))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH9" s="4">
-        <f>IF(AG9="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG9,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI9" s="4">
-        <f>IF(OR(AH9="",AH9="_"),"",IF(LEFT(AH9,1)="_",IF(RIGHT(AH9,1)="_",MID(AH9,2,LEN(AH9)-2),RIGHT(AH9,LEN(AH9)-1)),IF(RIGHT(AH9,1)="_",LEFT(AH9,LEN(AH9)-1),AH9)))</f>
+      <c r="AJ9" s="4">
+        <f>IF(AI9="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI9,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK9" s="4">
+        <f>IF(OR(AJ9="",AJ9="_"),"",IF(LEFT(AJ9,1)="_",IF(RIGHT(AJ9,1)="_",MID(AJ9,2,LEN(AJ9)-2),RIGHT(AJ9,LEN(AJ9)-1)),IF(RIGHT(AJ9,1)="_",LEFT(AJ9,LEN(AJ9)-1),AJ9)))</f>
         <v/>
       </c>
     </row>
@@ -1470,7 +1511,7 @@
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="4">
-        <f>IF(AC10&lt;&gt;"",AC10,"")&amp;IF(AF10&lt;&gt;"",IF(AC10&lt;&gt;"","_"&amp;AF10,AF10),"")&amp;IF(AI10&lt;&gt;"",IF(AC10&lt;&gt;"","_"&amp;AI10,AI10),"")</f>
+        <f>IF(AE10&lt;&gt;"",AE10,"")&amp;IF(AH10&lt;&gt;"",IF(AE10&lt;&gt;"","_"&amp;AH10,AH10),"")&amp;IF(AK10&lt;&gt;"",IF(AE10&lt;&gt;"","_"&amp;AK10,AK10),"")</f>
         <v/>
       </c>
       <c r="M10" s="4">
@@ -1491,42 +1532,44 @@
       <c r="V10" s="4" t="inlineStr"/>
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="4" t="n"/>
-      <c r="Z10" s="4" t="n"/>
-      <c r="AA10" s="4">
+      <c r="Y10" s="4" t="inlineStr"/>
+      <c r="Z10" s="4" t="inlineStr"/>
+      <c r="AA10" s="4" t="n"/>
+      <c r="AB10" s="4" t="n"/>
+      <c r="AC10" s="4">
         <f>IF(OR(LOWER(TRIM(A10))="",LOWER(TRIM(A10))="nan",LOWER(TRIM(A10))="none",LOWER(TRIM(A10))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A10))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB10" s="4">
-        <f>IF(AA10="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA10,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC10" s="4">
-        <f>IF(OR(AB10="",AB10="_"),"",IF(LEFT(AB10,1)="_",IF(RIGHT(AB10,1)="_",MID(AB10,2,LEN(AB10)-2),RIGHT(AB10,LEN(AB10)-1)),IF(RIGHT(AB10,1)="_",LEFT(AB10,LEN(AB10)-1),AB10)))</f>
-        <v/>
-      </c>
       <c r="AD10" s="4">
+        <f>IF(AC10="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC10,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE10" s="4">
+        <f>IF(OR(AD10="",AD10="_"),"",IF(LEFT(AD10,1)="_",IF(RIGHT(AD10,1)="_",MID(AD10,2,LEN(AD10)-2),RIGHT(AD10,LEN(AD10)-1)),IF(RIGHT(AD10,1)="_",LEFT(AD10,LEN(AD10)-1),AD10)))</f>
+        <v/>
+      </c>
+      <c r="AF10" s="4">
         <f>IF(OR(LOWER(TRIM(O10))="",LOWER(TRIM(O10))="nan",LOWER(TRIM(O10))="none",LOWER(TRIM(O10))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O10))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE10" s="4">
-        <f>IF(AD10="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD10,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF10" s="4">
-        <f>IF(OR(AE10="",AE10="_"),"",IF(LEFT(AE10,1)="_",IF(RIGHT(AE10,1)="_",MID(AE10,2,LEN(AE10)-2),RIGHT(AE10,LEN(AE10)-1)),IF(RIGHT(AE10,1)="_",LEFT(AE10,LEN(AE10)-1),AE10)))</f>
-        <v/>
-      </c>
       <c r="AG10" s="4">
+        <f>IF(AF10="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF10,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH10" s="4">
+        <f>IF(OR(AG10="",AG10="_"),"",IF(LEFT(AG10,1)="_",IF(RIGHT(AG10,1)="_",MID(AG10,2,LEN(AG10)-2),RIGHT(AG10,LEN(AG10)-1)),IF(RIGHT(AG10,1)="_",LEFT(AG10,LEN(AG10)-1),AG10)))</f>
+        <v/>
+      </c>
+      <c r="AI10" s="4">
         <f>IF(OR(LOWER(TRIM(P10))="",LOWER(TRIM(P10))="nan",LOWER(TRIM(P10))="none",LOWER(TRIM(P10))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P10))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH10" s="4">
-        <f>IF(AG10="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG10,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI10" s="4">
-        <f>IF(OR(AH10="",AH10="_"),"",IF(LEFT(AH10,1)="_",IF(RIGHT(AH10,1)="_",MID(AH10,2,LEN(AH10)-2),RIGHT(AH10,LEN(AH10)-1)),IF(RIGHT(AH10,1)="_",LEFT(AH10,LEN(AH10)-1),AH10)))</f>
+      <c r="AJ10" s="4">
+        <f>IF(AI10="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI10,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK10" s="4">
+        <f>IF(OR(AJ10="",AJ10="_"),"",IF(LEFT(AJ10,1)="_",IF(RIGHT(AJ10,1)="_",MID(AJ10,2,LEN(AJ10)-2),RIGHT(AJ10,LEN(AJ10)-1)),IF(RIGHT(AJ10,1)="_",LEFT(AJ10,LEN(AJ10)-1),AJ10)))</f>
         <v/>
       </c>
     </row>
@@ -1575,7 +1618,7 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="4">
-        <f>IF(AC11&lt;&gt;"",AC11,"")&amp;IF(AF11&lt;&gt;"",IF(AC11&lt;&gt;"","_"&amp;AF11,AF11),"")&amp;IF(AI11&lt;&gt;"",IF(AC11&lt;&gt;"","_"&amp;AI11,AI11),"")</f>
+        <f>IF(AE11&lt;&gt;"",AE11,"")&amp;IF(AH11&lt;&gt;"",IF(AE11&lt;&gt;"","_"&amp;AH11,AH11),"")&amp;IF(AK11&lt;&gt;"",IF(AE11&lt;&gt;"","_"&amp;AK11,AK11),"")</f>
         <v/>
       </c>
       <c r="M11" s="4">
@@ -1596,42 +1639,44 @@
       <c r="V11" s="4" t="inlineStr"/>
       <c r="W11" s="4" t="inlineStr"/>
       <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="4" t="n"/>
-      <c r="Z11" s="4" t="n"/>
-      <c r="AA11" s="4">
+      <c r="Y11" s="4" t="inlineStr"/>
+      <c r="Z11" s="4" t="inlineStr"/>
+      <c r="AA11" s="4" t="n"/>
+      <c r="AB11" s="4" t="n"/>
+      <c r="AC11" s="4">
         <f>IF(OR(LOWER(TRIM(A11))="",LOWER(TRIM(A11))="nan",LOWER(TRIM(A11))="none",LOWER(TRIM(A11))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A11))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB11" s="4">
-        <f>IF(AA11="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA11,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC11" s="4">
-        <f>IF(OR(AB11="",AB11="_"),"",IF(LEFT(AB11,1)="_",IF(RIGHT(AB11,1)="_",MID(AB11,2,LEN(AB11)-2),RIGHT(AB11,LEN(AB11)-1)),IF(RIGHT(AB11,1)="_",LEFT(AB11,LEN(AB11)-1),AB11)))</f>
-        <v/>
-      </c>
       <c r="AD11" s="4">
+        <f>IF(AC11="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC11,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE11" s="4">
+        <f>IF(OR(AD11="",AD11="_"),"",IF(LEFT(AD11,1)="_",IF(RIGHT(AD11,1)="_",MID(AD11,2,LEN(AD11)-2),RIGHT(AD11,LEN(AD11)-1)),IF(RIGHT(AD11,1)="_",LEFT(AD11,LEN(AD11)-1),AD11)))</f>
+        <v/>
+      </c>
+      <c r="AF11" s="4">
         <f>IF(OR(LOWER(TRIM(O11))="",LOWER(TRIM(O11))="nan",LOWER(TRIM(O11))="none",LOWER(TRIM(O11))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O11))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE11" s="4">
-        <f>IF(AD11="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD11,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF11" s="4">
-        <f>IF(OR(AE11="",AE11="_"),"",IF(LEFT(AE11,1)="_",IF(RIGHT(AE11,1)="_",MID(AE11,2,LEN(AE11)-2),RIGHT(AE11,LEN(AE11)-1)),IF(RIGHT(AE11,1)="_",LEFT(AE11,LEN(AE11)-1),AE11)))</f>
-        <v/>
-      </c>
       <c r="AG11" s="4">
+        <f>IF(AF11="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF11,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH11" s="4">
+        <f>IF(OR(AG11="",AG11="_"),"",IF(LEFT(AG11,1)="_",IF(RIGHT(AG11,1)="_",MID(AG11,2,LEN(AG11)-2),RIGHT(AG11,LEN(AG11)-1)),IF(RIGHT(AG11,1)="_",LEFT(AG11,LEN(AG11)-1),AG11)))</f>
+        <v/>
+      </c>
+      <c r="AI11" s="4">
         <f>IF(OR(LOWER(TRIM(P11))="",LOWER(TRIM(P11))="nan",LOWER(TRIM(P11))="none",LOWER(TRIM(P11))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P11))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH11" s="4">
-        <f>IF(AG11="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG11,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI11" s="4">
-        <f>IF(OR(AH11="",AH11="_"),"",IF(LEFT(AH11,1)="_",IF(RIGHT(AH11,1)="_",MID(AH11,2,LEN(AH11)-2),RIGHT(AH11,LEN(AH11)-1)),IF(RIGHT(AH11,1)="_",LEFT(AH11,LEN(AH11)-1),AH11)))</f>
+      <c r="AJ11" s="4">
+        <f>IF(AI11="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI11,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK11" s="4">
+        <f>IF(OR(AJ11="",AJ11="_"),"",IF(LEFT(AJ11,1)="_",IF(RIGHT(AJ11,1)="_",MID(AJ11,2,LEN(AJ11)-2),RIGHT(AJ11,LEN(AJ11)-1)),IF(RIGHT(AJ11,1)="_",LEFT(AJ11,LEN(AJ11)-1),AJ11)))</f>
         <v/>
       </c>
     </row>
@@ -1648,7 +1693,7 @@
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="4">
-        <f>IF(AC12&lt;&gt;"",AC12,"")&amp;IF(AF12&lt;&gt;"",IF(AC12&lt;&gt;"","_"&amp;AF12,AF12),"")&amp;IF(AI12&lt;&gt;"",IF(AC12&lt;&gt;"","_"&amp;AI12,AI12),"")</f>
+        <f>IF(AE12&lt;&gt;"",AE12,"")&amp;IF(AH12&lt;&gt;"",IF(AE12&lt;&gt;"","_"&amp;AH12,AH12),"")&amp;IF(AK12&lt;&gt;"",IF(AE12&lt;&gt;"","_"&amp;AK12,AK12),"")</f>
         <v/>
       </c>
       <c r="M12" s="4">
@@ -1669,42 +1714,44 @@
       <c r="V12" s="4" t="inlineStr"/>
       <c r="W12" s="4" t="inlineStr"/>
       <c r="X12" s="4" t="inlineStr"/>
-      <c r="Y12" s="4" t="n"/>
-      <c r="Z12" s="4" t="n"/>
-      <c r="AA12" s="4">
+      <c r="Y12" s="4" t="inlineStr"/>
+      <c r="Z12" s="4" t="inlineStr"/>
+      <c r="AA12" s="4" t="n"/>
+      <c r="AB12" s="4" t="n"/>
+      <c r="AC12" s="4">
         <f>IF(OR(LOWER(TRIM(A12))="",LOWER(TRIM(A12))="nan",LOWER(TRIM(A12))="none",LOWER(TRIM(A12))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A12))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB12" s="4">
-        <f>IF(AA12="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA12,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC12" s="4">
-        <f>IF(OR(AB12="",AB12="_"),"",IF(LEFT(AB12,1)="_",IF(RIGHT(AB12,1)="_",MID(AB12,2,LEN(AB12)-2),RIGHT(AB12,LEN(AB12)-1)),IF(RIGHT(AB12,1)="_",LEFT(AB12,LEN(AB12)-1),AB12)))</f>
-        <v/>
-      </c>
       <c r="AD12" s="4">
+        <f>IF(AC12="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC12,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE12" s="4">
+        <f>IF(OR(AD12="",AD12="_"),"",IF(LEFT(AD12,1)="_",IF(RIGHT(AD12,1)="_",MID(AD12,2,LEN(AD12)-2),RIGHT(AD12,LEN(AD12)-1)),IF(RIGHT(AD12,1)="_",LEFT(AD12,LEN(AD12)-1),AD12)))</f>
+        <v/>
+      </c>
+      <c r="AF12" s="4">
         <f>IF(OR(LOWER(TRIM(O12))="",LOWER(TRIM(O12))="nan",LOWER(TRIM(O12))="none",LOWER(TRIM(O12))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O12))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE12" s="4">
-        <f>IF(AD12="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD12,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF12" s="4">
-        <f>IF(OR(AE12="",AE12="_"),"",IF(LEFT(AE12,1)="_",IF(RIGHT(AE12,1)="_",MID(AE12,2,LEN(AE12)-2),RIGHT(AE12,LEN(AE12)-1)),IF(RIGHT(AE12,1)="_",LEFT(AE12,LEN(AE12)-1),AE12)))</f>
-        <v/>
-      </c>
       <c r="AG12" s="4">
+        <f>IF(AF12="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF12,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH12" s="4">
+        <f>IF(OR(AG12="",AG12="_"),"",IF(LEFT(AG12,1)="_",IF(RIGHT(AG12,1)="_",MID(AG12,2,LEN(AG12)-2),RIGHT(AG12,LEN(AG12)-1)),IF(RIGHT(AG12,1)="_",LEFT(AG12,LEN(AG12)-1),AG12)))</f>
+        <v/>
+      </c>
+      <c r="AI12" s="4">
         <f>IF(OR(LOWER(TRIM(P12))="",LOWER(TRIM(P12))="nan",LOWER(TRIM(P12))="none",LOWER(TRIM(P12))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P12))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH12" s="4">
-        <f>IF(AG12="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG12,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI12" s="4">
-        <f>IF(OR(AH12="",AH12="_"),"",IF(LEFT(AH12,1)="_",IF(RIGHT(AH12,1)="_",MID(AH12,2,LEN(AH12)-2),RIGHT(AH12,LEN(AH12)-1)),IF(RIGHT(AH12,1)="_",LEFT(AH12,LEN(AH12)-1),AH12)))</f>
+      <c r="AJ12" s="4">
+        <f>IF(AI12="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI12,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK12" s="4">
+        <f>IF(OR(AJ12="",AJ12="_"),"",IF(LEFT(AJ12,1)="_",IF(RIGHT(AJ12,1)="_",MID(AJ12,2,LEN(AJ12)-2),RIGHT(AJ12,LEN(AJ12)-1)),IF(RIGHT(AJ12,1)="_",LEFT(AJ12,LEN(AJ12)-1),AJ12)))</f>
         <v/>
       </c>
     </row>
@@ -1721,7 +1768,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="4">
-        <f>IF(AC13&lt;&gt;"",AC13,"")&amp;IF(AF13&lt;&gt;"",IF(AC13&lt;&gt;"","_"&amp;AF13,AF13),"")&amp;IF(AI13&lt;&gt;"",IF(AC13&lt;&gt;"","_"&amp;AI13,AI13),"")</f>
+        <f>IF(AE13&lt;&gt;"",AE13,"")&amp;IF(AH13&lt;&gt;"",IF(AE13&lt;&gt;"","_"&amp;AH13,AH13),"")&amp;IF(AK13&lt;&gt;"",IF(AE13&lt;&gt;"","_"&amp;AK13,AK13),"")</f>
         <v/>
       </c>
       <c r="M13" s="4">
@@ -1742,42 +1789,44 @@
       <c r="V13" s="4" t="inlineStr"/>
       <c r="W13" s="4" t="inlineStr"/>
       <c r="X13" s="4" t="inlineStr"/>
-      <c r="Y13" s="4" t="n"/>
-      <c r="Z13" s="4" t="n"/>
-      <c r="AA13" s="4">
+      <c r="Y13" s="4" t="inlineStr"/>
+      <c r="Z13" s="4" t="inlineStr"/>
+      <c r="AA13" s="4" t="n"/>
+      <c r="AB13" s="4" t="n"/>
+      <c r="AC13" s="4">
         <f>IF(OR(LOWER(TRIM(A13))="",LOWER(TRIM(A13))="nan",LOWER(TRIM(A13))="none",LOWER(TRIM(A13))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A13))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB13" s="4">
-        <f>IF(AA13="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA13,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC13" s="4">
-        <f>IF(OR(AB13="",AB13="_"),"",IF(LEFT(AB13,1)="_",IF(RIGHT(AB13,1)="_",MID(AB13,2,LEN(AB13)-2),RIGHT(AB13,LEN(AB13)-1)),IF(RIGHT(AB13,1)="_",LEFT(AB13,LEN(AB13)-1),AB13)))</f>
-        <v/>
-      </c>
       <c r="AD13" s="4">
+        <f>IF(AC13="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC13,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE13" s="4">
+        <f>IF(OR(AD13="",AD13="_"),"",IF(LEFT(AD13,1)="_",IF(RIGHT(AD13,1)="_",MID(AD13,2,LEN(AD13)-2),RIGHT(AD13,LEN(AD13)-1)),IF(RIGHT(AD13,1)="_",LEFT(AD13,LEN(AD13)-1),AD13)))</f>
+        <v/>
+      </c>
+      <c r="AF13" s="4">
         <f>IF(OR(LOWER(TRIM(O13))="",LOWER(TRIM(O13))="nan",LOWER(TRIM(O13))="none",LOWER(TRIM(O13))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O13))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE13" s="4">
-        <f>IF(AD13="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD13,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF13" s="4">
-        <f>IF(OR(AE13="",AE13="_"),"",IF(LEFT(AE13,1)="_",IF(RIGHT(AE13,1)="_",MID(AE13,2,LEN(AE13)-2),RIGHT(AE13,LEN(AE13)-1)),IF(RIGHT(AE13,1)="_",LEFT(AE13,LEN(AE13)-1),AE13)))</f>
-        <v/>
-      </c>
       <c r="AG13" s="4">
+        <f>IF(AF13="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF13,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH13" s="4">
+        <f>IF(OR(AG13="",AG13="_"),"",IF(LEFT(AG13,1)="_",IF(RIGHT(AG13,1)="_",MID(AG13,2,LEN(AG13)-2),RIGHT(AG13,LEN(AG13)-1)),IF(RIGHT(AG13,1)="_",LEFT(AG13,LEN(AG13)-1),AG13)))</f>
+        <v/>
+      </c>
+      <c r="AI13" s="4">
         <f>IF(OR(LOWER(TRIM(P13))="",LOWER(TRIM(P13))="nan",LOWER(TRIM(P13))="none",LOWER(TRIM(P13))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P13))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH13" s="4">
-        <f>IF(AG13="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG13,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI13" s="4">
-        <f>IF(OR(AH13="",AH13="_"),"",IF(LEFT(AH13,1)="_",IF(RIGHT(AH13,1)="_",MID(AH13,2,LEN(AH13)-2),RIGHT(AH13,LEN(AH13)-1)),IF(RIGHT(AH13,1)="_",LEFT(AH13,LEN(AH13)-1),AH13)))</f>
+      <c r="AJ13" s="4">
+        <f>IF(AI13="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI13,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK13" s="4">
+        <f>IF(OR(AJ13="",AJ13="_"),"",IF(LEFT(AJ13,1)="_",IF(RIGHT(AJ13,1)="_",MID(AJ13,2,LEN(AJ13)-2),RIGHT(AJ13,LEN(AJ13)-1)),IF(RIGHT(AJ13,1)="_",LEFT(AJ13,LEN(AJ13)-1),AJ13)))</f>
         <v/>
       </c>
     </row>
@@ -1794,7 +1843,7 @@
       <c r="J14" s="4" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="4">
-        <f>IF(AC14&lt;&gt;"",AC14,"")&amp;IF(AF14&lt;&gt;"",IF(AC14&lt;&gt;"","_"&amp;AF14,AF14),"")&amp;IF(AI14&lt;&gt;"",IF(AC14&lt;&gt;"","_"&amp;AI14,AI14),"")</f>
+        <f>IF(AE14&lt;&gt;"",AE14,"")&amp;IF(AH14&lt;&gt;"",IF(AE14&lt;&gt;"","_"&amp;AH14,AH14),"")&amp;IF(AK14&lt;&gt;"",IF(AE14&lt;&gt;"","_"&amp;AK14,AK14),"")</f>
         <v/>
       </c>
       <c r="M14" s="4">
@@ -1815,42 +1864,44 @@
       <c r="V14" s="4" t="inlineStr"/>
       <c r="W14" s="4" t="inlineStr"/>
       <c r="X14" s="4" t="inlineStr"/>
-      <c r="Y14" s="4" t="n"/>
-      <c r="Z14" s="4" t="n"/>
-      <c r="AA14" s="4">
+      <c r="Y14" s="4" t="inlineStr"/>
+      <c r="Z14" s="4" t="inlineStr"/>
+      <c r="AA14" s="4" t="n"/>
+      <c r="AB14" s="4" t="n"/>
+      <c r="AC14" s="4">
         <f>IF(OR(LOWER(TRIM(A14))="",LOWER(TRIM(A14))="nan",LOWER(TRIM(A14))="none",LOWER(TRIM(A14))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A14))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB14" s="4">
-        <f>IF(AA14="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA14,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC14" s="4">
-        <f>IF(OR(AB14="",AB14="_"),"",IF(LEFT(AB14,1)="_",IF(RIGHT(AB14,1)="_",MID(AB14,2,LEN(AB14)-2),RIGHT(AB14,LEN(AB14)-1)),IF(RIGHT(AB14,1)="_",LEFT(AB14,LEN(AB14)-1),AB14)))</f>
-        <v/>
-      </c>
       <c r="AD14" s="4">
+        <f>IF(AC14="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC14,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="4">
+        <f>IF(OR(AD14="",AD14="_"),"",IF(LEFT(AD14,1)="_",IF(RIGHT(AD14,1)="_",MID(AD14,2,LEN(AD14)-2),RIGHT(AD14,LEN(AD14)-1)),IF(RIGHT(AD14,1)="_",LEFT(AD14,LEN(AD14)-1),AD14)))</f>
+        <v/>
+      </c>
+      <c r="AF14" s="4">
         <f>IF(OR(LOWER(TRIM(O14))="",LOWER(TRIM(O14))="nan",LOWER(TRIM(O14))="none",LOWER(TRIM(O14))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O14))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE14" s="4">
-        <f>IF(AD14="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD14,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF14" s="4">
-        <f>IF(OR(AE14="",AE14="_"),"",IF(LEFT(AE14,1)="_",IF(RIGHT(AE14,1)="_",MID(AE14,2,LEN(AE14)-2),RIGHT(AE14,LEN(AE14)-1)),IF(RIGHT(AE14,1)="_",LEFT(AE14,LEN(AE14)-1),AE14)))</f>
-        <v/>
-      </c>
       <c r="AG14" s="4">
+        <f>IF(AF14="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF14,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH14" s="4">
+        <f>IF(OR(AG14="",AG14="_"),"",IF(LEFT(AG14,1)="_",IF(RIGHT(AG14,1)="_",MID(AG14,2,LEN(AG14)-2),RIGHT(AG14,LEN(AG14)-1)),IF(RIGHT(AG14,1)="_",LEFT(AG14,LEN(AG14)-1),AG14)))</f>
+        <v/>
+      </c>
+      <c r="AI14" s="4">
         <f>IF(OR(LOWER(TRIM(P14))="",LOWER(TRIM(P14))="nan",LOWER(TRIM(P14))="none",LOWER(TRIM(P14))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P14))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH14" s="4">
-        <f>IF(AG14="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG14,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI14" s="4">
-        <f>IF(OR(AH14="",AH14="_"),"",IF(LEFT(AH14,1)="_",IF(RIGHT(AH14,1)="_",MID(AH14,2,LEN(AH14)-2),RIGHT(AH14,LEN(AH14)-1)),IF(RIGHT(AH14,1)="_",LEFT(AH14,LEN(AH14)-1),AH14)))</f>
+      <c r="AJ14" s="4">
+        <f>IF(AI14="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI14,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK14" s="4">
+        <f>IF(OR(AJ14="",AJ14="_"),"",IF(LEFT(AJ14,1)="_",IF(RIGHT(AJ14,1)="_",MID(AJ14,2,LEN(AJ14)-2),RIGHT(AJ14,LEN(AJ14)-1)),IF(RIGHT(AJ14,1)="_",LEFT(AJ14,LEN(AJ14)-1),AJ14)))</f>
         <v/>
       </c>
     </row>
@@ -1867,7 +1918,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="4">
-        <f>IF(AC15&lt;&gt;"",AC15,"")&amp;IF(AF15&lt;&gt;"",IF(AC15&lt;&gt;"","_"&amp;AF15,AF15),"")&amp;IF(AI15&lt;&gt;"",IF(AC15&lt;&gt;"","_"&amp;AI15,AI15),"")</f>
+        <f>IF(AE15&lt;&gt;"",AE15,"")&amp;IF(AH15&lt;&gt;"",IF(AE15&lt;&gt;"","_"&amp;AH15,AH15),"")&amp;IF(AK15&lt;&gt;"",IF(AE15&lt;&gt;"","_"&amp;AK15,AK15),"")</f>
         <v/>
       </c>
       <c r="M15" s="4">
@@ -1888,42 +1939,44 @@
       <c r="V15" s="4" t="inlineStr"/>
       <c r="W15" s="4" t="inlineStr"/>
       <c r="X15" s="4" t="inlineStr"/>
-      <c r="Y15" s="4" t="n"/>
-      <c r="Z15" s="4" t="n"/>
-      <c r="AA15" s="4">
+      <c r="Y15" s="4" t="inlineStr"/>
+      <c r="Z15" s="4" t="inlineStr"/>
+      <c r="AA15" s="4" t="n"/>
+      <c r="AB15" s="4" t="n"/>
+      <c r="AC15" s="4">
         <f>IF(OR(LOWER(TRIM(A15))="",LOWER(TRIM(A15))="nan",LOWER(TRIM(A15))="none",LOWER(TRIM(A15))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A15))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB15" s="4">
-        <f>IF(AA15="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA15,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC15" s="4">
-        <f>IF(OR(AB15="",AB15="_"),"",IF(LEFT(AB15,1)="_",IF(RIGHT(AB15,1)="_",MID(AB15,2,LEN(AB15)-2),RIGHT(AB15,LEN(AB15)-1)),IF(RIGHT(AB15,1)="_",LEFT(AB15,LEN(AB15)-1),AB15)))</f>
-        <v/>
-      </c>
       <c r="AD15" s="4">
+        <f>IF(AC15="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC15,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="4">
+        <f>IF(OR(AD15="",AD15="_"),"",IF(LEFT(AD15,1)="_",IF(RIGHT(AD15,1)="_",MID(AD15,2,LEN(AD15)-2),RIGHT(AD15,LEN(AD15)-1)),IF(RIGHT(AD15,1)="_",LEFT(AD15,LEN(AD15)-1),AD15)))</f>
+        <v/>
+      </c>
+      <c r="AF15" s="4">
         <f>IF(OR(LOWER(TRIM(O15))="",LOWER(TRIM(O15))="nan",LOWER(TRIM(O15))="none",LOWER(TRIM(O15))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O15))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE15" s="4">
-        <f>IF(AD15="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD15,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF15" s="4">
-        <f>IF(OR(AE15="",AE15="_"),"",IF(LEFT(AE15,1)="_",IF(RIGHT(AE15,1)="_",MID(AE15,2,LEN(AE15)-2),RIGHT(AE15,LEN(AE15)-1)),IF(RIGHT(AE15,1)="_",LEFT(AE15,LEN(AE15)-1),AE15)))</f>
-        <v/>
-      </c>
       <c r="AG15" s="4">
+        <f>IF(AF15="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF15,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH15" s="4">
+        <f>IF(OR(AG15="",AG15="_"),"",IF(LEFT(AG15,1)="_",IF(RIGHT(AG15,1)="_",MID(AG15,2,LEN(AG15)-2),RIGHT(AG15,LEN(AG15)-1)),IF(RIGHT(AG15,1)="_",LEFT(AG15,LEN(AG15)-1),AG15)))</f>
+        <v/>
+      </c>
+      <c r="AI15" s="4">
         <f>IF(OR(LOWER(TRIM(P15))="",LOWER(TRIM(P15))="nan",LOWER(TRIM(P15))="none",LOWER(TRIM(P15))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P15))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH15" s="4">
-        <f>IF(AG15="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG15,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI15" s="4">
-        <f>IF(OR(AH15="",AH15="_"),"",IF(LEFT(AH15,1)="_",IF(RIGHT(AH15,1)="_",MID(AH15,2,LEN(AH15)-2),RIGHT(AH15,LEN(AH15)-1)),IF(RIGHT(AH15,1)="_",LEFT(AH15,LEN(AH15)-1),AH15)))</f>
+      <c r="AJ15" s="4">
+        <f>IF(AI15="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI15,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK15" s="4">
+        <f>IF(OR(AJ15="",AJ15="_"),"",IF(LEFT(AJ15,1)="_",IF(RIGHT(AJ15,1)="_",MID(AJ15,2,LEN(AJ15)-2),RIGHT(AJ15,LEN(AJ15)-1)),IF(RIGHT(AJ15,1)="_",LEFT(AJ15,LEN(AJ15)-1),AJ15)))</f>
         <v/>
       </c>
     </row>
@@ -1940,7 +1993,7 @@
       <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="4">
-        <f>IF(AC16&lt;&gt;"",AC16,"")&amp;IF(AF16&lt;&gt;"",IF(AC16&lt;&gt;"","_"&amp;AF16,AF16),"")&amp;IF(AI16&lt;&gt;"",IF(AC16&lt;&gt;"","_"&amp;AI16,AI16),"")</f>
+        <f>IF(AE16&lt;&gt;"",AE16,"")&amp;IF(AH16&lt;&gt;"",IF(AE16&lt;&gt;"","_"&amp;AH16,AH16),"")&amp;IF(AK16&lt;&gt;"",IF(AE16&lt;&gt;"","_"&amp;AK16,AK16),"")</f>
         <v/>
       </c>
       <c r="M16" s="4">
@@ -1961,42 +2014,44 @@
       <c r="V16" s="4" t="inlineStr"/>
       <c r="W16" s="4" t="inlineStr"/>
       <c r="X16" s="4" t="inlineStr"/>
-      <c r="Y16" s="4" t="n"/>
-      <c r="Z16" s="4" t="n"/>
-      <c r="AA16" s="4">
+      <c r="Y16" s="4" t="inlineStr"/>
+      <c r="Z16" s="4" t="inlineStr"/>
+      <c r="AA16" s="4" t="n"/>
+      <c r="AB16" s="4" t="n"/>
+      <c r="AC16" s="4">
         <f>IF(OR(LOWER(TRIM(A16))="",LOWER(TRIM(A16))="nan",LOWER(TRIM(A16))="none",LOWER(TRIM(A16))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A16))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB16" s="4">
-        <f>IF(AA16="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA16,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC16" s="4">
-        <f>IF(OR(AB16="",AB16="_"),"",IF(LEFT(AB16,1)="_",IF(RIGHT(AB16,1)="_",MID(AB16,2,LEN(AB16)-2),RIGHT(AB16,LEN(AB16)-1)),IF(RIGHT(AB16,1)="_",LEFT(AB16,LEN(AB16)-1),AB16)))</f>
-        <v/>
-      </c>
       <c r="AD16" s="4">
+        <f>IF(AC16="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC16,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="4">
+        <f>IF(OR(AD16="",AD16="_"),"",IF(LEFT(AD16,1)="_",IF(RIGHT(AD16,1)="_",MID(AD16,2,LEN(AD16)-2),RIGHT(AD16,LEN(AD16)-1)),IF(RIGHT(AD16,1)="_",LEFT(AD16,LEN(AD16)-1),AD16)))</f>
+        <v/>
+      </c>
+      <c r="AF16" s="4">
         <f>IF(OR(LOWER(TRIM(O16))="",LOWER(TRIM(O16))="nan",LOWER(TRIM(O16))="none",LOWER(TRIM(O16))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O16))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE16" s="4">
-        <f>IF(AD16="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD16,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF16" s="4">
-        <f>IF(OR(AE16="",AE16="_"),"",IF(LEFT(AE16,1)="_",IF(RIGHT(AE16,1)="_",MID(AE16,2,LEN(AE16)-2),RIGHT(AE16,LEN(AE16)-1)),IF(RIGHT(AE16,1)="_",LEFT(AE16,LEN(AE16)-1),AE16)))</f>
-        <v/>
-      </c>
       <c r="AG16" s="4">
+        <f>IF(AF16="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF16,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH16" s="4">
+        <f>IF(OR(AG16="",AG16="_"),"",IF(LEFT(AG16,1)="_",IF(RIGHT(AG16,1)="_",MID(AG16,2,LEN(AG16)-2),RIGHT(AG16,LEN(AG16)-1)),IF(RIGHT(AG16,1)="_",LEFT(AG16,LEN(AG16)-1),AG16)))</f>
+        <v/>
+      </c>
+      <c r="AI16" s="4">
         <f>IF(OR(LOWER(TRIM(P16))="",LOWER(TRIM(P16))="nan",LOWER(TRIM(P16))="none",LOWER(TRIM(P16))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P16))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH16" s="4">
-        <f>IF(AG16="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG16,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI16" s="4">
-        <f>IF(OR(AH16="",AH16="_"),"",IF(LEFT(AH16,1)="_",IF(RIGHT(AH16,1)="_",MID(AH16,2,LEN(AH16)-2),RIGHT(AH16,LEN(AH16)-1)),IF(RIGHT(AH16,1)="_",LEFT(AH16,LEN(AH16)-1),AH16)))</f>
+      <c r="AJ16" s="4">
+        <f>IF(AI16="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI16,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK16" s="4">
+        <f>IF(OR(AJ16="",AJ16="_"),"",IF(LEFT(AJ16,1)="_",IF(RIGHT(AJ16,1)="_",MID(AJ16,2,LEN(AJ16)-2),RIGHT(AJ16,LEN(AJ16)-1)),IF(RIGHT(AJ16,1)="_",LEFT(AJ16,LEN(AJ16)-1),AJ16)))</f>
         <v/>
       </c>
     </row>
@@ -2013,7 +2068,7 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="4">
-        <f>IF(AC17&lt;&gt;"",AC17,"")&amp;IF(AF17&lt;&gt;"",IF(AC17&lt;&gt;"","_"&amp;AF17,AF17),"")&amp;IF(AI17&lt;&gt;"",IF(AC17&lt;&gt;"","_"&amp;AI17,AI17),"")</f>
+        <f>IF(AE17&lt;&gt;"",AE17,"")&amp;IF(AH17&lt;&gt;"",IF(AE17&lt;&gt;"","_"&amp;AH17,AH17),"")&amp;IF(AK17&lt;&gt;"",IF(AE17&lt;&gt;"","_"&amp;AK17,AK17),"")</f>
         <v/>
       </c>
       <c r="M17" s="4">
@@ -2034,42 +2089,44 @@
       <c r="V17" s="4" t="inlineStr"/>
       <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
-      <c r="Y17" s="4" t="n"/>
-      <c r="Z17" s="4" t="n"/>
-      <c r="AA17" s="4">
+      <c r="Y17" s="4" t="inlineStr"/>
+      <c r="Z17" s="4" t="inlineStr"/>
+      <c r="AA17" s="4" t="n"/>
+      <c r="AB17" s="4" t="n"/>
+      <c r="AC17" s="4">
         <f>IF(OR(LOWER(TRIM(A17))="",LOWER(TRIM(A17))="nan",LOWER(TRIM(A17))="none",LOWER(TRIM(A17))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A17))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB17" s="4">
-        <f>IF(AA17="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA17,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC17" s="4">
-        <f>IF(OR(AB17="",AB17="_"),"",IF(LEFT(AB17,1)="_",IF(RIGHT(AB17,1)="_",MID(AB17,2,LEN(AB17)-2),RIGHT(AB17,LEN(AB17)-1)),IF(RIGHT(AB17,1)="_",LEFT(AB17,LEN(AB17)-1),AB17)))</f>
-        <v/>
-      </c>
       <c r="AD17" s="4">
+        <f>IF(AC17="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC17,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="4">
+        <f>IF(OR(AD17="",AD17="_"),"",IF(LEFT(AD17,1)="_",IF(RIGHT(AD17,1)="_",MID(AD17,2,LEN(AD17)-2),RIGHT(AD17,LEN(AD17)-1)),IF(RIGHT(AD17,1)="_",LEFT(AD17,LEN(AD17)-1),AD17)))</f>
+        <v/>
+      </c>
+      <c r="AF17" s="4">
         <f>IF(OR(LOWER(TRIM(O17))="",LOWER(TRIM(O17))="nan",LOWER(TRIM(O17))="none",LOWER(TRIM(O17))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O17))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE17" s="4">
-        <f>IF(AD17="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD17,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF17" s="4">
-        <f>IF(OR(AE17="",AE17="_"),"",IF(LEFT(AE17,1)="_",IF(RIGHT(AE17,1)="_",MID(AE17,2,LEN(AE17)-2),RIGHT(AE17,LEN(AE17)-1)),IF(RIGHT(AE17,1)="_",LEFT(AE17,LEN(AE17)-1),AE17)))</f>
-        <v/>
-      </c>
       <c r="AG17" s="4">
+        <f>IF(AF17="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF17,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH17" s="4">
+        <f>IF(OR(AG17="",AG17="_"),"",IF(LEFT(AG17,1)="_",IF(RIGHT(AG17,1)="_",MID(AG17,2,LEN(AG17)-2),RIGHT(AG17,LEN(AG17)-1)),IF(RIGHT(AG17,1)="_",LEFT(AG17,LEN(AG17)-1),AG17)))</f>
+        <v/>
+      </c>
+      <c r="AI17" s="4">
         <f>IF(OR(LOWER(TRIM(P17))="",LOWER(TRIM(P17))="nan",LOWER(TRIM(P17))="none",LOWER(TRIM(P17))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P17))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH17" s="4">
-        <f>IF(AG17="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG17,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI17" s="4">
-        <f>IF(OR(AH17="",AH17="_"),"",IF(LEFT(AH17,1)="_",IF(RIGHT(AH17,1)="_",MID(AH17,2,LEN(AH17)-2),RIGHT(AH17,LEN(AH17)-1)),IF(RIGHT(AH17,1)="_",LEFT(AH17,LEN(AH17)-1),AH17)))</f>
+      <c r="AJ17" s="4">
+        <f>IF(AI17="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI17,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK17" s="4">
+        <f>IF(OR(AJ17="",AJ17="_"),"",IF(LEFT(AJ17,1)="_",IF(RIGHT(AJ17,1)="_",MID(AJ17,2,LEN(AJ17)-2),RIGHT(AJ17,LEN(AJ17)-1)),IF(RIGHT(AJ17,1)="_",LEFT(AJ17,LEN(AJ17)-1),AJ17)))</f>
         <v/>
       </c>
     </row>
@@ -2086,7 +2143,7 @@
       <c r="J18" s="4" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="4">
-        <f>IF(AC18&lt;&gt;"",AC18,"")&amp;IF(AF18&lt;&gt;"",IF(AC18&lt;&gt;"","_"&amp;AF18,AF18),"")&amp;IF(AI18&lt;&gt;"",IF(AC18&lt;&gt;"","_"&amp;AI18,AI18),"")</f>
+        <f>IF(AE18&lt;&gt;"",AE18,"")&amp;IF(AH18&lt;&gt;"",IF(AE18&lt;&gt;"","_"&amp;AH18,AH18),"")&amp;IF(AK18&lt;&gt;"",IF(AE18&lt;&gt;"","_"&amp;AK18,AK18),"")</f>
         <v/>
       </c>
       <c r="M18" s="4">
@@ -2107,42 +2164,44 @@
       <c r="V18" s="4" t="inlineStr"/>
       <c r="W18" s="4" t="inlineStr"/>
       <c r="X18" s="4" t="inlineStr"/>
-      <c r="Y18" s="4" t="n"/>
-      <c r="Z18" s="4" t="n"/>
-      <c r="AA18" s="4">
+      <c r="Y18" s="4" t="inlineStr"/>
+      <c r="Z18" s="4" t="inlineStr"/>
+      <c r="AA18" s="4" t="n"/>
+      <c r="AB18" s="4" t="n"/>
+      <c r="AC18" s="4">
         <f>IF(OR(LOWER(TRIM(A18))="",LOWER(TRIM(A18))="nan",LOWER(TRIM(A18))="none",LOWER(TRIM(A18))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A18))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB18" s="4">
-        <f>IF(AA18="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA18,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC18" s="4">
-        <f>IF(OR(AB18="",AB18="_"),"",IF(LEFT(AB18,1)="_",IF(RIGHT(AB18,1)="_",MID(AB18,2,LEN(AB18)-2),RIGHT(AB18,LEN(AB18)-1)),IF(RIGHT(AB18,1)="_",LEFT(AB18,LEN(AB18)-1),AB18)))</f>
-        <v/>
-      </c>
       <c r="AD18" s="4">
+        <f>IF(AC18="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC18,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="4">
+        <f>IF(OR(AD18="",AD18="_"),"",IF(LEFT(AD18,1)="_",IF(RIGHT(AD18,1)="_",MID(AD18,2,LEN(AD18)-2),RIGHT(AD18,LEN(AD18)-1)),IF(RIGHT(AD18,1)="_",LEFT(AD18,LEN(AD18)-1),AD18)))</f>
+        <v/>
+      </c>
+      <c r="AF18" s="4">
         <f>IF(OR(LOWER(TRIM(O18))="",LOWER(TRIM(O18))="nan",LOWER(TRIM(O18))="none",LOWER(TRIM(O18))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O18))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE18" s="4">
-        <f>IF(AD18="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD18,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF18" s="4">
-        <f>IF(OR(AE18="",AE18="_"),"",IF(LEFT(AE18,1)="_",IF(RIGHT(AE18,1)="_",MID(AE18,2,LEN(AE18)-2),RIGHT(AE18,LEN(AE18)-1)),IF(RIGHT(AE18,1)="_",LEFT(AE18,LEN(AE18)-1),AE18)))</f>
-        <v/>
-      </c>
       <c r="AG18" s="4">
+        <f>IF(AF18="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF18,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH18" s="4">
+        <f>IF(OR(AG18="",AG18="_"),"",IF(LEFT(AG18,1)="_",IF(RIGHT(AG18,1)="_",MID(AG18,2,LEN(AG18)-2),RIGHT(AG18,LEN(AG18)-1)),IF(RIGHT(AG18,1)="_",LEFT(AG18,LEN(AG18)-1),AG18)))</f>
+        <v/>
+      </c>
+      <c r="AI18" s="4">
         <f>IF(OR(LOWER(TRIM(P18))="",LOWER(TRIM(P18))="nan",LOWER(TRIM(P18))="none",LOWER(TRIM(P18))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P18))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH18" s="4">
-        <f>IF(AG18="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG18,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI18" s="4">
-        <f>IF(OR(AH18="",AH18="_"),"",IF(LEFT(AH18,1)="_",IF(RIGHT(AH18,1)="_",MID(AH18,2,LEN(AH18)-2),RIGHT(AH18,LEN(AH18)-1)),IF(RIGHT(AH18,1)="_",LEFT(AH18,LEN(AH18)-1),AH18)))</f>
+      <c r="AJ18" s="4">
+        <f>IF(AI18="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI18,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK18" s="4">
+        <f>IF(OR(AJ18="",AJ18="_"),"",IF(LEFT(AJ18,1)="_",IF(RIGHT(AJ18,1)="_",MID(AJ18,2,LEN(AJ18)-2),RIGHT(AJ18,LEN(AJ18)-1)),IF(RIGHT(AJ18,1)="_",LEFT(AJ18,LEN(AJ18)-1),AJ18)))</f>
         <v/>
       </c>
     </row>
@@ -2159,7 +2218,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="4">
-        <f>IF(AC19&lt;&gt;"",AC19,"")&amp;IF(AF19&lt;&gt;"",IF(AC19&lt;&gt;"","_"&amp;AF19,AF19),"")&amp;IF(AI19&lt;&gt;"",IF(AC19&lt;&gt;"","_"&amp;AI19,AI19),"")</f>
+        <f>IF(AE19&lt;&gt;"",AE19,"")&amp;IF(AH19&lt;&gt;"",IF(AE19&lt;&gt;"","_"&amp;AH19,AH19),"")&amp;IF(AK19&lt;&gt;"",IF(AE19&lt;&gt;"","_"&amp;AK19,AK19),"")</f>
         <v/>
       </c>
       <c r="M19" s="4">
@@ -2180,42 +2239,44 @@
       <c r="V19" s="4" t="inlineStr"/>
       <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="inlineStr"/>
-      <c r="Y19" s="4" t="n"/>
-      <c r="Z19" s="4" t="n"/>
-      <c r="AA19" s="4">
+      <c r="Y19" s="4" t="inlineStr"/>
+      <c r="Z19" s="4" t="inlineStr"/>
+      <c r="AA19" s="4" t="n"/>
+      <c r="AB19" s="4" t="n"/>
+      <c r="AC19" s="4">
         <f>IF(OR(LOWER(TRIM(A19))="",LOWER(TRIM(A19))="nan",LOWER(TRIM(A19))="none",LOWER(TRIM(A19))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A19))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB19" s="4">
-        <f>IF(AA19="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA19,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC19" s="4">
-        <f>IF(OR(AB19="",AB19="_"),"",IF(LEFT(AB19,1)="_",IF(RIGHT(AB19,1)="_",MID(AB19,2,LEN(AB19)-2),RIGHT(AB19,LEN(AB19)-1)),IF(RIGHT(AB19,1)="_",LEFT(AB19,LEN(AB19)-1),AB19)))</f>
-        <v/>
-      </c>
       <c r="AD19" s="4">
+        <f>IF(AC19="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC19,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="4">
+        <f>IF(OR(AD19="",AD19="_"),"",IF(LEFT(AD19,1)="_",IF(RIGHT(AD19,1)="_",MID(AD19,2,LEN(AD19)-2),RIGHT(AD19,LEN(AD19)-1)),IF(RIGHT(AD19,1)="_",LEFT(AD19,LEN(AD19)-1),AD19)))</f>
+        <v/>
+      </c>
+      <c r="AF19" s="4">
         <f>IF(OR(LOWER(TRIM(O19))="",LOWER(TRIM(O19))="nan",LOWER(TRIM(O19))="none",LOWER(TRIM(O19))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O19))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE19" s="4">
-        <f>IF(AD19="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD19,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF19" s="4">
-        <f>IF(OR(AE19="",AE19="_"),"",IF(LEFT(AE19,1)="_",IF(RIGHT(AE19,1)="_",MID(AE19,2,LEN(AE19)-2),RIGHT(AE19,LEN(AE19)-1)),IF(RIGHT(AE19,1)="_",LEFT(AE19,LEN(AE19)-1),AE19)))</f>
-        <v/>
-      </c>
       <c r="AG19" s="4">
+        <f>IF(AF19="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF19,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH19" s="4">
+        <f>IF(OR(AG19="",AG19="_"),"",IF(LEFT(AG19,1)="_",IF(RIGHT(AG19,1)="_",MID(AG19,2,LEN(AG19)-2),RIGHT(AG19,LEN(AG19)-1)),IF(RIGHT(AG19,1)="_",LEFT(AG19,LEN(AG19)-1),AG19)))</f>
+        <v/>
+      </c>
+      <c r="AI19" s="4">
         <f>IF(OR(LOWER(TRIM(P19))="",LOWER(TRIM(P19))="nan",LOWER(TRIM(P19))="none",LOWER(TRIM(P19))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P19))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH19" s="4">
-        <f>IF(AG19="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG19,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI19" s="4">
-        <f>IF(OR(AH19="",AH19="_"),"",IF(LEFT(AH19,1)="_",IF(RIGHT(AH19,1)="_",MID(AH19,2,LEN(AH19)-2),RIGHT(AH19,LEN(AH19)-1)),IF(RIGHT(AH19,1)="_",LEFT(AH19,LEN(AH19)-1),AH19)))</f>
+      <c r="AJ19" s="4">
+        <f>IF(AI19="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI19,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK19" s="4">
+        <f>IF(OR(AJ19="",AJ19="_"),"",IF(LEFT(AJ19,1)="_",IF(RIGHT(AJ19,1)="_",MID(AJ19,2,LEN(AJ19)-2),RIGHT(AJ19,LEN(AJ19)-1)),IF(RIGHT(AJ19,1)="_",LEFT(AJ19,LEN(AJ19)-1),AJ19)))</f>
         <v/>
       </c>
     </row>
@@ -2232,7 +2293,7 @@
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="4">
-        <f>IF(AC20&lt;&gt;"",AC20,"")&amp;IF(AF20&lt;&gt;"",IF(AC20&lt;&gt;"","_"&amp;AF20,AF20),"")&amp;IF(AI20&lt;&gt;"",IF(AC20&lt;&gt;"","_"&amp;AI20,AI20),"")</f>
+        <f>IF(AE20&lt;&gt;"",AE20,"")&amp;IF(AH20&lt;&gt;"",IF(AE20&lt;&gt;"","_"&amp;AH20,AH20),"")&amp;IF(AK20&lt;&gt;"",IF(AE20&lt;&gt;"","_"&amp;AK20,AK20),"")</f>
         <v/>
       </c>
       <c r="M20" s="4">
@@ -2253,42 +2314,44 @@
       <c r="V20" s="4" t="inlineStr"/>
       <c r="W20" s="4" t="inlineStr"/>
       <c r="X20" s="4" t="inlineStr"/>
-      <c r="Y20" s="4" t="n"/>
-      <c r="Z20" s="4" t="n"/>
-      <c r="AA20" s="4">
+      <c r="Y20" s="4" t="inlineStr"/>
+      <c r="Z20" s="4" t="inlineStr"/>
+      <c r="AA20" s="4" t="n"/>
+      <c r="AB20" s="4" t="n"/>
+      <c r="AC20" s="4">
         <f>IF(OR(LOWER(TRIM(A20))="",LOWER(TRIM(A20))="nan",LOWER(TRIM(A20))="none",LOWER(TRIM(A20))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A20))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB20" s="4">
-        <f>IF(AA20="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA20,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC20" s="4">
-        <f>IF(OR(AB20="",AB20="_"),"",IF(LEFT(AB20,1)="_",IF(RIGHT(AB20,1)="_",MID(AB20,2,LEN(AB20)-2),RIGHT(AB20,LEN(AB20)-1)),IF(RIGHT(AB20,1)="_",LEFT(AB20,LEN(AB20)-1),AB20)))</f>
-        <v/>
-      </c>
       <c r="AD20" s="4">
+        <f>IF(AC20="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC20,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="4">
+        <f>IF(OR(AD20="",AD20="_"),"",IF(LEFT(AD20,1)="_",IF(RIGHT(AD20,1)="_",MID(AD20,2,LEN(AD20)-2),RIGHT(AD20,LEN(AD20)-1)),IF(RIGHT(AD20,1)="_",LEFT(AD20,LEN(AD20)-1),AD20)))</f>
+        <v/>
+      </c>
+      <c r="AF20" s="4">
         <f>IF(OR(LOWER(TRIM(O20))="",LOWER(TRIM(O20))="nan",LOWER(TRIM(O20))="none",LOWER(TRIM(O20))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O20))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE20" s="4">
-        <f>IF(AD20="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD20,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF20" s="4">
-        <f>IF(OR(AE20="",AE20="_"),"",IF(LEFT(AE20,1)="_",IF(RIGHT(AE20,1)="_",MID(AE20,2,LEN(AE20)-2),RIGHT(AE20,LEN(AE20)-1)),IF(RIGHT(AE20,1)="_",LEFT(AE20,LEN(AE20)-1),AE20)))</f>
-        <v/>
-      </c>
       <c r="AG20" s="4">
+        <f>IF(AF20="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF20,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH20" s="4">
+        <f>IF(OR(AG20="",AG20="_"),"",IF(LEFT(AG20,1)="_",IF(RIGHT(AG20,1)="_",MID(AG20,2,LEN(AG20)-2),RIGHT(AG20,LEN(AG20)-1)),IF(RIGHT(AG20,1)="_",LEFT(AG20,LEN(AG20)-1),AG20)))</f>
+        <v/>
+      </c>
+      <c r="AI20" s="4">
         <f>IF(OR(LOWER(TRIM(P20))="",LOWER(TRIM(P20))="nan",LOWER(TRIM(P20))="none",LOWER(TRIM(P20))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P20))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH20" s="4">
-        <f>IF(AG20="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG20,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI20" s="4">
-        <f>IF(OR(AH20="",AH20="_"),"",IF(LEFT(AH20,1)="_",IF(RIGHT(AH20,1)="_",MID(AH20,2,LEN(AH20)-2),RIGHT(AH20,LEN(AH20)-1)),IF(RIGHT(AH20,1)="_",LEFT(AH20,LEN(AH20)-1),AH20)))</f>
+      <c r="AJ20" s="4">
+        <f>IF(AI20="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI20,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK20" s="4">
+        <f>IF(OR(AJ20="",AJ20="_"),"",IF(LEFT(AJ20,1)="_",IF(RIGHT(AJ20,1)="_",MID(AJ20,2,LEN(AJ20)-2),RIGHT(AJ20,LEN(AJ20)-1)),IF(RIGHT(AJ20,1)="_",LEFT(AJ20,LEN(AJ20)-1),AJ20)))</f>
         <v/>
       </c>
     </row>
@@ -2305,7 +2368,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="4">
-        <f>IF(AC21&lt;&gt;"",AC21,"")&amp;IF(AF21&lt;&gt;"",IF(AC21&lt;&gt;"","_"&amp;AF21,AF21),"")&amp;IF(AI21&lt;&gt;"",IF(AC21&lt;&gt;"","_"&amp;AI21,AI21),"")</f>
+        <f>IF(AE21&lt;&gt;"",AE21,"")&amp;IF(AH21&lt;&gt;"",IF(AE21&lt;&gt;"","_"&amp;AH21,AH21),"")&amp;IF(AK21&lt;&gt;"",IF(AE21&lt;&gt;"","_"&amp;AK21,AK21),"")</f>
         <v/>
       </c>
       <c r="M21" s="4">
@@ -2326,42 +2389,44 @@
       <c r="V21" s="4" t="inlineStr"/>
       <c r="W21" s="4" t="inlineStr"/>
       <c r="X21" s="4" t="inlineStr"/>
-      <c r="Y21" s="4" t="n"/>
-      <c r="Z21" s="4" t="n"/>
-      <c r="AA21" s="4">
+      <c r="Y21" s="4" t="inlineStr"/>
+      <c r="Z21" s="4" t="inlineStr"/>
+      <c r="AA21" s="4" t="n"/>
+      <c r="AB21" s="4" t="n"/>
+      <c r="AC21" s="4">
         <f>IF(OR(LOWER(TRIM(A21))="",LOWER(TRIM(A21))="nan",LOWER(TRIM(A21))="none",LOWER(TRIM(A21))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A21))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB21" s="4">
-        <f>IF(AA21="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA21,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC21" s="4">
-        <f>IF(OR(AB21="",AB21="_"),"",IF(LEFT(AB21,1)="_",IF(RIGHT(AB21,1)="_",MID(AB21,2,LEN(AB21)-2),RIGHT(AB21,LEN(AB21)-1)),IF(RIGHT(AB21,1)="_",LEFT(AB21,LEN(AB21)-1),AB21)))</f>
-        <v/>
-      </c>
       <c r="AD21" s="4">
+        <f>IF(AC21="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC21,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE21" s="4">
+        <f>IF(OR(AD21="",AD21="_"),"",IF(LEFT(AD21,1)="_",IF(RIGHT(AD21,1)="_",MID(AD21,2,LEN(AD21)-2),RIGHT(AD21,LEN(AD21)-1)),IF(RIGHT(AD21,1)="_",LEFT(AD21,LEN(AD21)-1),AD21)))</f>
+        <v/>
+      </c>
+      <c r="AF21" s="4">
         <f>IF(OR(LOWER(TRIM(O21))="",LOWER(TRIM(O21))="nan",LOWER(TRIM(O21))="none",LOWER(TRIM(O21))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O21))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE21" s="4">
-        <f>IF(AD21="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD21,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF21" s="4">
-        <f>IF(OR(AE21="",AE21="_"),"",IF(LEFT(AE21,1)="_",IF(RIGHT(AE21,1)="_",MID(AE21,2,LEN(AE21)-2),RIGHT(AE21,LEN(AE21)-1)),IF(RIGHT(AE21,1)="_",LEFT(AE21,LEN(AE21)-1),AE21)))</f>
-        <v/>
-      </c>
       <c r="AG21" s="4">
+        <f>IF(AF21="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF21,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH21" s="4">
+        <f>IF(OR(AG21="",AG21="_"),"",IF(LEFT(AG21,1)="_",IF(RIGHT(AG21,1)="_",MID(AG21,2,LEN(AG21)-2),RIGHT(AG21,LEN(AG21)-1)),IF(RIGHT(AG21,1)="_",LEFT(AG21,LEN(AG21)-1),AG21)))</f>
+        <v/>
+      </c>
+      <c r="AI21" s="4">
         <f>IF(OR(LOWER(TRIM(P21))="",LOWER(TRIM(P21))="nan",LOWER(TRIM(P21))="none",LOWER(TRIM(P21))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P21))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH21" s="4">
-        <f>IF(AG21="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG21,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI21" s="4">
-        <f>IF(OR(AH21="",AH21="_"),"",IF(LEFT(AH21,1)="_",IF(RIGHT(AH21,1)="_",MID(AH21,2,LEN(AH21)-2),RIGHT(AH21,LEN(AH21)-1)),IF(RIGHT(AH21,1)="_",LEFT(AH21,LEN(AH21)-1),AH21)))</f>
+      <c r="AJ21" s="4">
+        <f>IF(AI21="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI21,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK21" s="4">
+        <f>IF(OR(AJ21="",AJ21="_"),"",IF(LEFT(AJ21,1)="_",IF(RIGHT(AJ21,1)="_",MID(AJ21,2,LEN(AJ21)-2),RIGHT(AJ21,LEN(AJ21)-1)),IF(RIGHT(AJ21,1)="_",LEFT(AJ21,LEN(AJ21)-1),AJ21)))</f>
         <v/>
       </c>
     </row>
@@ -2378,7 +2443,7 @@
       <c r="J22" s="4" t="inlineStr"/>
       <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="4">
-        <f>IF(AC22&lt;&gt;"",AC22,"")&amp;IF(AF22&lt;&gt;"",IF(AC22&lt;&gt;"","_"&amp;AF22,AF22),"")&amp;IF(AI22&lt;&gt;"",IF(AC22&lt;&gt;"","_"&amp;AI22,AI22),"")</f>
+        <f>IF(AE22&lt;&gt;"",AE22,"")&amp;IF(AH22&lt;&gt;"",IF(AE22&lt;&gt;"","_"&amp;AH22,AH22),"")&amp;IF(AK22&lt;&gt;"",IF(AE22&lt;&gt;"","_"&amp;AK22,AK22),"")</f>
         <v/>
       </c>
       <c r="M22" s="4">
@@ -2399,42 +2464,44 @@
       <c r="V22" s="4" t="inlineStr"/>
       <c r="W22" s="4" t="inlineStr"/>
       <c r="X22" s="4" t="inlineStr"/>
-      <c r="Y22" s="4" t="n"/>
-      <c r="Z22" s="4" t="n"/>
-      <c r="AA22" s="4">
+      <c r="Y22" s="4" t="inlineStr"/>
+      <c r="Z22" s="4" t="inlineStr"/>
+      <c r="AA22" s="4" t="n"/>
+      <c r="AB22" s="4" t="n"/>
+      <c r="AC22" s="4">
         <f>IF(OR(LOWER(TRIM(A22))="",LOWER(TRIM(A22))="nan",LOWER(TRIM(A22))="none",LOWER(TRIM(A22))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A22))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB22" s="4">
-        <f>IF(AA22="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA22,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC22" s="4">
-        <f>IF(OR(AB22="",AB22="_"),"",IF(LEFT(AB22,1)="_",IF(RIGHT(AB22,1)="_",MID(AB22,2,LEN(AB22)-2),RIGHT(AB22,LEN(AB22)-1)),IF(RIGHT(AB22,1)="_",LEFT(AB22,LEN(AB22)-1),AB22)))</f>
-        <v/>
-      </c>
       <c r="AD22" s="4">
+        <f>IF(AC22="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC22,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE22" s="4">
+        <f>IF(OR(AD22="",AD22="_"),"",IF(LEFT(AD22,1)="_",IF(RIGHT(AD22,1)="_",MID(AD22,2,LEN(AD22)-2),RIGHT(AD22,LEN(AD22)-1)),IF(RIGHT(AD22,1)="_",LEFT(AD22,LEN(AD22)-1),AD22)))</f>
+        <v/>
+      </c>
+      <c r="AF22" s="4">
         <f>IF(OR(LOWER(TRIM(O22))="",LOWER(TRIM(O22))="nan",LOWER(TRIM(O22))="none",LOWER(TRIM(O22))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O22))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE22" s="4">
-        <f>IF(AD22="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD22,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF22" s="4">
-        <f>IF(OR(AE22="",AE22="_"),"",IF(LEFT(AE22,1)="_",IF(RIGHT(AE22,1)="_",MID(AE22,2,LEN(AE22)-2),RIGHT(AE22,LEN(AE22)-1)),IF(RIGHT(AE22,1)="_",LEFT(AE22,LEN(AE22)-1),AE22)))</f>
-        <v/>
-      </c>
       <c r="AG22" s="4">
+        <f>IF(AF22="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF22,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH22" s="4">
+        <f>IF(OR(AG22="",AG22="_"),"",IF(LEFT(AG22,1)="_",IF(RIGHT(AG22,1)="_",MID(AG22,2,LEN(AG22)-2),RIGHT(AG22,LEN(AG22)-1)),IF(RIGHT(AG22,1)="_",LEFT(AG22,LEN(AG22)-1),AG22)))</f>
+        <v/>
+      </c>
+      <c r="AI22" s="4">
         <f>IF(OR(LOWER(TRIM(P22))="",LOWER(TRIM(P22))="nan",LOWER(TRIM(P22))="none",LOWER(TRIM(P22))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P22))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH22" s="4">
-        <f>IF(AG22="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG22,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI22" s="4">
-        <f>IF(OR(AH22="",AH22="_"),"",IF(LEFT(AH22,1)="_",IF(RIGHT(AH22,1)="_",MID(AH22,2,LEN(AH22)-2),RIGHT(AH22,LEN(AH22)-1)),IF(RIGHT(AH22,1)="_",LEFT(AH22,LEN(AH22)-1),AH22)))</f>
+      <c r="AJ22" s="4">
+        <f>IF(AI22="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI22,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK22" s="4">
+        <f>IF(OR(AJ22="",AJ22="_"),"",IF(LEFT(AJ22,1)="_",IF(RIGHT(AJ22,1)="_",MID(AJ22,2,LEN(AJ22)-2),RIGHT(AJ22,LEN(AJ22)-1)),IF(RIGHT(AJ22,1)="_",LEFT(AJ22,LEN(AJ22)-1),AJ22)))</f>
         <v/>
       </c>
     </row>
@@ -2451,7 +2518,7 @@
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="4">
-        <f>IF(AC23&lt;&gt;"",AC23,"")&amp;IF(AF23&lt;&gt;"",IF(AC23&lt;&gt;"","_"&amp;AF23,AF23),"")&amp;IF(AI23&lt;&gt;"",IF(AC23&lt;&gt;"","_"&amp;AI23,AI23),"")</f>
+        <f>IF(AE23&lt;&gt;"",AE23,"")&amp;IF(AH23&lt;&gt;"",IF(AE23&lt;&gt;"","_"&amp;AH23,AH23),"")&amp;IF(AK23&lt;&gt;"",IF(AE23&lt;&gt;"","_"&amp;AK23,AK23),"")</f>
         <v/>
       </c>
       <c r="M23" s="4">
@@ -2472,42 +2539,44 @@
       <c r="V23" s="4" t="inlineStr"/>
       <c r="W23" s="4" t="inlineStr"/>
       <c r="X23" s="4" t="inlineStr"/>
-      <c r="Y23" s="4" t="n"/>
-      <c r="Z23" s="4" t="n"/>
-      <c r="AA23" s="4">
+      <c r="Y23" s="4" t="inlineStr"/>
+      <c r="Z23" s="4" t="inlineStr"/>
+      <c r="AA23" s="4" t="n"/>
+      <c r="AB23" s="4" t="n"/>
+      <c r="AC23" s="4">
         <f>IF(OR(LOWER(TRIM(A23))="",LOWER(TRIM(A23))="nan",LOWER(TRIM(A23))="none",LOWER(TRIM(A23))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A23))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB23" s="4">
-        <f>IF(AA23="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA23,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC23" s="4">
-        <f>IF(OR(AB23="",AB23="_"),"",IF(LEFT(AB23,1)="_",IF(RIGHT(AB23,1)="_",MID(AB23,2,LEN(AB23)-2),RIGHT(AB23,LEN(AB23)-1)),IF(RIGHT(AB23,1)="_",LEFT(AB23,LEN(AB23)-1),AB23)))</f>
-        <v/>
-      </c>
       <c r="AD23" s="4">
+        <f>IF(AC23="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC23,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE23" s="4">
+        <f>IF(OR(AD23="",AD23="_"),"",IF(LEFT(AD23,1)="_",IF(RIGHT(AD23,1)="_",MID(AD23,2,LEN(AD23)-2),RIGHT(AD23,LEN(AD23)-1)),IF(RIGHT(AD23,1)="_",LEFT(AD23,LEN(AD23)-1),AD23)))</f>
+        <v/>
+      </c>
+      <c r="AF23" s="4">
         <f>IF(OR(LOWER(TRIM(O23))="",LOWER(TRIM(O23))="nan",LOWER(TRIM(O23))="none",LOWER(TRIM(O23))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O23))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE23" s="4">
-        <f>IF(AD23="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD23,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF23" s="4">
-        <f>IF(OR(AE23="",AE23="_"),"",IF(LEFT(AE23,1)="_",IF(RIGHT(AE23,1)="_",MID(AE23,2,LEN(AE23)-2),RIGHT(AE23,LEN(AE23)-1)),IF(RIGHT(AE23,1)="_",LEFT(AE23,LEN(AE23)-1),AE23)))</f>
-        <v/>
-      </c>
       <c r="AG23" s="4">
+        <f>IF(AF23="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF23,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH23" s="4">
+        <f>IF(OR(AG23="",AG23="_"),"",IF(LEFT(AG23,1)="_",IF(RIGHT(AG23,1)="_",MID(AG23,2,LEN(AG23)-2),RIGHT(AG23,LEN(AG23)-1)),IF(RIGHT(AG23,1)="_",LEFT(AG23,LEN(AG23)-1),AG23)))</f>
+        <v/>
+      </c>
+      <c r="AI23" s="4">
         <f>IF(OR(LOWER(TRIM(P23))="",LOWER(TRIM(P23))="nan",LOWER(TRIM(P23))="none",LOWER(TRIM(P23))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P23))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH23" s="4">
-        <f>IF(AG23="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG23,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI23" s="4">
-        <f>IF(OR(AH23="",AH23="_"),"",IF(LEFT(AH23,1)="_",IF(RIGHT(AH23,1)="_",MID(AH23,2,LEN(AH23)-2),RIGHT(AH23,LEN(AH23)-1)),IF(RIGHT(AH23,1)="_",LEFT(AH23,LEN(AH23)-1),AH23)))</f>
+      <c r="AJ23" s="4">
+        <f>IF(AI23="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI23,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK23" s="4">
+        <f>IF(OR(AJ23="",AJ23="_"),"",IF(LEFT(AJ23,1)="_",IF(RIGHT(AJ23,1)="_",MID(AJ23,2,LEN(AJ23)-2),RIGHT(AJ23,LEN(AJ23)-1)),IF(RIGHT(AJ23,1)="_",LEFT(AJ23,LEN(AJ23)-1),AJ23)))</f>
         <v/>
       </c>
     </row>
@@ -2524,7 +2593,7 @@
       <c r="J24" s="4" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="4">
-        <f>IF(AC24&lt;&gt;"",AC24,"")&amp;IF(AF24&lt;&gt;"",IF(AC24&lt;&gt;"","_"&amp;AF24,AF24),"")&amp;IF(AI24&lt;&gt;"",IF(AC24&lt;&gt;"","_"&amp;AI24,AI24),"")</f>
+        <f>IF(AE24&lt;&gt;"",AE24,"")&amp;IF(AH24&lt;&gt;"",IF(AE24&lt;&gt;"","_"&amp;AH24,AH24),"")&amp;IF(AK24&lt;&gt;"",IF(AE24&lt;&gt;"","_"&amp;AK24,AK24),"")</f>
         <v/>
       </c>
       <c r="M24" s="4">
@@ -2545,42 +2614,44 @@
       <c r="V24" s="4" t="inlineStr"/>
       <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
-      <c r="Y24" s="4" t="n"/>
-      <c r="Z24" s="4" t="n"/>
-      <c r="AA24" s="4">
+      <c r="Y24" s="4" t="inlineStr"/>
+      <c r="Z24" s="4" t="inlineStr"/>
+      <c r="AA24" s="4" t="n"/>
+      <c r="AB24" s="4" t="n"/>
+      <c r="AC24" s="4">
         <f>IF(OR(LOWER(TRIM(A24))="",LOWER(TRIM(A24))="nan",LOWER(TRIM(A24))="none",LOWER(TRIM(A24))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A24))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB24" s="4">
-        <f>IF(AA24="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA24,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC24" s="4">
-        <f>IF(OR(AB24="",AB24="_"),"",IF(LEFT(AB24,1)="_",IF(RIGHT(AB24,1)="_",MID(AB24,2,LEN(AB24)-2),RIGHT(AB24,LEN(AB24)-1)),IF(RIGHT(AB24,1)="_",LEFT(AB24,LEN(AB24)-1),AB24)))</f>
-        <v/>
-      </c>
       <c r="AD24" s="4">
+        <f>IF(AC24="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC24,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE24" s="4">
+        <f>IF(OR(AD24="",AD24="_"),"",IF(LEFT(AD24,1)="_",IF(RIGHT(AD24,1)="_",MID(AD24,2,LEN(AD24)-2),RIGHT(AD24,LEN(AD24)-1)),IF(RIGHT(AD24,1)="_",LEFT(AD24,LEN(AD24)-1),AD24)))</f>
+        <v/>
+      </c>
+      <c r="AF24" s="4">
         <f>IF(OR(LOWER(TRIM(O24))="",LOWER(TRIM(O24))="nan",LOWER(TRIM(O24))="none",LOWER(TRIM(O24))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O24))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE24" s="4">
-        <f>IF(AD24="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD24,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF24" s="4">
-        <f>IF(OR(AE24="",AE24="_"),"",IF(LEFT(AE24,1)="_",IF(RIGHT(AE24,1)="_",MID(AE24,2,LEN(AE24)-2),RIGHT(AE24,LEN(AE24)-1)),IF(RIGHT(AE24,1)="_",LEFT(AE24,LEN(AE24)-1),AE24)))</f>
-        <v/>
-      </c>
       <c r="AG24" s="4">
+        <f>IF(AF24="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF24,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH24" s="4">
+        <f>IF(OR(AG24="",AG24="_"),"",IF(LEFT(AG24,1)="_",IF(RIGHT(AG24,1)="_",MID(AG24,2,LEN(AG24)-2),RIGHT(AG24,LEN(AG24)-1)),IF(RIGHT(AG24,1)="_",LEFT(AG24,LEN(AG24)-1),AG24)))</f>
+        <v/>
+      </c>
+      <c r="AI24" s="4">
         <f>IF(OR(LOWER(TRIM(P24))="",LOWER(TRIM(P24))="nan",LOWER(TRIM(P24))="none",LOWER(TRIM(P24))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P24))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH24" s="4">
-        <f>IF(AG24="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG24,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI24" s="4">
-        <f>IF(OR(AH24="",AH24="_"),"",IF(LEFT(AH24,1)="_",IF(RIGHT(AH24,1)="_",MID(AH24,2,LEN(AH24)-2),RIGHT(AH24,LEN(AH24)-1)),IF(RIGHT(AH24,1)="_",LEFT(AH24,LEN(AH24)-1),AH24)))</f>
+      <c r="AJ24" s="4">
+        <f>IF(AI24="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI24,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK24" s="4">
+        <f>IF(OR(AJ24="",AJ24="_"),"",IF(LEFT(AJ24,1)="_",IF(RIGHT(AJ24,1)="_",MID(AJ24,2,LEN(AJ24)-2),RIGHT(AJ24,LEN(AJ24)-1)),IF(RIGHT(AJ24,1)="_",LEFT(AJ24,LEN(AJ24)-1),AJ24)))</f>
         <v/>
       </c>
     </row>
@@ -2597,7 +2668,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="4">
-        <f>IF(AC25&lt;&gt;"",AC25,"")&amp;IF(AF25&lt;&gt;"",IF(AC25&lt;&gt;"","_"&amp;AF25,AF25),"")&amp;IF(AI25&lt;&gt;"",IF(AC25&lt;&gt;"","_"&amp;AI25,AI25),"")</f>
+        <f>IF(AE25&lt;&gt;"",AE25,"")&amp;IF(AH25&lt;&gt;"",IF(AE25&lt;&gt;"","_"&amp;AH25,AH25),"")&amp;IF(AK25&lt;&gt;"",IF(AE25&lt;&gt;"","_"&amp;AK25,AK25),"")</f>
         <v/>
       </c>
       <c r="M25" s="4">
@@ -2618,42 +2689,44 @@
       <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="inlineStr"/>
       <c r="X25" s="4" t="inlineStr"/>
-      <c r="Y25" s="4" t="n"/>
-      <c r="Z25" s="4" t="n"/>
-      <c r="AA25" s="4">
+      <c r="Y25" s="4" t="inlineStr"/>
+      <c r="Z25" s="4" t="inlineStr"/>
+      <c r="AA25" s="4" t="n"/>
+      <c r="AB25" s="4" t="n"/>
+      <c r="AC25" s="4">
         <f>IF(OR(LOWER(TRIM(A25))="",LOWER(TRIM(A25))="nan",LOWER(TRIM(A25))="none",LOWER(TRIM(A25))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A25))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB25" s="4">
-        <f>IF(AA25="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA25,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC25" s="4">
-        <f>IF(OR(AB25="",AB25="_"),"",IF(LEFT(AB25,1)="_",IF(RIGHT(AB25,1)="_",MID(AB25,2,LEN(AB25)-2),RIGHT(AB25,LEN(AB25)-1)),IF(RIGHT(AB25,1)="_",LEFT(AB25,LEN(AB25)-1),AB25)))</f>
-        <v/>
-      </c>
       <c r="AD25" s="4">
+        <f>IF(AC25="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC25,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE25" s="4">
+        <f>IF(OR(AD25="",AD25="_"),"",IF(LEFT(AD25,1)="_",IF(RIGHT(AD25,1)="_",MID(AD25,2,LEN(AD25)-2),RIGHT(AD25,LEN(AD25)-1)),IF(RIGHT(AD25,1)="_",LEFT(AD25,LEN(AD25)-1),AD25)))</f>
+        <v/>
+      </c>
+      <c r="AF25" s="4">
         <f>IF(OR(LOWER(TRIM(O25))="",LOWER(TRIM(O25))="nan",LOWER(TRIM(O25))="none",LOWER(TRIM(O25))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O25))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE25" s="4">
-        <f>IF(AD25="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD25,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF25" s="4">
-        <f>IF(OR(AE25="",AE25="_"),"",IF(LEFT(AE25,1)="_",IF(RIGHT(AE25,1)="_",MID(AE25,2,LEN(AE25)-2),RIGHT(AE25,LEN(AE25)-1)),IF(RIGHT(AE25,1)="_",LEFT(AE25,LEN(AE25)-1),AE25)))</f>
-        <v/>
-      </c>
       <c r="AG25" s="4">
+        <f>IF(AF25="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF25,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH25" s="4">
+        <f>IF(OR(AG25="",AG25="_"),"",IF(LEFT(AG25,1)="_",IF(RIGHT(AG25,1)="_",MID(AG25,2,LEN(AG25)-2),RIGHT(AG25,LEN(AG25)-1)),IF(RIGHT(AG25,1)="_",LEFT(AG25,LEN(AG25)-1),AG25)))</f>
+        <v/>
+      </c>
+      <c r="AI25" s="4">
         <f>IF(OR(LOWER(TRIM(P25))="",LOWER(TRIM(P25))="nan",LOWER(TRIM(P25))="none",LOWER(TRIM(P25))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P25))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH25" s="4">
-        <f>IF(AG25="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG25,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI25" s="4">
-        <f>IF(OR(AH25="",AH25="_"),"",IF(LEFT(AH25,1)="_",IF(RIGHT(AH25,1)="_",MID(AH25,2,LEN(AH25)-2),RIGHT(AH25,LEN(AH25)-1)),IF(RIGHT(AH25,1)="_",LEFT(AH25,LEN(AH25)-1),AH25)))</f>
+      <c r="AJ25" s="4">
+        <f>IF(AI25="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI25,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK25" s="4">
+        <f>IF(OR(AJ25="",AJ25="_"),"",IF(LEFT(AJ25,1)="_",IF(RIGHT(AJ25,1)="_",MID(AJ25,2,LEN(AJ25)-2),RIGHT(AJ25,LEN(AJ25)-1)),IF(RIGHT(AJ25,1)="_",LEFT(AJ25,LEN(AJ25)-1),AJ25)))</f>
         <v/>
       </c>
     </row>
@@ -2670,7 +2743,7 @@
       <c r="J26" s="4" t="inlineStr"/>
       <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="4">
-        <f>IF(AC26&lt;&gt;"",AC26,"")&amp;IF(AF26&lt;&gt;"",IF(AC26&lt;&gt;"","_"&amp;AF26,AF26),"")&amp;IF(AI26&lt;&gt;"",IF(AC26&lt;&gt;"","_"&amp;AI26,AI26),"")</f>
+        <f>IF(AE26&lt;&gt;"",AE26,"")&amp;IF(AH26&lt;&gt;"",IF(AE26&lt;&gt;"","_"&amp;AH26,AH26),"")&amp;IF(AK26&lt;&gt;"",IF(AE26&lt;&gt;"","_"&amp;AK26,AK26),"")</f>
         <v/>
       </c>
       <c r="M26" s="4">
@@ -2691,42 +2764,44 @@
       <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="4" t="inlineStr"/>
       <c r="X26" s="4" t="inlineStr"/>
-      <c r="Y26" s="4" t="n"/>
-      <c r="Z26" s="4" t="n"/>
-      <c r="AA26" s="4">
+      <c r="Y26" s="4" t="inlineStr"/>
+      <c r="Z26" s="4" t="inlineStr"/>
+      <c r="AA26" s="4" t="n"/>
+      <c r="AB26" s="4" t="n"/>
+      <c r="AC26" s="4">
         <f>IF(OR(LOWER(TRIM(A26))="",LOWER(TRIM(A26))="nan",LOWER(TRIM(A26))="none",LOWER(TRIM(A26))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A26))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB26" s="4">
-        <f>IF(AA26="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA26,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC26" s="4">
-        <f>IF(OR(AB26="",AB26="_"),"",IF(LEFT(AB26,1)="_",IF(RIGHT(AB26,1)="_",MID(AB26,2,LEN(AB26)-2),RIGHT(AB26,LEN(AB26)-1)),IF(RIGHT(AB26,1)="_",LEFT(AB26,LEN(AB26)-1),AB26)))</f>
-        <v/>
-      </c>
       <c r="AD26" s="4">
+        <f>IF(AC26="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC26,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE26" s="4">
+        <f>IF(OR(AD26="",AD26="_"),"",IF(LEFT(AD26,1)="_",IF(RIGHT(AD26,1)="_",MID(AD26,2,LEN(AD26)-2),RIGHT(AD26,LEN(AD26)-1)),IF(RIGHT(AD26,1)="_",LEFT(AD26,LEN(AD26)-1),AD26)))</f>
+        <v/>
+      </c>
+      <c r="AF26" s="4">
         <f>IF(OR(LOWER(TRIM(O26))="",LOWER(TRIM(O26))="nan",LOWER(TRIM(O26))="none",LOWER(TRIM(O26))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O26))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE26" s="4">
-        <f>IF(AD26="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD26,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF26" s="4">
-        <f>IF(OR(AE26="",AE26="_"),"",IF(LEFT(AE26,1)="_",IF(RIGHT(AE26,1)="_",MID(AE26,2,LEN(AE26)-2),RIGHT(AE26,LEN(AE26)-1)),IF(RIGHT(AE26,1)="_",LEFT(AE26,LEN(AE26)-1),AE26)))</f>
-        <v/>
-      </c>
       <c r="AG26" s="4">
+        <f>IF(AF26="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF26,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH26" s="4">
+        <f>IF(OR(AG26="",AG26="_"),"",IF(LEFT(AG26,1)="_",IF(RIGHT(AG26,1)="_",MID(AG26,2,LEN(AG26)-2),RIGHT(AG26,LEN(AG26)-1)),IF(RIGHT(AG26,1)="_",LEFT(AG26,LEN(AG26)-1),AG26)))</f>
+        <v/>
+      </c>
+      <c r="AI26" s="4">
         <f>IF(OR(LOWER(TRIM(P26))="",LOWER(TRIM(P26))="nan",LOWER(TRIM(P26))="none",LOWER(TRIM(P26))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P26))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH26" s="4">
-        <f>IF(AG26="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG26,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI26" s="4">
-        <f>IF(OR(AH26="",AH26="_"),"",IF(LEFT(AH26,1)="_",IF(RIGHT(AH26,1)="_",MID(AH26,2,LEN(AH26)-2),RIGHT(AH26,LEN(AH26)-1)),IF(RIGHT(AH26,1)="_",LEFT(AH26,LEN(AH26)-1),AH26)))</f>
+      <c r="AJ26" s="4">
+        <f>IF(AI26="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI26,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK26" s="4">
+        <f>IF(OR(AJ26="",AJ26="_"),"",IF(LEFT(AJ26,1)="_",IF(RIGHT(AJ26,1)="_",MID(AJ26,2,LEN(AJ26)-2),RIGHT(AJ26,LEN(AJ26)-1)),IF(RIGHT(AJ26,1)="_",LEFT(AJ26,LEN(AJ26)-1),AJ26)))</f>
         <v/>
       </c>
     </row>
@@ -2743,7 +2818,7 @@
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="4">
-        <f>IF(AC27&lt;&gt;"",AC27,"")&amp;IF(AF27&lt;&gt;"",IF(AC27&lt;&gt;"","_"&amp;AF27,AF27),"")&amp;IF(AI27&lt;&gt;"",IF(AC27&lt;&gt;"","_"&amp;AI27,AI27),"")</f>
+        <f>IF(AE27&lt;&gt;"",AE27,"")&amp;IF(AH27&lt;&gt;"",IF(AE27&lt;&gt;"","_"&amp;AH27,AH27),"")&amp;IF(AK27&lt;&gt;"",IF(AE27&lt;&gt;"","_"&amp;AK27,AK27),"")</f>
         <v/>
       </c>
       <c r="M27" s="4">
@@ -2764,42 +2839,44 @@
       <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
-      <c r="Y27" s="4" t="n"/>
-      <c r="Z27" s="4" t="n"/>
-      <c r="AA27" s="4">
+      <c r="Y27" s="4" t="inlineStr"/>
+      <c r="Z27" s="4" t="inlineStr"/>
+      <c r="AA27" s="4" t="n"/>
+      <c r="AB27" s="4" t="n"/>
+      <c r="AC27" s="4">
         <f>IF(OR(LOWER(TRIM(A27))="",LOWER(TRIM(A27))="nan",LOWER(TRIM(A27))="none",LOWER(TRIM(A27))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A27))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB27" s="4">
-        <f>IF(AA27="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA27,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC27" s="4">
-        <f>IF(OR(AB27="",AB27="_"),"",IF(LEFT(AB27,1)="_",IF(RIGHT(AB27,1)="_",MID(AB27,2,LEN(AB27)-2),RIGHT(AB27,LEN(AB27)-1)),IF(RIGHT(AB27,1)="_",LEFT(AB27,LEN(AB27)-1),AB27)))</f>
-        <v/>
-      </c>
       <c r="AD27" s="4">
+        <f>IF(AC27="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC27,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE27" s="4">
+        <f>IF(OR(AD27="",AD27="_"),"",IF(LEFT(AD27,1)="_",IF(RIGHT(AD27,1)="_",MID(AD27,2,LEN(AD27)-2),RIGHT(AD27,LEN(AD27)-1)),IF(RIGHT(AD27,1)="_",LEFT(AD27,LEN(AD27)-1),AD27)))</f>
+        <v/>
+      </c>
+      <c r="AF27" s="4">
         <f>IF(OR(LOWER(TRIM(O27))="",LOWER(TRIM(O27))="nan",LOWER(TRIM(O27))="none",LOWER(TRIM(O27))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O27))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE27" s="4">
-        <f>IF(AD27="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD27,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF27" s="4">
-        <f>IF(OR(AE27="",AE27="_"),"",IF(LEFT(AE27,1)="_",IF(RIGHT(AE27,1)="_",MID(AE27,2,LEN(AE27)-2),RIGHT(AE27,LEN(AE27)-1)),IF(RIGHT(AE27,1)="_",LEFT(AE27,LEN(AE27)-1),AE27)))</f>
-        <v/>
-      </c>
       <c r="AG27" s="4">
+        <f>IF(AF27="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF27,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH27" s="4">
+        <f>IF(OR(AG27="",AG27="_"),"",IF(LEFT(AG27,1)="_",IF(RIGHT(AG27,1)="_",MID(AG27,2,LEN(AG27)-2),RIGHT(AG27,LEN(AG27)-1)),IF(RIGHT(AG27,1)="_",LEFT(AG27,LEN(AG27)-1),AG27)))</f>
+        <v/>
+      </c>
+      <c r="AI27" s="4">
         <f>IF(OR(LOWER(TRIM(P27))="",LOWER(TRIM(P27))="nan",LOWER(TRIM(P27))="none",LOWER(TRIM(P27))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P27))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH27" s="4">
-        <f>IF(AG27="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG27,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI27" s="4">
-        <f>IF(OR(AH27="",AH27="_"),"",IF(LEFT(AH27,1)="_",IF(RIGHT(AH27,1)="_",MID(AH27,2,LEN(AH27)-2),RIGHT(AH27,LEN(AH27)-1)),IF(RIGHT(AH27,1)="_",LEFT(AH27,LEN(AH27)-1),AH27)))</f>
+      <c r="AJ27" s="4">
+        <f>IF(AI27="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI27,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK27" s="4">
+        <f>IF(OR(AJ27="",AJ27="_"),"",IF(LEFT(AJ27,1)="_",IF(RIGHT(AJ27,1)="_",MID(AJ27,2,LEN(AJ27)-2),RIGHT(AJ27,LEN(AJ27)-1)),IF(RIGHT(AJ27,1)="_",LEFT(AJ27,LEN(AJ27)-1),AJ27)))</f>
         <v/>
       </c>
     </row>
@@ -2816,7 +2893,7 @@
       <c r="J28" s="4" t="inlineStr"/>
       <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="4">
-        <f>IF(AC28&lt;&gt;"",AC28,"")&amp;IF(AF28&lt;&gt;"",IF(AC28&lt;&gt;"","_"&amp;AF28,AF28),"")&amp;IF(AI28&lt;&gt;"",IF(AC28&lt;&gt;"","_"&amp;AI28,AI28),"")</f>
+        <f>IF(AE28&lt;&gt;"",AE28,"")&amp;IF(AH28&lt;&gt;"",IF(AE28&lt;&gt;"","_"&amp;AH28,AH28),"")&amp;IF(AK28&lt;&gt;"",IF(AE28&lt;&gt;"","_"&amp;AK28,AK28),"")</f>
         <v/>
       </c>
       <c r="M28" s="4">
@@ -2837,42 +2914,44 @@
       <c r="V28" s="4" t="inlineStr"/>
       <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
-      <c r="Y28" s="4" t="n"/>
-      <c r="Z28" s="4" t="n"/>
-      <c r="AA28" s="4">
+      <c r="Y28" s="4" t="inlineStr"/>
+      <c r="Z28" s="4" t="inlineStr"/>
+      <c r="AA28" s="4" t="n"/>
+      <c r="AB28" s="4" t="n"/>
+      <c r="AC28" s="4">
         <f>IF(OR(LOWER(TRIM(A28))="",LOWER(TRIM(A28))="nan",LOWER(TRIM(A28))="none",LOWER(TRIM(A28))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A28))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB28" s="4">
-        <f>IF(AA28="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA28,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC28" s="4">
-        <f>IF(OR(AB28="",AB28="_"),"",IF(LEFT(AB28,1)="_",IF(RIGHT(AB28,1)="_",MID(AB28,2,LEN(AB28)-2),RIGHT(AB28,LEN(AB28)-1)),IF(RIGHT(AB28,1)="_",LEFT(AB28,LEN(AB28)-1),AB28)))</f>
-        <v/>
-      </c>
       <c r="AD28" s="4">
+        <f>IF(AC28="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC28,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE28" s="4">
+        <f>IF(OR(AD28="",AD28="_"),"",IF(LEFT(AD28,1)="_",IF(RIGHT(AD28,1)="_",MID(AD28,2,LEN(AD28)-2),RIGHT(AD28,LEN(AD28)-1)),IF(RIGHT(AD28,1)="_",LEFT(AD28,LEN(AD28)-1),AD28)))</f>
+        <v/>
+      </c>
+      <c r="AF28" s="4">
         <f>IF(OR(LOWER(TRIM(O28))="",LOWER(TRIM(O28))="nan",LOWER(TRIM(O28))="none",LOWER(TRIM(O28))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O28))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE28" s="4">
-        <f>IF(AD28="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD28,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF28" s="4">
-        <f>IF(OR(AE28="",AE28="_"),"",IF(LEFT(AE28,1)="_",IF(RIGHT(AE28,1)="_",MID(AE28,2,LEN(AE28)-2),RIGHT(AE28,LEN(AE28)-1)),IF(RIGHT(AE28,1)="_",LEFT(AE28,LEN(AE28)-1),AE28)))</f>
-        <v/>
-      </c>
       <c r="AG28" s="4">
+        <f>IF(AF28="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF28,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH28" s="4">
+        <f>IF(OR(AG28="",AG28="_"),"",IF(LEFT(AG28,1)="_",IF(RIGHT(AG28,1)="_",MID(AG28,2,LEN(AG28)-2),RIGHT(AG28,LEN(AG28)-1)),IF(RIGHT(AG28,1)="_",LEFT(AG28,LEN(AG28)-1),AG28)))</f>
+        <v/>
+      </c>
+      <c r="AI28" s="4">
         <f>IF(OR(LOWER(TRIM(P28))="",LOWER(TRIM(P28))="nan",LOWER(TRIM(P28))="none",LOWER(TRIM(P28))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P28))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH28" s="4">
-        <f>IF(AG28="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG28,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI28" s="4">
-        <f>IF(OR(AH28="",AH28="_"),"",IF(LEFT(AH28,1)="_",IF(RIGHT(AH28,1)="_",MID(AH28,2,LEN(AH28)-2),RIGHT(AH28,LEN(AH28)-1)),IF(RIGHT(AH28,1)="_",LEFT(AH28,LEN(AH28)-1),AH28)))</f>
+      <c r="AJ28" s="4">
+        <f>IF(AI28="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI28,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK28" s="4">
+        <f>IF(OR(AJ28="",AJ28="_"),"",IF(LEFT(AJ28,1)="_",IF(RIGHT(AJ28,1)="_",MID(AJ28,2,LEN(AJ28)-2),RIGHT(AJ28,LEN(AJ28)-1)),IF(RIGHT(AJ28,1)="_",LEFT(AJ28,LEN(AJ28)-1),AJ28)))</f>
         <v/>
       </c>
     </row>
@@ -2889,7 +2968,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="4">
-        <f>IF(AC29&lt;&gt;"",AC29,"")&amp;IF(AF29&lt;&gt;"",IF(AC29&lt;&gt;"","_"&amp;AF29,AF29),"")&amp;IF(AI29&lt;&gt;"",IF(AC29&lt;&gt;"","_"&amp;AI29,AI29),"")</f>
+        <f>IF(AE29&lt;&gt;"",AE29,"")&amp;IF(AH29&lt;&gt;"",IF(AE29&lt;&gt;"","_"&amp;AH29,AH29),"")&amp;IF(AK29&lt;&gt;"",IF(AE29&lt;&gt;"","_"&amp;AK29,AK29),"")</f>
         <v/>
       </c>
       <c r="M29" s="4">
@@ -2910,42 +2989,44 @@
       <c r="V29" s="4" t="inlineStr"/>
       <c r="W29" s="4" t="inlineStr"/>
       <c r="X29" s="4" t="inlineStr"/>
-      <c r="Y29" s="4" t="n"/>
-      <c r="Z29" s="4" t="n"/>
-      <c r="AA29" s="4">
+      <c r="Y29" s="4" t="inlineStr"/>
+      <c r="Z29" s="4" t="inlineStr"/>
+      <c r="AA29" s="4" t="n"/>
+      <c r="AB29" s="4" t="n"/>
+      <c r="AC29" s="4">
         <f>IF(OR(LOWER(TRIM(A29))="",LOWER(TRIM(A29))="nan",LOWER(TRIM(A29))="none",LOWER(TRIM(A29))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A29))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB29" s="4">
-        <f>IF(AA29="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA29,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC29" s="4">
-        <f>IF(OR(AB29="",AB29="_"),"",IF(LEFT(AB29,1)="_",IF(RIGHT(AB29,1)="_",MID(AB29,2,LEN(AB29)-2),RIGHT(AB29,LEN(AB29)-1)),IF(RIGHT(AB29,1)="_",LEFT(AB29,LEN(AB29)-1),AB29)))</f>
-        <v/>
-      </c>
       <c r="AD29" s="4">
+        <f>IF(AC29="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC29,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE29" s="4">
+        <f>IF(OR(AD29="",AD29="_"),"",IF(LEFT(AD29,1)="_",IF(RIGHT(AD29,1)="_",MID(AD29,2,LEN(AD29)-2),RIGHT(AD29,LEN(AD29)-1)),IF(RIGHT(AD29,1)="_",LEFT(AD29,LEN(AD29)-1),AD29)))</f>
+        <v/>
+      </c>
+      <c r="AF29" s="4">
         <f>IF(OR(LOWER(TRIM(O29))="",LOWER(TRIM(O29))="nan",LOWER(TRIM(O29))="none",LOWER(TRIM(O29))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O29))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE29" s="4">
-        <f>IF(AD29="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD29,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF29" s="4">
-        <f>IF(OR(AE29="",AE29="_"),"",IF(LEFT(AE29,1)="_",IF(RIGHT(AE29,1)="_",MID(AE29,2,LEN(AE29)-2),RIGHT(AE29,LEN(AE29)-1)),IF(RIGHT(AE29,1)="_",LEFT(AE29,LEN(AE29)-1),AE29)))</f>
-        <v/>
-      </c>
       <c r="AG29" s="4">
+        <f>IF(AF29="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF29,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH29" s="4">
+        <f>IF(OR(AG29="",AG29="_"),"",IF(LEFT(AG29,1)="_",IF(RIGHT(AG29,1)="_",MID(AG29,2,LEN(AG29)-2),RIGHT(AG29,LEN(AG29)-1)),IF(RIGHT(AG29,1)="_",LEFT(AG29,LEN(AG29)-1),AG29)))</f>
+        <v/>
+      </c>
+      <c r="AI29" s="4">
         <f>IF(OR(LOWER(TRIM(P29))="",LOWER(TRIM(P29))="nan",LOWER(TRIM(P29))="none",LOWER(TRIM(P29))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P29))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH29" s="4">
-        <f>IF(AG29="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG29,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI29" s="4">
-        <f>IF(OR(AH29="",AH29="_"),"",IF(LEFT(AH29,1)="_",IF(RIGHT(AH29,1)="_",MID(AH29,2,LEN(AH29)-2),RIGHT(AH29,LEN(AH29)-1)),IF(RIGHT(AH29,1)="_",LEFT(AH29,LEN(AH29)-1),AH29)))</f>
+      <c r="AJ29" s="4">
+        <f>IF(AI29="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI29,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK29" s="4">
+        <f>IF(OR(AJ29="",AJ29="_"),"",IF(LEFT(AJ29,1)="_",IF(RIGHT(AJ29,1)="_",MID(AJ29,2,LEN(AJ29)-2),RIGHT(AJ29,LEN(AJ29)-1)),IF(RIGHT(AJ29,1)="_",LEFT(AJ29,LEN(AJ29)-1),AJ29)))</f>
         <v/>
       </c>
     </row>
@@ -2962,7 +3043,7 @@
       <c r="J30" s="4" t="inlineStr"/>
       <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="4">
-        <f>IF(AC30&lt;&gt;"",AC30,"")&amp;IF(AF30&lt;&gt;"",IF(AC30&lt;&gt;"","_"&amp;AF30,AF30),"")&amp;IF(AI30&lt;&gt;"",IF(AC30&lt;&gt;"","_"&amp;AI30,AI30),"")</f>
+        <f>IF(AE30&lt;&gt;"",AE30,"")&amp;IF(AH30&lt;&gt;"",IF(AE30&lt;&gt;"","_"&amp;AH30,AH30),"")&amp;IF(AK30&lt;&gt;"",IF(AE30&lt;&gt;"","_"&amp;AK30,AK30),"")</f>
         <v/>
       </c>
       <c r="M30" s="4">
@@ -2983,42 +3064,44 @@
       <c r="V30" s="4" t="inlineStr"/>
       <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
-      <c r="Y30" s="4" t="n"/>
-      <c r="Z30" s="4" t="n"/>
-      <c r="AA30" s="4">
+      <c r="Y30" s="4" t="inlineStr"/>
+      <c r="Z30" s="4" t="inlineStr"/>
+      <c r="AA30" s="4" t="n"/>
+      <c r="AB30" s="4" t="n"/>
+      <c r="AC30" s="4">
         <f>IF(OR(LOWER(TRIM(A30))="",LOWER(TRIM(A30))="nan",LOWER(TRIM(A30))="none",LOWER(TRIM(A30))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A30))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB30" s="4">
-        <f>IF(AA30="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA30,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC30" s="4">
-        <f>IF(OR(AB30="",AB30="_"),"",IF(LEFT(AB30,1)="_",IF(RIGHT(AB30,1)="_",MID(AB30,2,LEN(AB30)-2),RIGHT(AB30,LEN(AB30)-1)),IF(RIGHT(AB30,1)="_",LEFT(AB30,LEN(AB30)-1),AB30)))</f>
-        <v/>
-      </c>
       <c r="AD30" s="4">
+        <f>IF(AC30="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC30,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE30" s="4">
+        <f>IF(OR(AD30="",AD30="_"),"",IF(LEFT(AD30,1)="_",IF(RIGHT(AD30,1)="_",MID(AD30,2,LEN(AD30)-2),RIGHT(AD30,LEN(AD30)-1)),IF(RIGHT(AD30,1)="_",LEFT(AD30,LEN(AD30)-1),AD30)))</f>
+        <v/>
+      </c>
+      <c r="AF30" s="4">
         <f>IF(OR(LOWER(TRIM(O30))="",LOWER(TRIM(O30))="nan",LOWER(TRIM(O30))="none",LOWER(TRIM(O30))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O30))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE30" s="4">
-        <f>IF(AD30="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD30,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF30" s="4">
-        <f>IF(OR(AE30="",AE30="_"),"",IF(LEFT(AE30,1)="_",IF(RIGHT(AE30,1)="_",MID(AE30,2,LEN(AE30)-2),RIGHT(AE30,LEN(AE30)-1)),IF(RIGHT(AE30,1)="_",LEFT(AE30,LEN(AE30)-1),AE30)))</f>
-        <v/>
-      </c>
       <c r="AG30" s="4">
+        <f>IF(AF30="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF30,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH30" s="4">
+        <f>IF(OR(AG30="",AG30="_"),"",IF(LEFT(AG30,1)="_",IF(RIGHT(AG30,1)="_",MID(AG30,2,LEN(AG30)-2),RIGHT(AG30,LEN(AG30)-1)),IF(RIGHT(AG30,1)="_",LEFT(AG30,LEN(AG30)-1),AG30)))</f>
+        <v/>
+      </c>
+      <c r="AI30" s="4">
         <f>IF(OR(LOWER(TRIM(P30))="",LOWER(TRIM(P30))="nan",LOWER(TRIM(P30))="none",LOWER(TRIM(P30))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P30))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH30" s="4">
-        <f>IF(AG30="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG30,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI30" s="4">
-        <f>IF(OR(AH30="",AH30="_"),"",IF(LEFT(AH30,1)="_",IF(RIGHT(AH30,1)="_",MID(AH30,2,LEN(AH30)-2),RIGHT(AH30,LEN(AH30)-1)),IF(RIGHT(AH30,1)="_",LEFT(AH30,LEN(AH30)-1),AH30)))</f>
+      <c r="AJ30" s="4">
+        <f>IF(AI30="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI30,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK30" s="4">
+        <f>IF(OR(AJ30="",AJ30="_"),"",IF(LEFT(AJ30,1)="_",IF(RIGHT(AJ30,1)="_",MID(AJ30,2,LEN(AJ30)-2),RIGHT(AJ30,LEN(AJ30)-1)),IF(RIGHT(AJ30,1)="_",LEFT(AJ30,LEN(AJ30)-1),AJ30)))</f>
         <v/>
       </c>
     </row>
@@ -3035,7 +3118,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="4">
-        <f>IF(AC31&lt;&gt;"",AC31,"")&amp;IF(AF31&lt;&gt;"",IF(AC31&lt;&gt;"","_"&amp;AF31,AF31),"")&amp;IF(AI31&lt;&gt;"",IF(AC31&lt;&gt;"","_"&amp;AI31,AI31),"")</f>
+        <f>IF(AE31&lt;&gt;"",AE31,"")&amp;IF(AH31&lt;&gt;"",IF(AE31&lt;&gt;"","_"&amp;AH31,AH31),"")&amp;IF(AK31&lt;&gt;"",IF(AE31&lt;&gt;"","_"&amp;AK31,AK31),"")</f>
         <v/>
       </c>
       <c r="M31" s="4">
@@ -3056,42 +3139,44 @@
       <c r="V31" s="4" t="inlineStr"/>
       <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
-      <c r="Y31" s="4" t="n"/>
-      <c r="Z31" s="4" t="n"/>
-      <c r="AA31" s="4">
+      <c r="Y31" s="4" t="inlineStr"/>
+      <c r="Z31" s="4" t="inlineStr"/>
+      <c r="AA31" s="4" t="n"/>
+      <c r="AB31" s="4" t="n"/>
+      <c r="AC31" s="4">
         <f>IF(OR(LOWER(TRIM(A31))="",LOWER(TRIM(A31))="nan",LOWER(TRIM(A31))="none",LOWER(TRIM(A31))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(A31))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AB31" s="4">
-        <f>IF(AA31="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AA31,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AC31" s="4">
-        <f>IF(OR(AB31="",AB31="_"),"",IF(LEFT(AB31,1)="_",IF(RIGHT(AB31,1)="_",MID(AB31,2,LEN(AB31)-2),RIGHT(AB31,LEN(AB31)-1)),IF(RIGHT(AB31,1)="_",LEFT(AB31,LEN(AB31)-1),AB31)))</f>
-        <v/>
-      </c>
       <c r="AD31" s="4">
+        <f>IF(AC31="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AC31,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AE31" s="4">
+        <f>IF(OR(AD31="",AD31="_"),"",IF(LEFT(AD31,1)="_",IF(RIGHT(AD31,1)="_",MID(AD31,2,LEN(AD31)-2),RIGHT(AD31,LEN(AD31)-1)),IF(RIGHT(AD31,1)="_",LEFT(AD31,LEN(AD31)-1),AD31)))</f>
+        <v/>
+      </c>
+      <c r="AF31" s="4">
         <f>IF(OR(LOWER(TRIM(O31))="",LOWER(TRIM(O31))="nan",LOWER(TRIM(O31))="none",LOWER(TRIM(O31))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(O31))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AE31" s="4">
-        <f>IF(AD31="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AD31,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AF31" s="4">
-        <f>IF(OR(AE31="",AE31="_"),"",IF(LEFT(AE31,1)="_",IF(RIGHT(AE31,1)="_",MID(AE31,2,LEN(AE31)-2),RIGHT(AE31,LEN(AE31)-1)),IF(RIGHT(AE31,1)="_",LEFT(AE31,LEN(AE31)-1),AE31)))</f>
-        <v/>
-      </c>
       <c r="AG31" s="4">
+        <f>IF(AF31="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AF31,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AH31" s="4">
+        <f>IF(OR(AG31="",AG31="_"),"",IF(LEFT(AG31,1)="_",IF(RIGHT(AG31,1)="_",MID(AG31,2,LEN(AG31)-2),RIGHT(AG31,LEN(AG31)-1)),IF(RIGHT(AG31,1)="_",LEFT(AG31,LEN(AG31)-1),AG31)))</f>
+        <v/>
+      </c>
+      <c r="AI31" s="4">
         <f>IF(OR(LOWER(TRIM(P31))="",LOWER(TRIM(P31))="nan",LOWER(TRIM(P31))="none",LOWER(TRIM(P31))="n/a"),"",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(TRIM(P31))," ","_"),"!","_"),"#","_"),"$","_"),"%","_"),"&amp;","_"),"'","_"),"(","_"),")","_"),"*","_"),"+","_"),",","_"),"-","_"),".","_"),"/","_"),":","_"),";","_"),"&lt;","_"),"=","_"),"&gt;","_"),"?","_"),"@","_"),"[","_"),"\","_"),"]","_"),"^","_"),"`","_"),"{","_"),"|","_"),"}","_"),"~","_"),"–","_"),"—","_"),"’","_"),"“","_"),"”","_"),CHAR(9),"_"),CHAR(160),"_"))</f>
         <v/>
       </c>
-      <c r="AH31" s="4">
-        <f>IF(AG31="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AG31,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
-        <v/>
-      </c>
-      <c r="AI31" s="4">
-        <f>IF(OR(AH31="",AH31="_"),"",IF(LEFT(AH31,1)="_",IF(RIGHT(AH31,1)="_",MID(AH31,2,LEN(AH31)-2),RIGHT(AH31,LEN(AH31)-1)),IF(RIGHT(AH31,1)="_",LEFT(AH31,LEN(AH31)-1),AH31)))</f>
+      <c r="AJ31" s="4">
+        <f>IF(AI31="","",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(AI31,"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"),"__","_"))</f>
+        <v/>
+      </c>
+      <c r="AK31" s="4">
+        <f>IF(OR(AJ31="",AJ31="_"),"",IF(LEFT(AJ31,1)="_",IF(RIGHT(AJ31,1)="_",MID(AJ31,2,LEN(AJ31)-2),RIGHT(AJ31,LEN(AJ31)-1)),IF(RIGHT(AJ31,1)="_",LEFT(AJ31,LEN(AJ31)-1),AJ31)))</f>
         <v/>
       </c>
     </row>
@@ -3107,20 +3192,20 @@
       <formula>N8="Ready"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="10">
     <dataValidation sqref="C8:C31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="activity_ownership" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="activity_ownership" prompt="Select an approved value." type="list">
-      <formula1>"paid,owned,earned,external_event"</formula1>
+      <formula1>"paid,external_event,owned,earned"</formula1>
     </dataValidation>
     <dataValidation sqref="D8:D31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="intended_model_role" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="intended_model_role" prompt="Select an approved value." type="list">
-      <formula1>"mediator,event,demand_capture,control,intervention"</formula1>
+      <formula1>"control,mediator,demand_capture,event,intervention"</formula1>
     </dataValidation>
     <dataValidation sqref="G8:G31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="economic_treatment" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="economic_treatment" prompt="Select an approved value." type="list">
-      <formula1>"paid_media_cost,fully_loaded_cost,not_applicable,response_only,campaign_cost"</formula1>
+      <formula1>"not_applicable,campaign_cost,paid_media_cost,response_only,fully_loaded_cost"</formula1>
     </dataValidation>
     <dataValidation sqref="H8:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="planning_eligibility" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="planning_eligibility" prompt="Select an approved value." type="list">
-      <formula1>"optimisable,excluded,fixed,scenario_only"</formula1>
+      <formula1>"fixed,scenario_only,optimisable,excluded"</formula1>
     </dataValidation>
-    <dataValidation sqref="R8:R31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="funnel_stage" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="funnel_stage" prompt="Select an approved value." type="list">
+    <dataValidation sqref="T8:T31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="funnel_stage" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="funnel_stage" prompt="Select an approved value." type="list">
       <formula1>"brand_upper,mid_funnel,performance_lower,cross_funnel,not_applicable,unclassified"</formula1>
     </dataValidation>
     <dataValidation sqref="O8:O31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="platform" prompt="Choose a suggestion, or type your own text -- this field is not a closed list in the app." type="list">
@@ -3129,7 +3214,13 @@
     <dataValidation sqref="P8:P31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="campaign_type" prompt="Choose a suggestion, or type your own text -- this field is not a closed list in the app." type="list">
       <formula1>"Brand,Non-Brand"</formula1>
     </dataValidation>
-    <dataValidation sqref="S8:S31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="marketing_objective" prompt="Choose a suggestion, or type your own text -- this field is not a closed list in the app." type="list">
+    <dataValidation sqref="Q8:Q31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="search_intent_group_id" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="search_intent_group_id" prompt="Select an approved value." type="list">
+      <formula1>"brand_search,non_brand_search"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R8:R31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="search_platform" error="Choose a value from the approved list or leave it blank when the field is optional." promptTitle="search_platform" prompt="Select an approved value." type="list">
+      <formula1>"google,bing"</formula1>
+    </dataValidation>
+    <dataValidation sqref="U8:U31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="marketing_objective" prompt="Choose a suggestion, or type your own text -- this field is not a closed list in the app." type="list">
       <formula1>"brand awareness,consideration,acquisition/performance,retention/lifecycle,promotion,winback,service/transactional,other"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3147,7 +3238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3175,6 +3266,8 @@
     <col width="24" customWidth="1" min="23" max="23"/>
     <col width="24" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3303,6 +3396,16 @@
           <t>effective_to</t>
         </is>
       </c>
+      <c r="Z1" s="5" t="inlineStr">
+        <is>
+          <t>search_intent_group_id</t>
+        </is>
+      </c>
+      <c r="AA1" s="5" t="inlineStr">
+        <is>
+          <t>search_platform</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -3314,7 +3417,7 @@
         <v/>
       </c>
       <c r="C2">
-        <f>'BUILDER'!Q8</f>
+        <f>'BUILDER'!S8</f>
         <v/>
       </c>
       <c r="D2">
@@ -3330,19 +3433,19 @@
         <v/>
       </c>
       <c r="G2">
-        <f>IF(TRIM('BUILDER'!S8)&lt;&gt;"",'BUILDER'!S8,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U8)&lt;&gt;"",'BUILDER'!U8,"not specified")</f>
         <v/>
       </c>
       <c r="H2">
-        <f>IF(TRIM('BUILDER'!R8)&lt;&gt;"",'BUILDER'!R8,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T8)&lt;&gt;"",'BUILDER'!T8,"unclassified")</f>
         <v/>
       </c>
       <c r="I2">
-        <f>IF(TRIM('BUILDER'!T8)&lt;&gt;"",'BUILDER'!T8,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V8)&lt;&gt;"",'BUILDER'!V8,"not specified")</f>
         <v/>
       </c>
       <c r="J2">
-        <f>IF(TRIM('BUILDER'!U8)&lt;&gt;"",'BUILDER'!U8,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W8)&lt;&gt;"",'BUILDER'!W8,"not specified")</f>
         <v/>
       </c>
       <c r="K2">
@@ -3379,15 +3482,23 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2">
-        <f>'BUILDER'!V8</f>
+        <f>'BUILDER'!X8</f>
         <v/>
       </c>
       <c r="X2">
-        <f>'BUILDER'!W8</f>
+        <f>'BUILDER'!Y8</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>'BUILDER'!X8</f>
+        <f>'BUILDER'!Z8</f>
+        <v/>
+      </c>
+      <c r="Z2">
+        <f>'BUILDER'!Q8</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>'BUILDER'!R8</f>
         <v/>
       </c>
     </row>
@@ -3401,7 +3512,7 @@
         <v/>
       </c>
       <c r="C3">
-        <f>'BUILDER'!Q9</f>
+        <f>'BUILDER'!S9</f>
         <v/>
       </c>
       <c r="D3">
@@ -3417,19 +3528,19 @@
         <v/>
       </c>
       <c r="G3">
-        <f>IF(TRIM('BUILDER'!S9)&lt;&gt;"",'BUILDER'!S9,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U9)&lt;&gt;"",'BUILDER'!U9,"not specified")</f>
         <v/>
       </c>
       <c r="H3">
-        <f>IF(TRIM('BUILDER'!R9)&lt;&gt;"",'BUILDER'!R9,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T9)&lt;&gt;"",'BUILDER'!T9,"unclassified")</f>
         <v/>
       </c>
       <c r="I3">
-        <f>IF(TRIM('BUILDER'!T9)&lt;&gt;"",'BUILDER'!T9,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V9)&lt;&gt;"",'BUILDER'!V9,"not specified")</f>
         <v/>
       </c>
       <c r="J3">
-        <f>IF(TRIM('BUILDER'!U9)&lt;&gt;"",'BUILDER'!U9,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W9)&lt;&gt;"",'BUILDER'!W9,"not specified")</f>
         <v/>
       </c>
       <c r="K3">
@@ -3466,15 +3577,23 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3">
-        <f>'BUILDER'!V9</f>
+        <f>'BUILDER'!X9</f>
         <v/>
       </c>
       <c r="X3">
-        <f>'BUILDER'!W9</f>
+        <f>'BUILDER'!Y9</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>'BUILDER'!X9</f>
+        <f>'BUILDER'!Z9</f>
+        <v/>
+      </c>
+      <c r="Z3">
+        <f>'BUILDER'!Q9</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>'BUILDER'!R9</f>
         <v/>
       </c>
     </row>
@@ -3488,7 +3607,7 @@
         <v/>
       </c>
       <c r="C4">
-        <f>'BUILDER'!Q10</f>
+        <f>'BUILDER'!S10</f>
         <v/>
       </c>
       <c r="D4">
@@ -3504,19 +3623,19 @@
         <v/>
       </c>
       <c r="G4">
-        <f>IF(TRIM('BUILDER'!S10)&lt;&gt;"",'BUILDER'!S10,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U10)&lt;&gt;"",'BUILDER'!U10,"not specified")</f>
         <v/>
       </c>
       <c r="H4">
-        <f>IF(TRIM('BUILDER'!R10)&lt;&gt;"",'BUILDER'!R10,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T10)&lt;&gt;"",'BUILDER'!T10,"unclassified")</f>
         <v/>
       </c>
       <c r="I4">
-        <f>IF(TRIM('BUILDER'!T10)&lt;&gt;"",'BUILDER'!T10,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V10)&lt;&gt;"",'BUILDER'!V10,"not specified")</f>
         <v/>
       </c>
       <c r="J4">
-        <f>IF(TRIM('BUILDER'!U10)&lt;&gt;"",'BUILDER'!U10,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W10)&lt;&gt;"",'BUILDER'!W10,"not specified")</f>
         <v/>
       </c>
       <c r="K4">
@@ -3553,15 +3672,23 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4">
-        <f>'BUILDER'!V10</f>
+        <f>'BUILDER'!X10</f>
         <v/>
       </c>
       <c r="X4">
-        <f>'BUILDER'!W10</f>
+        <f>'BUILDER'!Y10</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>'BUILDER'!X10</f>
+        <f>'BUILDER'!Z10</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>'BUILDER'!Q10</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>'BUILDER'!R10</f>
         <v/>
       </c>
     </row>
@@ -3575,7 +3702,7 @@
         <v/>
       </c>
       <c r="C5">
-        <f>'BUILDER'!Q11</f>
+        <f>'BUILDER'!S11</f>
         <v/>
       </c>
       <c r="D5">
@@ -3591,19 +3718,19 @@
         <v/>
       </c>
       <c r="G5">
-        <f>IF(TRIM('BUILDER'!S11)&lt;&gt;"",'BUILDER'!S11,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U11)&lt;&gt;"",'BUILDER'!U11,"not specified")</f>
         <v/>
       </c>
       <c r="H5">
-        <f>IF(TRIM('BUILDER'!R11)&lt;&gt;"",'BUILDER'!R11,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T11)&lt;&gt;"",'BUILDER'!T11,"unclassified")</f>
         <v/>
       </c>
       <c r="I5">
-        <f>IF(TRIM('BUILDER'!T11)&lt;&gt;"",'BUILDER'!T11,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V11)&lt;&gt;"",'BUILDER'!V11,"not specified")</f>
         <v/>
       </c>
       <c r="J5">
-        <f>IF(TRIM('BUILDER'!U11)&lt;&gt;"",'BUILDER'!U11,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W11)&lt;&gt;"",'BUILDER'!W11,"not specified")</f>
         <v/>
       </c>
       <c r="K5">
@@ -3640,15 +3767,23 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5">
-        <f>'BUILDER'!V11</f>
+        <f>'BUILDER'!X11</f>
         <v/>
       </c>
       <c r="X5">
-        <f>'BUILDER'!W11</f>
+        <f>'BUILDER'!Y11</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>'BUILDER'!X11</f>
+        <f>'BUILDER'!Z11</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>'BUILDER'!Q11</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>'BUILDER'!R11</f>
         <v/>
       </c>
     </row>
@@ -3662,7 +3797,7 @@
         <v/>
       </c>
       <c r="C6">
-        <f>'BUILDER'!Q12</f>
+        <f>'BUILDER'!S12</f>
         <v/>
       </c>
       <c r="D6">
@@ -3678,19 +3813,19 @@
         <v/>
       </c>
       <c r="G6">
-        <f>IF(TRIM('BUILDER'!S12)&lt;&gt;"",'BUILDER'!S12,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U12)&lt;&gt;"",'BUILDER'!U12,"not specified")</f>
         <v/>
       </c>
       <c r="H6">
-        <f>IF(TRIM('BUILDER'!R12)&lt;&gt;"",'BUILDER'!R12,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T12)&lt;&gt;"",'BUILDER'!T12,"unclassified")</f>
         <v/>
       </c>
       <c r="I6">
-        <f>IF(TRIM('BUILDER'!T12)&lt;&gt;"",'BUILDER'!T12,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V12)&lt;&gt;"",'BUILDER'!V12,"not specified")</f>
         <v/>
       </c>
       <c r="J6">
-        <f>IF(TRIM('BUILDER'!U12)&lt;&gt;"",'BUILDER'!U12,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W12)&lt;&gt;"",'BUILDER'!W12,"not specified")</f>
         <v/>
       </c>
       <c r="K6">
@@ -3727,15 +3862,23 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6">
-        <f>'BUILDER'!V12</f>
+        <f>'BUILDER'!X12</f>
         <v/>
       </c>
       <c r="X6">
-        <f>'BUILDER'!W12</f>
+        <f>'BUILDER'!Y12</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>'BUILDER'!X12</f>
+        <f>'BUILDER'!Z12</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>'BUILDER'!Q12</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>'BUILDER'!R12</f>
         <v/>
       </c>
     </row>
@@ -3749,7 +3892,7 @@
         <v/>
       </c>
       <c r="C7">
-        <f>'BUILDER'!Q13</f>
+        <f>'BUILDER'!S13</f>
         <v/>
       </c>
       <c r="D7">
@@ -3765,19 +3908,19 @@
         <v/>
       </c>
       <c r="G7">
-        <f>IF(TRIM('BUILDER'!S13)&lt;&gt;"",'BUILDER'!S13,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U13)&lt;&gt;"",'BUILDER'!U13,"not specified")</f>
         <v/>
       </c>
       <c r="H7">
-        <f>IF(TRIM('BUILDER'!R13)&lt;&gt;"",'BUILDER'!R13,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T13)&lt;&gt;"",'BUILDER'!T13,"unclassified")</f>
         <v/>
       </c>
       <c r="I7">
-        <f>IF(TRIM('BUILDER'!T13)&lt;&gt;"",'BUILDER'!T13,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V13)&lt;&gt;"",'BUILDER'!V13,"not specified")</f>
         <v/>
       </c>
       <c r="J7">
-        <f>IF(TRIM('BUILDER'!U13)&lt;&gt;"",'BUILDER'!U13,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W13)&lt;&gt;"",'BUILDER'!W13,"not specified")</f>
         <v/>
       </c>
       <c r="K7">
@@ -3814,15 +3957,23 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7">
-        <f>'BUILDER'!V13</f>
+        <f>'BUILDER'!X13</f>
         <v/>
       </c>
       <c r="X7">
-        <f>'BUILDER'!W13</f>
+        <f>'BUILDER'!Y13</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>'BUILDER'!X13</f>
+        <f>'BUILDER'!Z13</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>'BUILDER'!Q13</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>'BUILDER'!R13</f>
         <v/>
       </c>
     </row>
@@ -3836,7 +3987,7 @@
         <v/>
       </c>
       <c r="C8">
-        <f>'BUILDER'!Q14</f>
+        <f>'BUILDER'!S14</f>
         <v/>
       </c>
       <c r="D8">
@@ -3852,19 +4003,19 @@
         <v/>
       </c>
       <c r="G8">
-        <f>IF(TRIM('BUILDER'!S14)&lt;&gt;"",'BUILDER'!S14,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U14)&lt;&gt;"",'BUILDER'!U14,"not specified")</f>
         <v/>
       </c>
       <c r="H8">
-        <f>IF(TRIM('BUILDER'!R14)&lt;&gt;"",'BUILDER'!R14,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T14)&lt;&gt;"",'BUILDER'!T14,"unclassified")</f>
         <v/>
       </c>
       <c r="I8">
-        <f>IF(TRIM('BUILDER'!T14)&lt;&gt;"",'BUILDER'!T14,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V14)&lt;&gt;"",'BUILDER'!V14,"not specified")</f>
         <v/>
       </c>
       <c r="J8">
-        <f>IF(TRIM('BUILDER'!U14)&lt;&gt;"",'BUILDER'!U14,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W14)&lt;&gt;"",'BUILDER'!W14,"not specified")</f>
         <v/>
       </c>
       <c r="K8">
@@ -3901,15 +4052,23 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8">
-        <f>'BUILDER'!V14</f>
+        <f>'BUILDER'!X14</f>
         <v/>
       </c>
       <c r="X8">
-        <f>'BUILDER'!W14</f>
+        <f>'BUILDER'!Y14</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>'BUILDER'!X14</f>
+        <f>'BUILDER'!Z14</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>'BUILDER'!Q14</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>'BUILDER'!R14</f>
         <v/>
       </c>
     </row>
@@ -3923,7 +4082,7 @@
         <v/>
       </c>
       <c r="C9">
-        <f>'BUILDER'!Q15</f>
+        <f>'BUILDER'!S15</f>
         <v/>
       </c>
       <c r="D9">
@@ -3939,19 +4098,19 @@
         <v/>
       </c>
       <c r="G9">
-        <f>IF(TRIM('BUILDER'!S15)&lt;&gt;"",'BUILDER'!S15,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U15)&lt;&gt;"",'BUILDER'!U15,"not specified")</f>
         <v/>
       </c>
       <c r="H9">
-        <f>IF(TRIM('BUILDER'!R15)&lt;&gt;"",'BUILDER'!R15,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T15)&lt;&gt;"",'BUILDER'!T15,"unclassified")</f>
         <v/>
       </c>
       <c r="I9">
-        <f>IF(TRIM('BUILDER'!T15)&lt;&gt;"",'BUILDER'!T15,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V15)&lt;&gt;"",'BUILDER'!V15,"not specified")</f>
         <v/>
       </c>
       <c r="J9">
-        <f>IF(TRIM('BUILDER'!U15)&lt;&gt;"",'BUILDER'!U15,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W15)&lt;&gt;"",'BUILDER'!W15,"not specified")</f>
         <v/>
       </c>
       <c r="K9">
@@ -3988,15 +4147,23 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9">
-        <f>'BUILDER'!V15</f>
+        <f>'BUILDER'!X15</f>
         <v/>
       </c>
       <c r="X9">
-        <f>'BUILDER'!W15</f>
+        <f>'BUILDER'!Y15</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>'BUILDER'!X15</f>
+        <f>'BUILDER'!Z15</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>'BUILDER'!Q15</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>'BUILDER'!R15</f>
         <v/>
       </c>
     </row>
@@ -4010,7 +4177,7 @@
         <v/>
       </c>
       <c r="C10">
-        <f>'BUILDER'!Q16</f>
+        <f>'BUILDER'!S16</f>
         <v/>
       </c>
       <c r="D10">
@@ -4026,19 +4193,19 @@
         <v/>
       </c>
       <c r="G10">
-        <f>IF(TRIM('BUILDER'!S16)&lt;&gt;"",'BUILDER'!S16,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U16)&lt;&gt;"",'BUILDER'!U16,"not specified")</f>
         <v/>
       </c>
       <c r="H10">
-        <f>IF(TRIM('BUILDER'!R16)&lt;&gt;"",'BUILDER'!R16,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T16)&lt;&gt;"",'BUILDER'!T16,"unclassified")</f>
         <v/>
       </c>
       <c r="I10">
-        <f>IF(TRIM('BUILDER'!T16)&lt;&gt;"",'BUILDER'!T16,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V16)&lt;&gt;"",'BUILDER'!V16,"not specified")</f>
         <v/>
       </c>
       <c r="J10">
-        <f>IF(TRIM('BUILDER'!U16)&lt;&gt;"",'BUILDER'!U16,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W16)&lt;&gt;"",'BUILDER'!W16,"not specified")</f>
         <v/>
       </c>
       <c r="K10">
@@ -4075,15 +4242,23 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10">
-        <f>'BUILDER'!V16</f>
+        <f>'BUILDER'!X16</f>
         <v/>
       </c>
       <c r="X10">
-        <f>'BUILDER'!W16</f>
+        <f>'BUILDER'!Y16</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>'BUILDER'!X16</f>
+        <f>'BUILDER'!Z16</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>'BUILDER'!Q16</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>'BUILDER'!R16</f>
         <v/>
       </c>
     </row>
@@ -4097,7 +4272,7 @@
         <v/>
       </c>
       <c r="C11">
-        <f>'BUILDER'!Q17</f>
+        <f>'BUILDER'!S17</f>
         <v/>
       </c>
       <c r="D11">
@@ -4113,19 +4288,19 @@
         <v/>
       </c>
       <c r="G11">
-        <f>IF(TRIM('BUILDER'!S17)&lt;&gt;"",'BUILDER'!S17,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U17)&lt;&gt;"",'BUILDER'!U17,"not specified")</f>
         <v/>
       </c>
       <c r="H11">
-        <f>IF(TRIM('BUILDER'!R17)&lt;&gt;"",'BUILDER'!R17,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T17)&lt;&gt;"",'BUILDER'!T17,"unclassified")</f>
         <v/>
       </c>
       <c r="I11">
-        <f>IF(TRIM('BUILDER'!T17)&lt;&gt;"",'BUILDER'!T17,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V17)&lt;&gt;"",'BUILDER'!V17,"not specified")</f>
         <v/>
       </c>
       <c r="J11">
-        <f>IF(TRIM('BUILDER'!U17)&lt;&gt;"",'BUILDER'!U17,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W17)&lt;&gt;"",'BUILDER'!W17,"not specified")</f>
         <v/>
       </c>
       <c r="K11">
@@ -4162,15 +4337,23 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11">
-        <f>'BUILDER'!V17</f>
+        <f>'BUILDER'!X17</f>
         <v/>
       </c>
       <c r="X11">
-        <f>'BUILDER'!W17</f>
+        <f>'BUILDER'!Y17</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>'BUILDER'!X17</f>
+        <f>'BUILDER'!Z17</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>'BUILDER'!Q17</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>'BUILDER'!R17</f>
         <v/>
       </c>
     </row>
@@ -4184,7 +4367,7 @@
         <v/>
       </c>
       <c r="C12">
-        <f>'BUILDER'!Q18</f>
+        <f>'BUILDER'!S18</f>
         <v/>
       </c>
       <c r="D12">
@@ -4200,19 +4383,19 @@
         <v/>
       </c>
       <c r="G12">
-        <f>IF(TRIM('BUILDER'!S18)&lt;&gt;"",'BUILDER'!S18,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U18)&lt;&gt;"",'BUILDER'!U18,"not specified")</f>
         <v/>
       </c>
       <c r="H12">
-        <f>IF(TRIM('BUILDER'!R18)&lt;&gt;"",'BUILDER'!R18,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T18)&lt;&gt;"",'BUILDER'!T18,"unclassified")</f>
         <v/>
       </c>
       <c r="I12">
-        <f>IF(TRIM('BUILDER'!T18)&lt;&gt;"",'BUILDER'!T18,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V18)&lt;&gt;"",'BUILDER'!V18,"not specified")</f>
         <v/>
       </c>
       <c r="J12">
-        <f>IF(TRIM('BUILDER'!U18)&lt;&gt;"",'BUILDER'!U18,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W18)&lt;&gt;"",'BUILDER'!W18,"not specified")</f>
         <v/>
       </c>
       <c r="K12">
@@ -4249,15 +4432,23 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12">
-        <f>'BUILDER'!V18</f>
+        <f>'BUILDER'!X18</f>
         <v/>
       </c>
       <c r="X12">
-        <f>'BUILDER'!W18</f>
+        <f>'BUILDER'!Y18</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>'BUILDER'!X18</f>
+        <f>'BUILDER'!Z18</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>'BUILDER'!Q18</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>'BUILDER'!R18</f>
         <v/>
       </c>
     </row>
@@ -4271,7 +4462,7 @@
         <v/>
       </c>
       <c r="C13">
-        <f>'BUILDER'!Q19</f>
+        <f>'BUILDER'!S19</f>
         <v/>
       </c>
       <c r="D13">
@@ -4287,19 +4478,19 @@
         <v/>
       </c>
       <c r="G13">
-        <f>IF(TRIM('BUILDER'!S19)&lt;&gt;"",'BUILDER'!S19,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U19)&lt;&gt;"",'BUILDER'!U19,"not specified")</f>
         <v/>
       </c>
       <c r="H13">
-        <f>IF(TRIM('BUILDER'!R19)&lt;&gt;"",'BUILDER'!R19,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T19)&lt;&gt;"",'BUILDER'!T19,"unclassified")</f>
         <v/>
       </c>
       <c r="I13">
-        <f>IF(TRIM('BUILDER'!T19)&lt;&gt;"",'BUILDER'!T19,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V19)&lt;&gt;"",'BUILDER'!V19,"not specified")</f>
         <v/>
       </c>
       <c r="J13">
-        <f>IF(TRIM('BUILDER'!U19)&lt;&gt;"",'BUILDER'!U19,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W19)&lt;&gt;"",'BUILDER'!W19,"not specified")</f>
         <v/>
       </c>
       <c r="K13">
@@ -4336,15 +4527,23 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13">
-        <f>'BUILDER'!V19</f>
+        <f>'BUILDER'!X19</f>
         <v/>
       </c>
       <c r="X13">
-        <f>'BUILDER'!W19</f>
+        <f>'BUILDER'!Y19</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>'BUILDER'!X19</f>
+        <f>'BUILDER'!Z19</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>'BUILDER'!Q19</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>'BUILDER'!R19</f>
         <v/>
       </c>
     </row>
@@ -4358,7 +4557,7 @@
         <v/>
       </c>
       <c r="C14">
-        <f>'BUILDER'!Q20</f>
+        <f>'BUILDER'!S20</f>
         <v/>
       </c>
       <c r="D14">
@@ -4374,19 +4573,19 @@
         <v/>
       </c>
       <c r="G14">
-        <f>IF(TRIM('BUILDER'!S20)&lt;&gt;"",'BUILDER'!S20,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U20)&lt;&gt;"",'BUILDER'!U20,"not specified")</f>
         <v/>
       </c>
       <c r="H14">
-        <f>IF(TRIM('BUILDER'!R20)&lt;&gt;"",'BUILDER'!R20,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T20)&lt;&gt;"",'BUILDER'!T20,"unclassified")</f>
         <v/>
       </c>
       <c r="I14">
-        <f>IF(TRIM('BUILDER'!T20)&lt;&gt;"",'BUILDER'!T20,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V20)&lt;&gt;"",'BUILDER'!V20,"not specified")</f>
         <v/>
       </c>
       <c r="J14">
-        <f>IF(TRIM('BUILDER'!U20)&lt;&gt;"",'BUILDER'!U20,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W20)&lt;&gt;"",'BUILDER'!W20,"not specified")</f>
         <v/>
       </c>
       <c r="K14">
@@ -4423,15 +4622,23 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14">
-        <f>'BUILDER'!V20</f>
+        <f>'BUILDER'!X20</f>
         <v/>
       </c>
       <c r="X14">
-        <f>'BUILDER'!W20</f>
+        <f>'BUILDER'!Y20</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>'BUILDER'!X20</f>
+        <f>'BUILDER'!Z20</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>'BUILDER'!Q20</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>'BUILDER'!R20</f>
         <v/>
       </c>
     </row>
@@ -4445,7 +4652,7 @@
         <v/>
       </c>
       <c r="C15">
-        <f>'BUILDER'!Q21</f>
+        <f>'BUILDER'!S21</f>
         <v/>
       </c>
       <c r="D15">
@@ -4461,19 +4668,19 @@
         <v/>
       </c>
       <c r="G15">
-        <f>IF(TRIM('BUILDER'!S21)&lt;&gt;"",'BUILDER'!S21,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U21)&lt;&gt;"",'BUILDER'!U21,"not specified")</f>
         <v/>
       </c>
       <c r="H15">
-        <f>IF(TRIM('BUILDER'!R21)&lt;&gt;"",'BUILDER'!R21,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T21)&lt;&gt;"",'BUILDER'!T21,"unclassified")</f>
         <v/>
       </c>
       <c r="I15">
-        <f>IF(TRIM('BUILDER'!T21)&lt;&gt;"",'BUILDER'!T21,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V21)&lt;&gt;"",'BUILDER'!V21,"not specified")</f>
         <v/>
       </c>
       <c r="J15">
-        <f>IF(TRIM('BUILDER'!U21)&lt;&gt;"",'BUILDER'!U21,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W21)&lt;&gt;"",'BUILDER'!W21,"not specified")</f>
         <v/>
       </c>
       <c r="K15">
@@ -4510,15 +4717,23 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15">
-        <f>'BUILDER'!V21</f>
+        <f>'BUILDER'!X21</f>
         <v/>
       </c>
       <c r="X15">
-        <f>'BUILDER'!W21</f>
+        <f>'BUILDER'!Y21</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>'BUILDER'!X21</f>
+        <f>'BUILDER'!Z21</f>
+        <v/>
+      </c>
+      <c r="Z15">
+        <f>'BUILDER'!Q21</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>'BUILDER'!R21</f>
         <v/>
       </c>
     </row>
@@ -4532,7 +4747,7 @@
         <v/>
       </c>
       <c r="C16">
-        <f>'BUILDER'!Q22</f>
+        <f>'BUILDER'!S22</f>
         <v/>
       </c>
       <c r="D16">
@@ -4548,19 +4763,19 @@
         <v/>
       </c>
       <c r="G16">
-        <f>IF(TRIM('BUILDER'!S22)&lt;&gt;"",'BUILDER'!S22,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U22)&lt;&gt;"",'BUILDER'!U22,"not specified")</f>
         <v/>
       </c>
       <c r="H16">
-        <f>IF(TRIM('BUILDER'!R22)&lt;&gt;"",'BUILDER'!R22,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T22)&lt;&gt;"",'BUILDER'!T22,"unclassified")</f>
         <v/>
       </c>
       <c r="I16">
-        <f>IF(TRIM('BUILDER'!T22)&lt;&gt;"",'BUILDER'!T22,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V22)&lt;&gt;"",'BUILDER'!V22,"not specified")</f>
         <v/>
       </c>
       <c r="J16">
-        <f>IF(TRIM('BUILDER'!U22)&lt;&gt;"",'BUILDER'!U22,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W22)&lt;&gt;"",'BUILDER'!W22,"not specified")</f>
         <v/>
       </c>
       <c r="K16">
@@ -4597,15 +4812,23 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16">
-        <f>'BUILDER'!V22</f>
+        <f>'BUILDER'!X22</f>
         <v/>
       </c>
       <c r="X16">
-        <f>'BUILDER'!W22</f>
+        <f>'BUILDER'!Y22</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>'BUILDER'!X22</f>
+        <f>'BUILDER'!Z22</f>
+        <v/>
+      </c>
+      <c r="Z16">
+        <f>'BUILDER'!Q22</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>'BUILDER'!R22</f>
         <v/>
       </c>
     </row>
@@ -4619,7 +4842,7 @@
         <v/>
       </c>
       <c r="C17">
-        <f>'BUILDER'!Q23</f>
+        <f>'BUILDER'!S23</f>
         <v/>
       </c>
       <c r="D17">
@@ -4635,19 +4858,19 @@
         <v/>
       </c>
       <c r="G17">
-        <f>IF(TRIM('BUILDER'!S23)&lt;&gt;"",'BUILDER'!S23,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U23)&lt;&gt;"",'BUILDER'!U23,"not specified")</f>
         <v/>
       </c>
       <c r="H17">
-        <f>IF(TRIM('BUILDER'!R23)&lt;&gt;"",'BUILDER'!R23,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T23)&lt;&gt;"",'BUILDER'!T23,"unclassified")</f>
         <v/>
       </c>
       <c r="I17">
-        <f>IF(TRIM('BUILDER'!T23)&lt;&gt;"",'BUILDER'!T23,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V23)&lt;&gt;"",'BUILDER'!V23,"not specified")</f>
         <v/>
       </c>
       <c r="J17">
-        <f>IF(TRIM('BUILDER'!U23)&lt;&gt;"",'BUILDER'!U23,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W23)&lt;&gt;"",'BUILDER'!W23,"not specified")</f>
         <v/>
       </c>
       <c r="K17">
@@ -4684,15 +4907,23 @@
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17">
-        <f>'BUILDER'!V23</f>
+        <f>'BUILDER'!X23</f>
         <v/>
       </c>
       <c r="X17">
-        <f>'BUILDER'!W23</f>
+        <f>'BUILDER'!Y23</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>'BUILDER'!X23</f>
+        <f>'BUILDER'!Z23</f>
+        <v/>
+      </c>
+      <c r="Z17">
+        <f>'BUILDER'!Q23</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>'BUILDER'!R23</f>
         <v/>
       </c>
     </row>
@@ -4706,7 +4937,7 @@
         <v/>
       </c>
       <c r="C18">
-        <f>'BUILDER'!Q24</f>
+        <f>'BUILDER'!S24</f>
         <v/>
       </c>
       <c r="D18">
@@ -4722,19 +4953,19 @@
         <v/>
       </c>
       <c r="G18">
-        <f>IF(TRIM('BUILDER'!S24)&lt;&gt;"",'BUILDER'!S24,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U24)&lt;&gt;"",'BUILDER'!U24,"not specified")</f>
         <v/>
       </c>
       <c r="H18">
-        <f>IF(TRIM('BUILDER'!R24)&lt;&gt;"",'BUILDER'!R24,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T24)&lt;&gt;"",'BUILDER'!T24,"unclassified")</f>
         <v/>
       </c>
       <c r="I18">
-        <f>IF(TRIM('BUILDER'!T24)&lt;&gt;"",'BUILDER'!T24,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V24)&lt;&gt;"",'BUILDER'!V24,"not specified")</f>
         <v/>
       </c>
       <c r="J18">
-        <f>IF(TRIM('BUILDER'!U24)&lt;&gt;"",'BUILDER'!U24,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W24)&lt;&gt;"",'BUILDER'!W24,"not specified")</f>
         <v/>
       </c>
       <c r="K18">
@@ -4771,15 +5002,23 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18">
-        <f>'BUILDER'!V24</f>
+        <f>'BUILDER'!X24</f>
         <v/>
       </c>
       <c r="X18">
-        <f>'BUILDER'!W24</f>
+        <f>'BUILDER'!Y24</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>'BUILDER'!X24</f>
+        <f>'BUILDER'!Z24</f>
+        <v/>
+      </c>
+      <c r="Z18">
+        <f>'BUILDER'!Q24</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>'BUILDER'!R24</f>
         <v/>
       </c>
     </row>
@@ -4793,7 +5032,7 @@
         <v/>
       </c>
       <c r="C19">
-        <f>'BUILDER'!Q25</f>
+        <f>'BUILDER'!S25</f>
         <v/>
       </c>
       <c r="D19">
@@ -4809,19 +5048,19 @@
         <v/>
       </c>
       <c r="G19">
-        <f>IF(TRIM('BUILDER'!S25)&lt;&gt;"",'BUILDER'!S25,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U25)&lt;&gt;"",'BUILDER'!U25,"not specified")</f>
         <v/>
       </c>
       <c r="H19">
-        <f>IF(TRIM('BUILDER'!R25)&lt;&gt;"",'BUILDER'!R25,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T25)&lt;&gt;"",'BUILDER'!T25,"unclassified")</f>
         <v/>
       </c>
       <c r="I19">
-        <f>IF(TRIM('BUILDER'!T25)&lt;&gt;"",'BUILDER'!T25,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V25)&lt;&gt;"",'BUILDER'!V25,"not specified")</f>
         <v/>
       </c>
       <c r="J19">
-        <f>IF(TRIM('BUILDER'!U25)&lt;&gt;"",'BUILDER'!U25,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W25)&lt;&gt;"",'BUILDER'!W25,"not specified")</f>
         <v/>
       </c>
       <c r="K19">
@@ -4858,15 +5097,23 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19">
-        <f>'BUILDER'!V25</f>
+        <f>'BUILDER'!X25</f>
         <v/>
       </c>
       <c r="X19">
-        <f>'BUILDER'!W25</f>
+        <f>'BUILDER'!Y25</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>'BUILDER'!X25</f>
+        <f>'BUILDER'!Z25</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>'BUILDER'!Q25</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>'BUILDER'!R25</f>
         <v/>
       </c>
     </row>
@@ -4880,7 +5127,7 @@
         <v/>
       </c>
       <c r="C20">
-        <f>'BUILDER'!Q26</f>
+        <f>'BUILDER'!S26</f>
         <v/>
       </c>
       <c r="D20">
@@ -4896,19 +5143,19 @@
         <v/>
       </c>
       <c r="G20">
-        <f>IF(TRIM('BUILDER'!S26)&lt;&gt;"",'BUILDER'!S26,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U26)&lt;&gt;"",'BUILDER'!U26,"not specified")</f>
         <v/>
       </c>
       <c r="H20">
-        <f>IF(TRIM('BUILDER'!R26)&lt;&gt;"",'BUILDER'!R26,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T26)&lt;&gt;"",'BUILDER'!T26,"unclassified")</f>
         <v/>
       </c>
       <c r="I20">
-        <f>IF(TRIM('BUILDER'!T26)&lt;&gt;"",'BUILDER'!T26,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V26)&lt;&gt;"",'BUILDER'!V26,"not specified")</f>
         <v/>
       </c>
       <c r="J20">
-        <f>IF(TRIM('BUILDER'!U26)&lt;&gt;"",'BUILDER'!U26,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W26)&lt;&gt;"",'BUILDER'!W26,"not specified")</f>
         <v/>
       </c>
       <c r="K20">
@@ -4945,15 +5192,23 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20">
-        <f>'BUILDER'!V26</f>
+        <f>'BUILDER'!X26</f>
         <v/>
       </c>
       <c r="X20">
-        <f>'BUILDER'!W26</f>
+        <f>'BUILDER'!Y26</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>'BUILDER'!X26</f>
+        <f>'BUILDER'!Z26</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>'BUILDER'!Q26</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>'BUILDER'!R26</f>
         <v/>
       </c>
     </row>
@@ -4967,7 +5222,7 @@
         <v/>
       </c>
       <c r="C21">
-        <f>'BUILDER'!Q27</f>
+        <f>'BUILDER'!S27</f>
         <v/>
       </c>
       <c r="D21">
@@ -4983,19 +5238,19 @@
         <v/>
       </c>
       <c r="G21">
-        <f>IF(TRIM('BUILDER'!S27)&lt;&gt;"",'BUILDER'!S27,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U27)&lt;&gt;"",'BUILDER'!U27,"not specified")</f>
         <v/>
       </c>
       <c r="H21">
-        <f>IF(TRIM('BUILDER'!R27)&lt;&gt;"",'BUILDER'!R27,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T27)&lt;&gt;"",'BUILDER'!T27,"unclassified")</f>
         <v/>
       </c>
       <c r="I21">
-        <f>IF(TRIM('BUILDER'!T27)&lt;&gt;"",'BUILDER'!T27,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V27)&lt;&gt;"",'BUILDER'!V27,"not specified")</f>
         <v/>
       </c>
       <c r="J21">
-        <f>IF(TRIM('BUILDER'!U27)&lt;&gt;"",'BUILDER'!U27,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W27)&lt;&gt;"",'BUILDER'!W27,"not specified")</f>
         <v/>
       </c>
       <c r="K21">
@@ -5032,15 +5287,23 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21">
-        <f>'BUILDER'!V27</f>
+        <f>'BUILDER'!X27</f>
         <v/>
       </c>
       <c r="X21">
-        <f>'BUILDER'!W27</f>
+        <f>'BUILDER'!Y27</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>'BUILDER'!X27</f>
+        <f>'BUILDER'!Z27</f>
+        <v/>
+      </c>
+      <c r="Z21">
+        <f>'BUILDER'!Q27</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>'BUILDER'!R27</f>
         <v/>
       </c>
     </row>
@@ -5054,7 +5317,7 @@
         <v/>
       </c>
       <c r="C22">
-        <f>'BUILDER'!Q28</f>
+        <f>'BUILDER'!S28</f>
         <v/>
       </c>
       <c r="D22">
@@ -5070,19 +5333,19 @@
         <v/>
       </c>
       <c r="G22">
-        <f>IF(TRIM('BUILDER'!S28)&lt;&gt;"",'BUILDER'!S28,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U28)&lt;&gt;"",'BUILDER'!U28,"not specified")</f>
         <v/>
       </c>
       <c r="H22">
-        <f>IF(TRIM('BUILDER'!R28)&lt;&gt;"",'BUILDER'!R28,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T28)&lt;&gt;"",'BUILDER'!T28,"unclassified")</f>
         <v/>
       </c>
       <c r="I22">
-        <f>IF(TRIM('BUILDER'!T28)&lt;&gt;"",'BUILDER'!T28,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V28)&lt;&gt;"",'BUILDER'!V28,"not specified")</f>
         <v/>
       </c>
       <c r="J22">
-        <f>IF(TRIM('BUILDER'!U28)&lt;&gt;"",'BUILDER'!U28,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W28)&lt;&gt;"",'BUILDER'!W28,"not specified")</f>
         <v/>
       </c>
       <c r="K22">
@@ -5119,15 +5382,23 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22">
-        <f>'BUILDER'!V28</f>
+        <f>'BUILDER'!X28</f>
         <v/>
       </c>
       <c r="X22">
-        <f>'BUILDER'!W28</f>
+        <f>'BUILDER'!Y28</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>'BUILDER'!X28</f>
+        <f>'BUILDER'!Z28</f>
+        <v/>
+      </c>
+      <c r="Z22">
+        <f>'BUILDER'!Q28</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>'BUILDER'!R28</f>
         <v/>
       </c>
     </row>
@@ -5141,7 +5412,7 @@
         <v/>
       </c>
       <c r="C23">
-        <f>'BUILDER'!Q29</f>
+        <f>'BUILDER'!S29</f>
         <v/>
       </c>
       <c r="D23">
@@ -5157,19 +5428,19 @@
         <v/>
       </c>
       <c r="G23">
-        <f>IF(TRIM('BUILDER'!S29)&lt;&gt;"",'BUILDER'!S29,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U29)&lt;&gt;"",'BUILDER'!U29,"not specified")</f>
         <v/>
       </c>
       <c r="H23">
-        <f>IF(TRIM('BUILDER'!R29)&lt;&gt;"",'BUILDER'!R29,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T29)&lt;&gt;"",'BUILDER'!T29,"unclassified")</f>
         <v/>
       </c>
       <c r="I23">
-        <f>IF(TRIM('BUILDER'!T29)&lt;&gt;"",'BUILDER'!T29,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V29)&lt;&gt;"",'BUILDER'!V29,"not specified")</f>
         <v/>
       </c>
       <c r="J23">
-        <f>IF(TRIM('BUILDER'!U29)&lt;&gt;"",'BUILDER'!U29,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W29)&lt;&gt;"",'BUILDER'!W29,"not specified")</f>
         <v/>
       </c>
       <c r="K23">
@@ -5206,15 +5477,23 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23">
-        <f>'BUILDER'!V29</f>
+        <f>'BUILDER'!X29</f>
         <v/>
       </c>
       <c r="X23">
-        <f>'BUILDER'!W29</f>
+        <f>'BUILDER'!Y29</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>'BUILDER'!X29</f>
+        <f>'BUILDER'!Z29</f>
+        <v/>
+      </c>
+      <c r="Z23">
+        <f>'BUILDER'!Q29</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>'BUILDER'!R29</f>
         <v/>
       </c>
     </row>
@@ -5228,7 +5507,7 @@
         <v/>
       </c>
       <c r="C24">
-        <f>'BUILDER'!Q30</f>
+        <f>'BUILDER'!S30</f>
         <v/>
       </c>
       <c r="D24">
@@ -5244,19 +5523,19 @@
         <v/>
       </c>
       <c r="G24">
-        <f>IF(TRIM('BUILDER'!S30)&lt;&gt;"",'BUILDER'!S30,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U30)&lt;&gt;"",'BUILDER'!U30,"not specified")</f>
         <v/>
       </c>
       <c r="H24">
-        <f>IF(TRIM('BUILDER'!R30)&lt;&gt;"",'BUILDER'!R30,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T30)&lt;&gt;"",'BUILDER'!T30,"unclassified")</f>
         <v/>
       </c>
       <c r="I24">
-        <f>IF(TRIM('BUILDER'!T30)&lt;&gt;"",'BUILDER'!T30,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V30)&lt;&gt;"",'BUILDER'!V30,"not specified")</f>
         <v/>
       </c>
       <c r="J24">
-        <f>IF(TRIM('BUILDER'!U30)&lt;&gt;"",'BUILDER'!U30,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W30)&lt;&gt;"",'BUILDER'!W30,"not specified")</f>
         <v/>
       </c>
       <c r="K24">
@@ -5293,15 +5572,23 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24">
-        <f>'BUILDER'!V30</f>
+        <f>'BUILDER'!X30</f>
         <v/>
       </c>
       <c r="X24">
-        <f>'BUILDER'!W30</f>
+        <f>'BUILDER'!Y30</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>'BUILDER'!X30</f>
+        <f>'BUILDER'!Z30</f>
+        <v/>
+      </c>
+      <c r="Z24">
+        <f>'BUILDER'!Q30</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>'BUILDER'!R30</f>
         <v/>
       </c>
     </row>
@@ -5315,7 +5602,7 @@
         <v/>
       </c>
       <c r="C25">
-        <f>'BUILDER'!Q31</f>
+        <f>'BUILDER'!S31</f>
         <v/>
       </c>
       <c r="D25">
@@ -5331,19 +5618,19 @@
         <v/>
       </c>
       <c r="G25">
-        <f>IF(TRIM('BUILDER'!S31)&lt;&gt;"",'BUILDER'!S31,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!U31)&lt;&gt;"",'BUILDER'!U31,"not specified")</f>
         <v/>
       </c>
       <c r="H25">
-        <f>IF(TRIM('BUILDER'!R31)&lt;&gt;"",'BUILDER'!R31,"unclassified")</f>
+        <f>IF(TRIM('BUILDER'!T31)&lt;&gt;"",'BUILDER'!T31,"unclassified")</f>
         <v/>
       </c>
       <c r="I25">
-        <f>IF(TRIM('BUILDER'!T31)&lt;&gt;"",'BUILDER'!T31,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!V31)&lt;&gt;"",'BUILDER'!V31,"not specified")</f>
         <v/>
       </c>
       <c r="J25">
-        <f>IF(TRIM('BUILDER'!U31)&lt;&gt;"",'BUILDER'!U31,"not specified")</f>
+        <f>IF(TRIM('BUILDER'!W31)&lt;&gt;"",'BUILDER'!W31,"not specified")</f>
         <v/>
       </c>
       <c r="K25">
@@ -5380,15 +5667,23 @@
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25">
-        <f>'BUILDER'!V31</f>
+        <f>'BUILDER'!X31</f>
         <v/>
       </c>
       <c r="X25">
-        <f>'BUILDER'!W31</f>
+        <f>'BUILDER'!Y31</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>'BUILDER'!X31</f>
+        <f>'BUILDER'!Z31</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>'BUILDER'!Q31</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>'BUILDER'!R31</f>
         <v/>
       </c>
     </row>
@@ -5406,7 +5701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5467,7 +5762,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>owned</t>
+          <t>external_event</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5489,7 +5784,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>earned</t>
+          <t>owned</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -5511,7 +5806,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>external_event</t>
+          <t>earned</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -5533,7 +5828,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>mediator</t>
+          <t>control</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -5555,7 +5850,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>mediator</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -5599,7 +5894,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -5643,7 +5938,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>paid_media_cost</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -5665,7 +5960,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>fully_loaded_cost</t>
+          <t>campaign_cost</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -5687,7 +5982,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>paid_media_cost</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -5731,7 +6026,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>campaign_cost</t>
+          <t>fully_loaded_cost</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -5753,7 +6048,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>optimisable</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -5775,7 +6070,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>excluded</t>
+          <t>scenario_only</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -5797,7 +6092,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>optimisable</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -5819,7 +6114,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>scenario_only</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -6034,51 +6329,51 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>search_platform / search_intent_group_id</t>
+          <t>search_intent_group_id</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Not offered by this builder</t>
+          <t>brand_search / non_brand_search</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Not activity_dictionary columns today -- the standard upload doesn't map them.</t>
+          <t>Governed closed enum -- a blank cell (not a random typed value) means unclassified.</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Configured separately, after upload, in the governed Search-taxonomy admin mapping. Use platform and campaign_type above to keep your activity_id readable in the meantime.</t>
+          <t>Leave blank for a non-Search activity, or a Search activity whose history only supports an aggregate Brand/Non-Brand view. Rejected on a PMax/Demand Gen/YouTube campaign_type.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>search_platform</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Free text — no fixed list</t>
+          <t>google / bing</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Not a governed enum.</t>
+          <t>Governed closed enum -- a blank cell means unclassified (platform-aggregate).</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Enter as plain text; there is no dropdown.</t>
+          <t>Leave blank when your Search history does not reliably support a Google/Bing split. Rejected on a PMax/Demand Gen/YouTube campaign_type.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>market</t>
+          <t>channel</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -6100,7 +6395,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>market</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -6122,7 +6417,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>model_input_measure</t>
+          <t>source</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -6144,7 +6439,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>product_advertised</t>
+          <t>model_input_measure</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -6166,7 +6461,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>message_type</t>
+          <t>product_advertised</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -6188,7 +6483,7 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>pooling_group_id</t>
+          <t>message_type</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -6210,7 +6505,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>pooling_group_id</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -6232,7 +6527,7 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>effective_from</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -6254,27 +6549,49 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
+          <t>effective_from</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Free text — no fixed list</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Not a governed enum.</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Enter as plain text; there is no dropdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
           <t>effective_to</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Free text — no fixed list</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Not a governed enum.</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Enter as plain text; there is no dropdown.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D39"/>
+  <autoFilter ref="A1:D40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
